--- a/DTS_204_Dataset.xlsx
+++ b/DTS_204_Dataset.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H345"/>
+  <dimension ref="A1:H334"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -503,6 +503,23 @@
           <t>Torgersen</t>
         </is>
       </c>
+      <c r="C5">
+        <v>36.7</v>
+      </c>
+      <c r="D5">
+        <v>19.3</v>
+      </c>
+      <c r="E5">
+        <v>193</v>
+      </c>
+      <c r="F5">
+        <v>3450</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
       <c r="H5">
         <v>2007</v>
       </c>
@@ -519,20 +536,20 @@
         </is>
       </c>
       <c r="C6">
-        <v>36.7</v>
+        <v>39.3</v>
       </c>
       <c r="D6">
-        <v>19.3</v>
+        <v>20.6</v>
       </c>
       <c r="E6">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F6">
-        <v>3450</v>
+        <v>3650</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H6">
@@ -551,20 +568,20 @@
         </is>
       </c>
       <c r="C7">
-        <v>39.3</v>
+        <v>38.9</v>
       </c>
       <c r="D7">
-        <v>20.6</v>
+        <v>17.8</v>
       </c>
       <c r="E7">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="F7">
-        <v>3650</v>
+        <v>3625</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H7">
@@ -583,20 +600,20 @@
         </is>
       </c>
       <c r="C8">
-        <v>38.9</v>
+        <v>39.2</v>
       </c>
       <c r="D8">
-        <v>17.8</v>
+        <v>19.6</v>
       </c>
       <c r="E8">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="F8">
-        <v>3625</v>
+        <v>4675</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H8">
@@ -615,20 +632,20 @@
         </is>
       </c>
       <c r="C9">
-        <v>39.2</v>
+        <v>41.1</v>
       </c>
       <c r="D9">
-        <v>19.6</v>
+        <v>17.6</v>
       </c>
       <c r="E9">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="F9">
-        <v>4675</v>
+        <v>3200</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H9">
@@ -647,16 +664,21 @@
         </is>
       </c>
       <c r="C10">
-        <v>34.1</v>
+        <v>38.6</v>
       </c>
       <c r="D10">
-        <v>18.1</v>
+        <v>21.2</v>
       </c>
       <c r="E10">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F10">
-        <v>3475</v>
+        <v>3800</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
       </c>
       <c r="H10">
         <v>2007</v>
@@ -674,16 +696,21 @@
         </is>
       </c>
       <c r="C11">
-        <v>42</v>
+        <v>34.6</v>
       </c>
       <c r="D11">
-        <v>20.2</v>
+        <v>21.1</v>
       </c>
       <c r="E11">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="F11">
-        <v>4250</v>
+        <v>4400</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
       </c>
       <c r="H11">
         <v>2007</v>
@@ -701,16 +728,21 @@
         </is>
       </c>
       <c r="C12">
-        <v>37.8</v>
+        <v>36.6</v>
       </c>
       <c r="D12">
-        <v>17.1</v>
+        <v>17.8</v>
       </c>
       <c r="E12">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F12">
-        <v>3300</v>
+        <v>3700</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
       </c>
       <c r="H12">
         <v>2007</v>
@@ -728,16 +760,21 @@
         </is>
       </c>
       <c r="C13">
-        <v>37.8</v>
+        <v>38.7</v>
       </c>
       <c r="D13">
-        <v>17.3</v>
+        <v>19</v>
       </c>
       <c r="E13">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="F13">
-        <v>3700</v>
+        <v>3450</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
       </c>
       <c r="H13">
         <v>2007</v>
@@ -755,20 +792,20 @@
         </is>
       </c>
       <c r="C14">
-        <v>41.1</v>
+        <v>42.5</v>
       </c>
       <c r="D14">
-        <v>17.6</v>
+        <v>20.7</v>
       </c>
       <c r="E14">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="F14">
-        <v>3200</v>
+        <v>4500</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H14">
@@ -787,20 +824,20 @@
         </is>
       </c>
       <c r="C15">
-        <v>38.6</v>
+        <v>34.4</v>
       </c>
       <c r="D15">
-        <v>21.2</v>
+        <v>18.4</v>
       </c>
       <c r="E15">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="F15">
-        <v>3800</v>
+        <v>3325</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H15">
@@ -819,16 +856,16 @@
         </is>
       </c>
       <c r="C16">
-        <v>34.6</v>
+        <v>46</v>
       </c>
       <c r="D16">
-        <v>21.1</v>
+        <v>21.5</v>
       </c>
       <c r="E16">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="F16">
-        <v>4400</v>
+        <v>4200</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -847,20 +884,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Torgersen</t>
+          <t>Biscoe</t>
         </is>
       </c>
       <c r="C17">
-        <v>36.6</v>
+        <v>37.8</v>
       </c>
       <c r="D17">
-        <v>17.8</v>
+        <v>18.3</v>
       </c>
       <c r="E17">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="F17">
-        <v>3700</v>
+        <v>3400</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -879,24 +916,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Torgersen</t>
+          <t>Biscoe</t>
         </is>
       </c>
       <c r="C18">
-        <v>38.7</v>
+        <v>37.7</v>
       </c>
       <c r="D18">
-        <v>19</v>
+        <v>18.7</v>
       </c>
       <c r="E18">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="F18">
-        <v>3450</v>
+        <v>3600</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H18">
@@ -911,24 +948,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Torgersen</t>
+          <t>Biscoe</t>
         </is>
       </c>
       <c r="C19">
-        <v>42.5</v>
+        <v>35.9</v>
       </c>
       <c r="D19">
-        <v>20.7</v>
+        <v>19.2</v>
       </c>
       <c r="E19">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="F19">
-        <v>4500</v>
+        <v>3800</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H19">
@@ -943,24 +980,24 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Torgersen</t>
+          <t>Biscoe</t>
         </is>
       </c>
       <c r="C20">
-        <v>34.4</v>
+        <v>38.2</v>
       </c>
       <c r="D20">
-        <v>18.4</v>
+        <v>18.1</v>
       </c>
       <c r="E20">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F20">
-        <v>3325</v>
+        <v>3950</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H20">
@@ -975,20 +1012,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Torgersen</t>
+          <t>Biscoe</t>
         </is>
       </c>
       <c r="C21">
-        <v>46</v>
+        <v>38.8</v>
       </c>
       <c r="D21">
-        <v>21.5</v>
+        <v>17.2</v>
       </c>
       <c r="E21">
-        <v>194</v>
+        <v>180</v>
       </c>
       <c r="F21">
-        <v>4200</v>
+        <v>3800</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1011,16 +1048,16 @@
         </is>
       </c>
       <c r="C22">
-        <v>37.8</v>
+        <v>35.3</v>
       </c>
       <c r="D22">
-        <v>18.3</v>
+        <v>18.9</v>
       </c>
       <c r="E22">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="F22">
-        <v>3400</v>
+        <v>3800</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1043,16 +1080,16 @@
         </is>
       </c>
       <c r="C23">
-        <v>37.7</v>
+        <v>40.6</v>
       </c>
       <c r="D23">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="E23">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="F23">
-        <v>3600</v>
+        <v>3550</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1075,16 +1112,16 @@
         </is>
       </c>
       <c r="C24">
-        <v>35.9</v>
+        <v>40.5</v>
       </c>
       <c r="D24">
-        <v>19.2</v>
+        <v>17.9</v>
       </c>
       <c r="E24">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F24">
-        <v>3800</v>
+        <v>3200</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1107,20 +1144,20 @@
         </is>
       </c>
       <c r="C25">
-        <v>38.2</v>
+        <v>37.9</v>
       </c>
       <c r="D25">
-        <v>18.1</v>
+        <v>18.6</v>
       </c>
       <c r="E25">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="F25">
-        <v>3950</v>
+        <v>3150</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H25">
@@ -1139,16 +1176,16 @@
         </is>
       </c>
       <c r="C26">
-        <v>38.8</v>
+        <v>40.5</v>
       </c>
       <c r="D26">
-        <v>17.2</v>
+        <v>18.9</v>
       </c>
       <c r="E26">
         <v>180</v>
       </c>
       <c r="F26">
-        <v>3800</v>
+        <v>3950</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1167,20 +1204,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Biscoe</t>
+          <t>Dream</t>
         </is>
       </c>
       <c r="C27">
-        <v>35.3</v>
+        <v>39.5</v>
       </c>
       <c r="D27">
-        <v>18.9</v>
+        <v>16.7</v>
       </c>
       <c r="E27">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="F27">
-        <v>3800</v>
+        <v>3250</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1199,20 +1236,20 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Biscoe</t>
+          <t>Dream</t>
         </is>
       </c>
       <c r="C28">
-        <v>40.6</v>
+        <v>37.2</v>
       </c>
       <c r="D28">
-        <v>18.6</v>
+        <v>18.1</v>
       </c>
       <c r="E28">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="F28">
-        <v>3550</v>
+        <v>3900</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1231,20 +1268,20 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Biscoe</t>
+          <t>Dream</t>
         </is>
       </c>
       <c r="C29">
-        <v>40.5</v>
+        <v>39.5</v>
       </c>
       <c r="D29">
-        <v>17.9</v>
+        <v>17.8</v>
       </c>
       <c r="E29">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F29">
-        <v>3200</v>
+        <v>3300</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1263,24 +1300,24 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Biscoe</t>
+          <t>Dream</t>
         </is>
       </c>
       <c r="C30">
-        <v>37.9</v>
+        <v>40.9</v>
       </c>
       <c r="D30">
-        <v>18.6</v>
+        <v>18.9</v>
       </c>
       <c r="E30">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="F30">
-        <v>3150</v>
+        <v>3900</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H30">
@@ -1295,24 +1332,24 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Biscoe</t>
+          <t>Dream</t>
         </is>
       </c>
       <c r="C31">
-        <v>40.5</v>
+        <v>36.4</v>
       </c>
       <c r="D31">
-        <v>18.9</v>
+        <v>17</v>
       </c>
       <c r="E31">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="F31">
-        <v>3950</v>
+        <v>3325</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H31">
@@ -1331,20 +1368,20 @@
         </is>
       </c>
       <c r="C32">
-        <v>39.5</v>
+        <v>39.2</v>
       </c>
       <c r="D32">
-        <v>16.7</v>
+        <v>21.1</v>
       </c>
       <c r="E32">
-        <v>178</v>
+        <v>196</v>
       </c>
       <c r="F32">
-        <v>3250</v>
+        <v>4150</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H32">
@@ -1363,16 +1400,16 @@
         </is>
       </c>
       <c r="C33">
-        <v>37.2</v>
+        <v>38.8</v>
       </c>
       <c r="D33">
-        <v>18.1</v>
+        <v>20</v>
       </c>
       <c r="E33">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="F33">
-        <v>3900</v>
+        <v>3950</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1395,16 +1432,16 @@
         </is>
       </c>
       <c r="C34">
-        <v>39.5</v>
+        <v>42.2</v>
       </c>
       <c r="D34">
-        <v>17.8</v>
+        <v>18.5</v>
       </c>
       <c r="E34">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="F34">
-        <v>3300</v>
+        <v>3550</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1427,20 +1464,20 @@
         </is>
       </c>
       <c r="C35">
-        <v>40.9</v>
+        <v>37.6</v>
       </c>
       <c r="D35">
-        <v>18.9</v>
+        <v>19.3</v>
       </c>
       <c r="E35">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="F35">
-        <v>3900</v>
+        <v>3300</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H35">
@@ -1459,20 +1496,20 @@
         </is>
       </c>
       <c r="C36">
-        <v>36.4</v>
+        <v>39.8</v>
       </c>
       <c r="D36">
-        <v>17</v>
+        <v>19.1</v>
       </c>
       <c r="E36">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="F36">
-        <v>3325</v>
+        <v>4650</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H36">
@@ -1491,20 +1528,20 @@
         </is>
       </c>
       <c r="C37">
-        <v>39.2</v>
+        <v>36.5</v>
       </c>
       <c r="D37">
-        <v>21.1</v>
+        <v>18</v>
       </c>
       <c r="E37">
-        <v>196</v>
+        <v>182</v>
       </c>
       <c r="F37">
-        <v>4150</v>
+        <v>3150</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H37">
@@ -1523,16 +1560,16 @@
         </is>
       </c>
       <c r="C38">
-        <v>38.8</v>
+        <v>40.8</v>
       </c>
       <c r="D38">
-        <v>20</v>
+        <v>18.4</v>
       </c>
       <c r="E38">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="F38">
-        <v>3950</v>
+        <v>3900</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1555,16 +1592,16 @@
         </is>
       </c>
       <c r="C39">
-        <v>42.2</v>
+        <v>36</v>
       </c>
       <c r="D39">
         <v>18.5</v>
       </c>
       <c r="E39">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="F39">
-        <v>3550</v>
+        <v>3100</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1587,20 +1624,20 @@
         </is>
       </c>
       <c r="C40">
-        <v>37.6</v>
+        <v>44.1</v>
       </c>
       <c r="D40">
-        <v>19.3</v>
+        <v>19.7</v>
       </c>
       <c r="E40">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="F40">
-        <v>3300</v>
+        <v>4400</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H40">
@@ -1619,20 +1656,20 @@
         </is>
       </c>
       <c r="C41">
-        <v>39.8</v>
+        <v>37</v>
       </c>
       <c r="D41">
-        <v>19.1</v>
+        <v>16.9</v>
       </c>
       <c r="E41">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F41">
-        <v>4650</v>
+        <v>3000</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H41">
@@ -1651,20 +1688,20 @@
         </is>
       </c>
       <c r="C42">
-        <v>36.5</v>
+        <v>39.6</v>
       </c>
       <c r="D42">
-        <v>18</v>
+        <v>18.8</v>
       </c>
       <c r="E42">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="F42">
-        <v>3150</v>
+        <v>4600</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H42">
@@ -1683,16 +1720,16 @@
         </is>
       </c>
       <c r="C43">
-        <v>40.8</v>
+        <v>41.1</v>
       </c>
       <c r="D43">
-        <v>18.4</v>
+        <v>19</v>
       </c>
       <c r="E43">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="F43">
-        <v>3900</v>
+        <v>3425</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1718,13 +1755,13 @@
         <v>36</v>
       </c>
       <c r="D44">
-        <v>18.5</v>
+        <v>17.9</v>
       </c>
       <c r="E44">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="F44">
-        <v>3100</v>
+        <v>3450</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1747,16 +1784,16 @@
         </is>
       </c>
       <c r="C45">
-        <v>44.1</v>
+        <v>42.3</v>
       </c>
       <c r="D45">
-        <v>19.7</v>
+        <v>21.2</v>
       </c>
       <c r="E45">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="F45">
-        <v>4400</v>
+        <v>4150</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1775,20 +1812,20 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Dream</t>
+          <t>Biscoe</t>
         </is>
       </c>
       <c r="C46">
-        <v>37</v>
+        <v>39.6</v>
       </c>
       <c r="D46">
-        <v>16.9</v>
+        <v>17.7</v>
       </c>
       <c r="E46">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F46">
-        <v>3000</v>
+        <v>3500</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -1796,7 +1833,7 @@
         </is>
       </c>
       <c r="H46">
-        <v>2007</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="47">
@@ -1807,20 +1844,20 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Dream</t>
+          <t>Biscoe</t>
         </is>
       </c>
       <c r="C47">
-        <v>39.6</v>
+        <v>40.1</v>
       </c>
       <c r="D47">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="E47">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F47">
-        <v>4600</v>
+        <v>4300</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -1828,7 +1865,7 @@
         </is>
       </c>
       <c r="H47">
-        <v>2007</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="48">
@@ -1839,28 +1876,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Dream</t>
+          <t>Biscoe</t>
         </is>
       </c>
       <c r="C48">
-        <v>41.1</v>
+        <v>35</v>
       </c>
       <c r="D48">
-        <v>19</v>
+        <v>17.9</v>
       </c>
       <c r="E48">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="F48">
-        <v>3425</v>
+        <v>3450</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H48">
-        <v>2007</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="49">
@@ -1871,23 +1908,28 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Dream</t>
+          <t>Biscoe</t>
         </is>
       </c>
       <c r="C49">
-        <v>37.5</v>
+        <v>42</v>
       </c>
       <c r="D49">
-        <v>18.9</v>
+        <v>19.5</v>
       </c>
       <c r="E49">
-        <v>179</v>
+        <v>200</v>
       </c>
       <c r="F49">
-        <v>2975</v>
+        <v>4050</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
       </c>
       <c r="H49">
-        <v>2007</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="50">
@@ -1898,20 +1940,20 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Dream</t>
+          <t>Biscoe</t>
         </is>
       </c>
       <c r="C50">
-        <v>36</v>
+        <v>34.5</v>
       </c>
       <c r="D50">
-        <v>17.9</v>
+        <v>18.1</v>
       </c>
       <c r="E50">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="F50">
-        <v>3450</v>
+        <v>2900</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -1919,7 +1961,7 @@
         </is>
       </c>
       <c r="H50">
-        <v>2007</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="51">
@@ -1930,20 +1972,20 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Dream</t>
+          <t>Biscoe</t>
         </is>
       </c>
       <c r="C51">
-        <v>42.3</v>
+        <v>41.4</v>
       </c>
       <c r="D51">
-        <v>21.2</v>
+        <v>18.6</v>
       </c>
       <c r="E51">
         <v>191</v>
       </c>
       <c r="F51">
-        <v>4150</v>
+        <v>3700</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -1951,7 +1993,7 @@
         </is>
       </c>
       <c r="H51">
-        <v>2007</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="52">
@@ -1966,16 +2008,16 @@
         </is>
       </c>
       <c r="C52">
-        <v>39.6</v>
+        <v>39</v>
       </c>
       <c r="D52">
-        <v>17.7</v>
+        <v>17.5</v>
       </c>
       <c r="E52">
         <v>186</v>
       </c>
       <c r="F52">
-        <v>3500</v>
+        <v>3550</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -1998,16 +2040,16 @@
         </is>
       </c>
       <c r="C53">
-        <v>40.1</v>
+        <v>40.6</v>
       </c>
       <c r="D53">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="E53">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="F53">
-        <v>4300</v>
+        <v>3800</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2030,16 +2072,16 @@
         </is>
       </c>
       <c r="C54">
-        <v>35</v>
+        <v>36.5</v>
       </c>
       <c r="D54">
-        <v>17.9</v>
+        <v>16.6</v>
       </c>
       <c r="E54">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="F54">
-        <v>3450</v>
+        <v>2850</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2062,16 +2104,16 @@
         </is>
       </c>
       <c r="C55">
-        <v>42</v>
+        <v>37.6</v>
       </c>
       <c r="D55">
-        <v>19.5</v>
+        <v>19.1</v>
       </c>
       <c r="E55">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="F55">
-        <v>4050</v>
+        <v>3750</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2094,16 +2136,16 @@
         </is>
       </c>
       <c r="C56">
-        <v>34.5</v>
+        <v>35.7</v>
       </c>
       <c r="D56">
-        <v>18.1</v>
+        <v>16.9</v>
       </c>
       <c r="E56">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F56">
-        <v>2900</v>
+        <v>3150</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2126,16 +2168,16 @@
         </is>
       </c>
       <c r="C57">
-        <v>41.4</v>
+        <v>41.3</v>
       </c>
       <c r="D57">
-        <v>18.6</v>
+        <v>21.1</v>
       </c>
       <c r="E57">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="F57">
-        <v>3700</v>
+        <v>4400</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2158,16 +2200,16 @@
         </is>
       </c>
       <c r="C58">
-        <v>39</v>
+        <v>37.6</v>
       </c>
       <c r="D58">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="E58">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F58">
-        <v>3550</v>
+        <v>3600</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2190,16 +2232,16 @@
         </is>
       </c>
       <c r="C59">
-        <v>40.6</v>
+        <v>41.1</v>
       </c>
       <c r="D59">
-        <v>18.8</v>
+        <v>18.2</v>
       </c>
       <c r="E59">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F59">
-        <v>3800</v>
+        <v>4050</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2222,13 +2264,13 @@
         </is>
       </c>
       <c r="C60">
-        <v>36.5</v>
+        <v>36.4</v>
       </c>
       <c r="D60">
-        <v>16.6</v>
+        <v>17.1</v>
       </c>
       <c r="E60">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F60">
         <v>2850</v>
@@ -2254,16 +2296,16 @@
         </is>
       </c>
       <c r="C61">
-        <v>37.6</v>
+        <v>41.6</v>
       </c>
       <c r="D61">
-        <v>19.1</v>
+        <v>18</v>
       </c>
       <c r="E61">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F61">
-        <v>3750</v>
+        <v>3950</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2286,16 +2328,16 @@
         </is>
       </c>
       <c r="C62">
-        <v>35.7</v>
+        <v>35.5</v>
       </c>
       <c r="D62">
-        <v>16.9</v>
+        <v>16.2</v>
       </c>
       <c r="E62">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="F62">
-        <v>3150</v>
+        <v>3350</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -2318,16 +2360,16 @@
         </is>
       </c>
       <c r="C63">
-        <v>41.3</v>
+        <v>41.1</v>
       </c>
       <c r="D63">
-        <v>21.1</v>
+        <v>19.1</v>
       </c>
       <c r="E63">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="F63">
-        <v>4400</v>
+        <v>4100</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2346,20 +2388,20 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Biscoe</t>
+          <t>Torgersen</t>
         </is>
       </c>
       <c r="C64">
-        <v>37.6</v>
+        <v>35.9</v>
       </c>
       <c r="D64">
-        <v>17</v>
+        <v>16.6</v>
       </c>
       <c r="E64">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="F64">
-        <v>3600</v>
+        <v>3050</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -2378,20 +2420,20 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Biscoe</t>
+          <t>Torgersen</t>
         </is>
       </c>
       <c r="C65">
-        <v>41.1</v>
+        <v>41.8</v>
       </c>
       <c r="D65">
-        <v>18.2</v>
+        <v>19.4</v>
       </c>
       <c r="E65">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="F65">
-        <v>4050</v>
+        <v>4450</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -2410,20 +2452,20 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Biscoe</t>
+          <t>Torgersen</t>
         </is>
       </c>
       <c r="C66">
-        <v>36.4</v>
+        <v>33.5</v>
       </c>
       <c r="D66">
-        <v>17.1</v>
+        <v>19</v>
       </c>
       <c r="E66">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="F66">
-        <v>2850</v>
+        <v>3600</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -2442,20 +2484,20 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Biscoe</t>
+          <t>Torgersen</t>
         </is>
       </c>
       <c r="C67">
-        <v>41.6</v>
+        <v>39.7</v>
       </c>
       <c r="D67">
-        <v>18</v>
+        <v>18.4</v>
       </c>
       <c r="E67">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F67">
-        <v>3950</v>
+        <v>3900</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -2474,20 +2516,20 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Biscoe</t>
+          <t>Torgersen</t>
         </is>
       </c>
       <c r="C68">
-        <v>35.5</v>
+        <v>39.6</v>
       </c>
       <c r="D68">
-        <v>16.2</v>
+        <v>17.2</v>
       </c>
       <c r="E68">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F68">
-        <v>3350</v>
+        <v>3550</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -2506,20 +2548,20 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Biscoe</t>
+          <t>Torgersen</t>
         </is>
       </c>
       <c r="C69">
-        <v>41.1</v>
+        <v>45.8</v>
       </c>
       <c r="D69">
-        <v>19.1</v>
+        <v>18.9</v>
       </c>
       <c r="E69">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="F69">
-        <v>4100</v>
+        <v>4150</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -2542,16 +2584,16 @@
         </is>
       </c>
       <c r="C70">
-        <v>35.9</v>
+        <v>35.5</v>
       </c>
       <c r="D70">
-        <v>16.6</v>
+        <v>17.5</v>
       </c>
       <c r="E70">
         <v>190</v>
       </c>
       <c r="F70">
-        <v>3050</v>
+        <v>3700</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -2574,16 +2616,16 @@
         </is>
       </c>
       <c r="C71">
-        <v>41.8</v>
+        <v>42.8</v>
       </c>
       <c r="D71">
-        <v>19.4</v>
+        <v>18.5</v>
       </c>
       <c r="E71">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="F71">
-        <v>4450</v>
+        <v>4250</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -2606,16 +2648,16 @@
         </is>
       </c>
       <c r="C72">
-        <v>33.5</v>
+        <v>40.9</v>
       </c>
       <c r="D72">
-        <v>19</v>
+        <v>16.8</v>
       </c>
       <c r="E72">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F72">
-        <v>3600</v>
+        <v>3700</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -2638,13 +2680,13 @@
         </is>
       </c>
       <c r="C73">
-        <v>39.7</v>
+        <v>37.2</v>
       </c>
       <c r="D73">
-        <v>18.4</v>
+        <v>19.4</v>
       </c>
       <c r="E73">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="F73">
         <v>3900</v>
@@ -2670,13 +2712,13 @@
         </is>
       </c>
       <c r="C74">
-        <v>39.6</v>
+        <v>36.2</v>
       </c>
       <c r="D74">
-        <v>17.2</v>
+        <v>16.1</v>
       </c>
       <c r="E74">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="F74">
         <v>3550</v>
@@ -2702,16 +2744,16 @@
         </is>
       </c>
       <c r="C75">
-        <v>45.8</v>
+        <v>42.1</v>
       </c>
       <c r="D75">
-        <v>18.9</v>
+        <v>19.1</v>
       </c>
       <c r="E75">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F75">
-        <v>4150</v>
+        <v>4000</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -2734,16 +2776,16 @@
         </is>
       </c>
       <c r="C76">
-        <v>35.5</v>
+        <v>34.6</v>
       </c>
       <c r="D76">
-        <v>17.5</v>
+        <v>17.2</v>
       </c>
       <c r="E76">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F76">
-        <v>3700</v>
+        <v>3200</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -2766,16 +2808,16 @@
         </is>
       </c>
       <c r="C77">
-        <v>42.8</v>
+        <v>42.9</v>
       </c>
       <c r="D77">
-        <v>18.5</v>
+        <v>17.6</v>
       </c>
       <c r="E77">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F77">
-        <v>4250</v>
+        <v>4700</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -2798,16 +2840,16 @@
         </is>
       </c>
       <c r="C78">
-        <v>40.9</v>
+        <v>36.7</v>
       </c>
       <c r="D78">
-        <v>16.8</v>
+        <v>18.8</v>
       </c>
       <c r="E78">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="F78">
-        <v>3700</v>
+        <v>3800</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -2830,16 +2872,16 @@
         </is>
       </c>
       <c r="C79">
-        <v>37.2</v>
+        <v>35.1</v>
       </c>
       <c r="D79">
         <v>19.4</v>
       </c>
       <c r="E79">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="F79">
-        <v>3900</v>
+        <v>4200</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -2858,20 +2900,20 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Torgersen</t>
+          <t>Dream</t>
         </is>
       </c>
       <c r="C80">
-        <v>36.2</v>
+        <v>37.3</v>
       </c>
       <c r="D80">
-        <v>16.1</v>
+        <v>17.8</v>
       </c>
       <c r="E80">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="F80">
-        <v>3550</v>
+        <v>3350</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -2890,20 +2932,20 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Torgersen</t>
+          <t>Dream</t>
         </is>
       </c>
       <c r="C81">
-        <v>42.1</v>
+        <v>41.3</v>
       </c>
       <c r="D81">
-        <v>19.1</v>
+        <v>20.3</v>
       </c>
       <c r="E81">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F81">
-        <v>4000</v>
+        <v>3550</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -2922,24 +2964,24 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Torgersen</t>
+          <t>Dream</t>
         </is>
       </c>
       <c r="C82">
-        <v>34.6</v>
+        <v>36.3</v>
       </c>
       <c r="D82">
-        <v>17.2</v>
+        <v>19.5</v>
       </c>
       <c r="E82">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F82">
-        <v>3200</v>
+        <v>3800</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H82">
@@ -2954,24 +2996,24 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Torgersen</t>
+          <t>Dream</t>
         </is>
       </c>
       <c r="C83">
-        <v>42.9</v>
+        <v>36.9</v>
       </c>
       <c r="D83">
-        <v>17.6</v>
+        <v>18.6</v>
       </c>
       <c r="E83">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="F83">
-        <v>4700</v>
+        <v>3500</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H83">
@@ -2986,24 +3028,24 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Torgersen</t>
+          <t>Dream</t>
         </is>
       </c>
       <c r="C84">
-        <v>36.7</v>
+        <v>38.3</v>
       </c>
       <c r="D84">
-        <v>18.8</v>
+        <v>19.2</v>
       </c>
       <c r="E84">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F84">
-        <v>3800</v>
+        <v>3950</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H84">
@@ -3018,24 +3060,24 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Torgersen</t>
+          <t>Dream</t>
         </is>
       </c>
       <c r="C85">
-        <v>35.1</v>
+        <v>38.9</v>
       </c>
       <c r="D85">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E85">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F85">
-        <v>4200</v>
+        <v>3600</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H85">
@@ -3054,16 +3096,16 @@
         </is>
       </c>
       <c r="C86">
-        <v>37.3</v>
+        <v>35.7</v>
       </c>
       <c r="D86">
-        <v>17.8</v>
+        <v>18</v>
       </c>
       <c r="E86">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="F86">
-        <v>3350</v>
+        <v>3550</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -3086,16 +3128,16 @@
         </is>
       </c>
       <c r="C87">
-        <v>41.3</v>
+        <v>41.1</v>
       </c>
       <c r="D87">
-        <v>20.3</v>
+        <v>18.1</v>
       </c>
       <c r="E87">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="F87">
-        <v>3550</v>
+        <v>4300</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -3118,20 +3160,20 @@
         </is>
       </c>
       <c r="C88">
-        <v>36.3</v>
+        <v>34</v>
       </c>
       <c r="D88">
-        <v>19.5</v>
+        <v>17.1</v>
       </c>
       <c r="E88">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="F88">
-        <v>3800</v>
+        <v>3400</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H88">
@@ -3150,20 +3192,20 @@
         </is>
       </c>
       <c r="C89">
-        <v>36.9</v>
+        <v>39.6</v>
       </c>
       <c r="D89">
-        <v>18.6</v>
+        <v>18.1</v>
       </c>
       <c r="E89">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F89">
-        <v>3500</v>
+        <v>4450</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H89">
@@ -3182,20 +3224,20 @@
         </is>
       </c>
       <c r="C90">
-        <v>38.3</v>
+        <v>36.2</v>
       </c>
       <c r="D90">
-        <v>19.2</v>
+        <v>17.3</v>
       </c>
       <c r="E90">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F90">
-        <v>3950</v>
+        <v>3300</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H90">
@@ -3214,20 +3256,20 @@
         </is>
       </c>
       <c r="C91">
-        <v>38.9</v>
+        <v>40.8</v>
       </c>
       <c r="D91">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="E91">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="F91">
-        <v>3600</v>
+        <v>4300</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H91">
@@ -3246,16 +3288,16 @@
         </is>
       </c>
       <c r="C92">
-        <v>35.7</v>
+        <v>38.1</v>
       </c>
       <c r="D92">
-        <v>18</v>
+        <v>18.6</v>
       </c>
       <c r="E92">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="F92">
-        <v>3550</v>
+        <v>3700</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -3278,16 +3320,16 @@
         </is>
       </c>
       <c r="C93">
-        <v>41.1</v>
+        <v>40.3</v>
       </c>
       <c r="D93">
-        <v>18.1</v>
+        <v>18.5</v>
       </c>
       <c r="E93">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="F93">
-        <v>4300</v>
+        <v>4350</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -3310,16 +3352,16 @@
         </is>
       </c>
       <c r="C94">
-        <v>34</v>
+        <v>33.1</v>
       </c>
       <c r="D94">
-        <v>17.1</v>
+        <v>16.1</v>
       </c>
       <c r="E94">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="F94">
-        <v>3400</v>
+        <v>2900</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -3342,16 +3384,16 @@
         </is>
       </c>
       <c r="C95">
-        <v>39.6</v>
+        <v>43.2</v>
       </c>
       <c r="D95">
-        <v>18.1</v>
+        <v>18.5</v>
       </c>
       <c r="E95">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="F95">
-        <v>4450</v>
+        <v>4100</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -3370,20 +3412,20 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Dream</t>
+          <t>Biscoe</t>
         </is>
       </c>
       <c r="C96">
-        <v>36.2</v>
+        <v>35</v>
       </c>
       <c r="D96">
-        <v>17.3</v>
+        <v>17.9</v>
       </c>
       <c r="E96">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="F96">
-        <v>3300</v>
+        <v>3725</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -3391,7 +3433,7 @@
         </is>
       </c>
       <c r="H96">
-        <v>2008</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="97">
@@ -3402,20 +3444,20 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Dream</t>
+          <t>Biscoe</t>
         </is>
       </c>
       <c r="C97">
-        <v>40.8</v>
+        <v>41</v>
       </c>
       <c r="D97">
-        <v>18.9</v>
+        <v>20</v>
       </c>
       <c r="E97">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="F97">
-        <v>4300</v>
+        <v>4725</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -3423,7 +3465,7 @@
         </is>
       </c>
       <c r="H97">
-        <v>2008</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="98">
@@ -3434,20 +3476,20 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Dream</t>
+          <t>Biscoe</t>
         </is>
       </c>
       <c r="C98">
-        <v>38.1</v>
+        <v>37.7</v>
       </c>
       <c r="D98">
-        <v>18.6</v>
+        <v>16</v>
       </c>
       <c r="E98">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="F98">
-        <v>3700</v>
+        <v>3075</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -3455,7 +3497,7 @@
         </is>
       </c>
       <c r="H98">
-        <v>2008</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="99">
@@ -3466,20 +3508,20 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Dream</t>
+          <t>Biscoe</t>
         </is>
       </c>
       <c r="C99">
-        <v>40.3</v>
+        <v>37.8</v>
       </c>
       <c r="D99">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="E99">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="F99">
-        <v>4350</v>
+        <v>4250</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -3487,7 +3529,7 @@
         </is>
       </c>
       <c r="H99">
-        <v>2008</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="100">
@@ -3498,20 +3540,20 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Dream</t>
+          <t>Biscoe</t>
         </is>
       </c>
       <c r="C100">
-        <v>33.1</v>
+        <v>37.9</v>
       </c>
       <c r="D100">
-        <v>16.1</v>
+        <v>18.6</v>
       </c>
       <c r="E100">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="F100">
-        <v>2900</v>
+        <v>2925</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -3519,7 +3561,7 @@
         </is>
       </c>
       <c r="H100">
-        <v>2008</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="101">
@@ -3530,20 +3572,20 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Dream</t>
+          <t>Biscoe</t>
         </is>
       </c>
       <c r="C101">
-        <v>43.2</v>
+        <v>39.7</v>
       </c>
       <c r="D101">
-        <v>18.5</v>
+        <v>18.9</v>
       </c>
       <c r="E101">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="F101">
-        <v>4100</v>
+        <v>3550</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -3551,7 +3593,7 @@
         </is>
       </c>
       <c r="H101">
-        <v>2008</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="102">
@@ -3566,16 +3608,16 @@
         </is>
       </c>
       <c r="C102">
-        <v>35</v>
+        <v>38.6</v>
       </c>
       <c r="D102">
-        <v>17.9</v>
+        <v>17.2</v>
       </c>
       <c r="E102">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="F102">
-        <v>3725</v>
+        <v>3750</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -3598,16 +3640,16 @@
         </is>
       </c>
       <c r="C103">
-        <v>41</v>
+        <v>38.2</v>
       </c>
       <c r="D103">
         <v>20</v>
       </c>
       <c r="E103">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="F103">
-        <v>4725</v>
+        <v>3900</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -3630,16 +3672,16 @@
         </is>
       </c>
       <c r="C104">
-        <v>37.7</v>
+        <v>38.1</v>
       </c>
       <c r="D104">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E104">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F104">
-        <v>3075</v>
+        <v>3175</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -3662,16 +3704,16 @@
         </is>
       </c>
       <c r="C105">
-        <v>37.8</v>
+        <v>43.2</v>
       </c>
       <c r="D105">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E105">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="F105">
-        <v>4250</v>
+        <v>4775</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -3694,16 +3736,16 @@
         </is>
       </c>
       <c r="C106">
-        <v>37.9</v>
+        <v>38.1</v>
       </c>
       <c r="D106">
-        <v>18.6</v>
+        <v>16.5</v>
       </c>
       <c r="E106">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="F106">
-        <v>2925</v>
+        <v>3825</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -3726,16 +3768,16 @@
         </is>
       </c>
       <c r="C107">
-        <v>39.7</v>
+        <v>45.6</v>
       </c>
       <c r="D107">
-        <v>18.9</v>
+        <v>20.3</v>
       </c>
       <c r="E107">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="F107">
-        <v>3550</v>
+        <v>4600</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -3758,16 +3800,16 @@
         </is>
       </c>
       <c r="C108">
-        <v>38.6</v>
+        <v>39.7</v>
       </c>
       <c r="D108">
-        <v>17.2</v>
+        <v>17.7</v>
       </c>
       <c r="E108">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="F108">
-        <v>3750</v>
+        <v>3200</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -3790,16 +3832,16 @@
         </is>
       </c>
       <c r="C109">
-        <v>38.2</v>
+        <v>42.2</v>
       </c>
       <c r="D109">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="E109">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="F109">
-        <v>3900</v>
+        <v>4275</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -3822,16 +3864,16 @@
         </is>
       </c>
       <c r="C110">
-        <v>38.1</v>
+        <v>39.6</v>
       </c>
       <c r="D110">
-        <v>17</v>
+        <v>20.7</v>
       </c>
       <c r="E110">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="F110">
-        <v>3175</v>
+        <v>3900</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -3854,16 +3896,16 @@
         </is>
       </c>
       <c r="C111">
-        <v>43.2</v>
+        <v>42.7</v>
       </c>
       <c r="D111">
-        <v>19</v>
+        <v>18.3</v>
       </c>
       <c r="E111">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F111">
-        <v>4775</v>
+        <v>4075</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -3882,20 +3924,20 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Biscoe</t>
+          <t>Torgersen</t>
         </is>
       </c>
       <c r="C112">
-        <v>38.1</v>
+        <v>38.6</v>
       </c>
       <c r="D112">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="E112">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="F112">
-        <v>3825</v>
+        <v>2900</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -3914,20 +3956,20 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Biscoe</t>
+          <t>Torgersen</t>
         </is>
       </c>
       <c r="C113">
-        <v>45.6</v>
+        <v>37.3</v>
       </c>
       <c r="D113">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="E113">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="F113">
-        <v>4600</v>
+        <v>3775</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -3946,20 +3988,20 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Biscoe</t>
+          <t>Torgersen</t>
         </is>
       </c>
       <c r="C114">
-        <v>39.7</v>
+        <v>35.7</v>
       </c>
       <c r="D114">
-        <v>17.7</v>
+        <v>17</v>
       </c>
       <c r="E114">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="F114">
-        <v>3200</v>
+        <v>3350</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -3978,20 +4020,20 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Biscoe</t>
+          <t>Torgersen</t>
         </is>
       </c>
       <c r="C115">
-        <v>42.2</v>
+        <v>41.1</v>
       </c>
       <c r="D115">
-        <v>19.5</v>
+        <v>18.6</v>
       </c>
       <c r="E115">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="F115">
-        <v>4275</v>
+        <v>3325</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -4010,20 +4052,20 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Biscoe</t>
+          <t>Torgersen</t>
         </is>
       </c>
       <c r="C116">
-        <v>39.6</v>
+        <v>36.2</v>
       </c>
       <c r="D116">
-        <v>20.7</v>
+        <v>17.2</v>
       </c>
       <c r="E116">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="F116">
-        <v>3900</v>
+        <v>3150</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -4042,20 +4084,20 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Biscoe</t>
+          <t>Torgersen</t>
         </is>
       </c>
       <c r="C117">
-        <v>42.7</v>
+        <v>37.7</v>
       </c>
       <c r="D117">
-        <v>18.3</v>
+        <v>19.8</v>
       </c>
       <c r="E117">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F117">
-        <v>4075</v>
+        <v>3500</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -4078,16 +4120,16 @@
         </is>
       </c>
       <c r="C118">
-        <v>38.6</v>
+        <v>40.2</v>
       </c>
       <c r="D118">
         <v>17</v>
       </c>
       <c r="E118">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="F118">
-        <v>2900</v>
+        <v>3450</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -4110,16 +4152,16 @@
         </is>
       </c>
       <c r="C119">
-        <v>37.3</v>
+        <v>41.4</v>
       </c>
       <c r="D119">
-        <v>20.5</v>
+        <v>18.5</v>
       </c>
       <c r="E119">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="F119">
-        <v>3775</v>
+        <v>3875</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -4142,16 +4184,16 @@
         </is>
       </c>
       <c r="C120">
-        <v>35.7</v>
+        <v>35.2</v>
       </c>
       <c r="D120">
-        <v>17</v>
+        <v>15.9</v>
       </c>
       <c r="E120">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F120">
-        <v>3350</v>
+        <v>3050</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -4174,16 +4216,16 @@
         </is>
       </c>
       <c r="C121">
-        <v>41.1</v>
+        <v>40.6</v>
       </c>
       <c r="D121">
-        <v>18.6</v>
+        <v>19</v>
       </c>
       <c r="E121">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="F121">
-        <v>3325</v>
+        <v>4000</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -4206,16 +4248,16 @@
         </is>
       </c>
       <c r="C122">
-        <v>36.2</v>
+        <v>38.8</v>
       </c>
       <c r="D122">
-        <v>17.2</v>
+        <v>17.6</v>
       </c>
       <c r="E122">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="F122">
-        <v>3150</v>
+        <v>3275</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -4238,16 +4280,16 @@
         </is>
       </c>
       <c r="C123">
-        <v>37.7</v>
+        <v>41.5</v>
       </c>
       <c r="D123">
-        <v>19.8</v>
+        <v>18.3</v>
       </c>
       <c r="E123">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="F123">
-        <v>3500</v>
+        <v>4300</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -4270,16 +4312,16 @@
         </is>
       </c>
       <c r="C124">
-        <v>40.2</v>
+        <v>39</v>
       </c>
       <c r="D124">
-        <v>17</v>
+        <v>17.1</v>
       </c>
       <c r="E124">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="F124">
-        <v>3450</v>
+        <v>3050</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -4302,16 +4344,16 @@
         </is>
       </c>
       <c r="C125">
-        <v>41.4</v>
+        <v>44.1</v>
       </c>
       <c r="D125">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="E125">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="F125">
-        <v>3875</v>
+        <v>4000</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
@@ -4334,16 +4376,16 @@
         </is>
       </c>
       <c r="C126">
-        <v>35.2</v>
+        <v>38.5</v>
       </c>
       <c r="D126">
-        <v>15.9</v>
+        <v>17.9</v>
       </c>
       <c r="E126">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="F126">
-        <v>3050</v>
+        <v>3325</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
@@ -4366,16 +4408,16 @@
         </is>
       </c>
       <c r="C127">
-        <v>40.6</v>
+        <v>43.1</v>
       </c>
       <c r="D127">
-        <v>19</v>
+        <v>19.2</v>
       </c>
       <c r="E127">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F127">
-        <v>4000</v>
+        <v>3500</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
@@ -4394,20 +4436,20 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Torgersen</t>
+          <t>Dream</t>
         </is>
       </c>
       <c r="C128">
-        <v>38.8</v>
+        <v>36.8</v>
       </c>
       <c r="D128">
-        <v>17.6</v>
+        <v>18.5</v>
       </c>
       <c r="E128">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F128">
-        <v>3275</v>
+        <v>3500</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
@@ -4426,20 +4468,20 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Torgersen</t>
+          <t>Dream</t>
         </is>
       </c>
       <c r="C129">
-        <v>41.5</v>
+        <v>37.5</v>
       </c>
       <c r="D129">
-        <v>18.3</v>
+        <v>18.5</v>
       </c>
       <c r="E129">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="F129">
-        <v>4300</v>
+        <v>4475</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
@@ -4458,20 +4500,20 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Torgersen</t>
+          <t>Dream</t>
         </is>
       </c>
       <c r="C130">
-        <v>39</v>
+        <v>38.1</v>
       </c>
       <c r="D130">
-        <v>17.1</v>
+        <v>17.6</v>
       </c>
       <c r="E130">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="F130">
-        <v>3050</v>
+        <v>3425</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
@@ -4490,20 +4532,20 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Torgersen</t>
+          <t>Dream</t>
         </is>
       </c>
       <c r="C131">
-        <v>44.1</v>
+        <v>41.1</v>
       </c>
       <c r="D131">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="E131">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="F131">
-        <v>4000</v>
+        <v>3900</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
@@ -4522,20 +4564,20 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Torgersen</t>
+          <t>Dream</t>
         </is>
       </c>
       <c r="C132">
-        <v>38.5</v>
+        <v>35.6</v>
       </c>
       <c r="D132">
-        <v>17.9</v>
+        <v>17.5</v>
       </c>
       <c r="E132">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="F132">
-        <v>3325</v>
+        <v>3175</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
@@ -4554,20 +4596,20 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Torgersen</t>
+          <t>Dream</t>
         </is>
       </c>
       <c r="C133">
-        <v>43.1</v>
+        <v>40.2</v>
       </c>
       <c r="D133">
-        <v>19.2</v>
+        <v>20.1</v>
       </c>
       <c r="E133">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="F133">
-        <v>3500</v>
+        <v>3975</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
@@ -4590,16 +4632,16 @@
         </is>
       </c>
       <c r="C134">
-        <v>36.8</v>
+        <v>37</v>
       </c>
       <c r="D134">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="E134">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="F134">
-        <v>3500</v>
+        <v>3400</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -4622,16 +4664,16 @@
         </is>
       </c>
       <c r="C135">
-        <v>37.5</v>
+        <v>39.7</v>
       </c>
       <c r="D135">
-        <v>18.5</v>
+        <v>17.9</v>
       </c>
       <c r="E135">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="F135">
-        <v>4475</v>
+        <v>4250</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -4654,16 +4696,16 @@
         </is>
       </c>
       <c r="C136">
-        <v>38.1</v>
+        <v>40.2</v>
       </c>
       <c r="D136">
-        <v>17.6</v>
+        <v>17.1</v>
       </c>
       <c r="E136">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="F136">
-        <v>3425</v>
+        <v>3400</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
@@ -4686,16 +4728,16 @@
         </is>
       </c>
       <c r="C137">
-        <v>41.1</v>
+        <v>40.6</v>
       </c>
       <c r="D137">
-        <v>17.5</v>
+        <v>17.2</v>
       </c>
       <c r="E137">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="F137">
-        <v>3900</v>
+        <v>3475</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
@@ -4718,16 +4760,16 @@
         </is>
       </c>
       <c r="C138">
-        <v>35.6</v>
+        <v>32.1</v>
       </c>
       <c r="D138">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="E138">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="F138">
-        <v>3175</v>
+        <v>3050</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
@@ -4750,16 +4792,16 @@
         </is>
       </c>
       <c r="C139">
-        <v>40.2</v>
+        <v>40.7</v>
       </c>
       <c r="D139">
-        <v>20.1</v>
+        <v>17</v>
       </c>
       <c r="E139">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="F139">
-        <v>3975</v>
+        <v>3725</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
@@ -4782,16 +4824,16 @@
         </is>
       </c>
       <c r="C140">
-        <v>37</v>
+        <v>37.3</v>
       </c>
       <c r="D140">
-        <v>16.5</v>
+        <v>16.8</v>
       </c>
       <c r="E140">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="F140">
-        <v>3400</v>
+        <v>3000</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -4814,16 +4856,16 @@
         </is>
       </c>
       <c r="C141">
-        <v>39.7</v>
+        <v>39</v>
       </c>
       <c r="D141">
-        <v>17.9</v>
+        <v>18.7</v>
       </c>
       <c r="E141">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="F141">
-        <v>4250</v>
+        <v>3650</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
@@ -4846,20 +4888,20 @@
         </is>
       </c>
       <c r="C142">
-        <v>40.2</v>
+        <v>39.2</v>
       </c>
       <c r="D142">
-        <v>17.1</v>
+        <v>18.6</v>
       </c>
       <c r="E142">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F142">
-        <v>3400</v>
+        <v>4250</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H142">
@@ -4878,20 +4920,20 @@
         </is>
       </c>
       <c r="C143">
-        <v>40.6</v>
+        <v>36.6</v>
       </c>
       <c r="D143">
-        <v>17.2</v>
+        <v>18.4</v>
       </c>
       <c r="E143">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F143">
         <v>3475</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H143">
@@ -4910,16 +4952,16 @@
         </is>
       </c>
       <c r="C144">
-        <v>32.1</v>
+        <v>36</v>
       </c>
       <c r="D144">
-        <v>15.5</v>
+        <v>17.8</v>
       </c>
       <c r="E144">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="F144">
-        <v>3050</v>
+        <v>3450</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -4942,16 +4984,16 @@
         </is>
       </c>
       <c r="C145">
-        <v>40.7</v>
+        <v>37.8</v>
       </c>
       <c r="D145">
-        <v>17</v>
+        <v>18.1</v>
       </c>
       <c r="E145">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="F145">
-        <v>3725</v>
+        <v>3750</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
@@ -4974,16 +5016,16 @@
         </is>
       </c>
       <c r="C146">
-        <v>37.3</v>
+        <v>36</v>
       </c>
       <c r="D146">
-        <v>16.8</v>
+        <v>17.1</v>
       </c>
       <c r="E146">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="F146">
-        <v>3000</v>
+        <v>3700</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
@@ -5006,16 +5048,16 @@
         </is>
       </c>
       <c r="C147">
-        <v>39</v>
+        <v>41.5</v>
       </c>
       <c r="D147">
-        <v>18.7</v>
+        <v>18.5</v>
       </c>
       <c r="E147">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="F147">
-        <v>3650</v>
+        <v>4000</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -5029,89 +5071,89 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Adelie</t>
+          <t>Gentoo</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Dream</t>
+          <t>Biscoe</t>
         </is>
       </c>
       <c r="C148">
-        <v>39.2</v>
+        <v>46.1</v>
       </c>
       <c r="D148">
-        <v>18.6</v>
+        <v>13.2</v>
       </c>
       <c r="E148">
-        <v>190</v>
+        <v>211</v>
       </c>
       <c r="F148">
-        <v>4250</v>
+        <v>4500</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H148">
-        <v>2009</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Adelie</t>
+          <t>Gentoo</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Dream</t>
+          <t>Biscoe</t>
         </is>
       </c>
       <c r="C149">
-        <v>36.6</v>
+        <v>50</v>
       </c>
       <c r="D149">
-        <v>18.4</v>
+        <v>16.3</v>
       </c>
       <c r="E149">
-        <v>184</v>
+        <v>230</v>
       </c>
       <c r="F149">
-        <v>3475</v>
+        <v>5700</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H149">
-        <v>2009</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Adelie</t>
+          <t>Gentoo</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Dream</t>
+          <t>Biscoe</t>
         </is>
       </c>
       <c r="C150">
-        <v>36</v>
+        <v>48.7</v>
       </c>
       <c r="D150">
-        <v>17.8</v>
+        <v>14.1</v>
       </c>
       <c r="E150">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="F150">
-        <v>3450</v>
+        <v>4450</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
@@ -5119,31 +5161,31 @@
         </is>
       </c>
       <c r="H150">
-        <v>2009</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Adelie</t>
+          <t>Gentoo</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Dream</t>
+          <t>Biscoe</t>
         </is>
       </c>
       <c r="C151">
-        <v>37.8</v>
+        <v>50</v>
       </c>
       <c r="D151">
-        <v>18.1</v>
+        <v>15.2</v>
       </c>
       <c r="E151">
-        <v>193</v>
+        <v>218</v>
       </c>
       <c r="F151">
-        <v>3750</v>
+        <v>5700</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
@@ -5151,71 +5193,71 @@
         </is>
       </c>
       <c r="H151">
-        <v>2009</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Adelie</t>
+          <t>Gentoo</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Dream</t>
+          <t>Biscoe</t>
         </is>
       </c>
       <c r="C152">
-        <v>36</v>
+        <v>47.6</v>
       </c>
       <c r="D152">
-        <v>17.1</v>
+        <v>14.5</v>
       </c>
       <c r="E152">
-        <v>187</v>
+        <v>215</v>
       </c>
       <c r="F152">
-        <v>3700</v>
+        <v>5400</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H152">
-        <v>2009</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Adelie</t>
+          <t>Gentoo</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Dream</t>
+          <t>Biscoe</t>
         </is>
       </c>
       <c r="C153">
-        <v>41.5</v>
+        <v>46.5</v>
       </c>
       <c r="D153">
-        <v>18.5</v>
+        <v>13.5</v>
       </c>
       <c r="E153">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="F153">
-        <v>4000</v>
+        <v>4550</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H153">
-        <v>2009</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="154">
@@ -5230,16 +5272,16 @@
         </is>
       </c>
       <c r="C154">
-        <v>46.1</v>
+        <v>45.4</v>
       </c>
       <c r="D154">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E154">
         <v>211</v>
       </c>
       <c r="F154">
-        <v>4500</v>
+        <v>4800</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
@@ -5262,16 +5304,16 @@
         </is>
       </c>
       <c r="C155">
-        <v>50</v>
+        <v>46.7</v>
       </c>
       <c r="D155">
-        <v>16.3</v>
+        <v>15.3</v>
       </c>
       <c r="E155">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="F155">
-        <v>5700</v>
+        <v>5200</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
@@ -5294,16 +5336,16 @@
         </is>
       </c>
       <c r="C156">
-        <v>48.7</v>
+        <v>43.3</v>
       </c>
       <c r="D156">
-        <v>14.1</v>
+        <v>13.4</v>
       </c>
       <c r="E156">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F156">
-        <v>4450</v>
+        <v>4400</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
@@ -5326,16 +5368,16 @@
         </is>
       </c>
       <c r="C157">
-        <v>50</v>
+        <v>46.8</v>
       </c>
       <c r="D157">
-        <v>15.2</v>
+        <v>15.4</v>
       </c>
       <c r="E157">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F157">
-        <v>5700</v>
+        <v>5150</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
@@ -5358,20 +5400,20 @@
         </is>
       </c>
       <c r="C158">
-        <v>47.6</v>
+        <v>40.9</v>
       </c>
       <c r="D158">
-        <v>14.5</v>
+        <v>13.7</v>
       </c>
       <c r="E158">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F158">
-        <v>5400</v>
+        <v>4650</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H158">
@@ -5390,20 +5432,20 @@
         </is>
       </c>
       <c r="C159">
-        <v>46.5</v>
+        <v>49</v>
       </c>
       <c r="D159">
-        <v>13.5</v>
+        <v>16.1</v>
       </c>
       <c r="E159">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="F159">
-        <v>4550</v>
+        <v>5550</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H159">
@@ -5422,16 +5464,16 @@
         </is>
       </c>
       <c r="C160">
-        <v>45.4</v>
+        <v>45.5</v>
       </c>
       <c r="D160">
-        <v>14.6</v>
+        <v>13.7</v>
       </c>
       <c r="E160">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="F160">
-        <v>4800</v>
+        <v>4650</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
@@ -5454,16 +5496,16 @@
         </is>
       </c>
       <c r="C161">
-        <v>46.7</v>
+        <v>48.4</v>
       </c>
       <c r="D161">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E161">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="F161">
-        <v>5200</v>
+        <v>5850</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
@@ -5486,16 +5528,16 @@
         </is>
       </c>
       <c r="C162">
-        <v>43.3</v>
+        <v>45.8</v>
       </c>
       <c r="D162">
-        <v>13.4</v>
+        <v>14.6</v>
       </c>
       <c r="E162">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F162">
-        <v>4400</v>
+        <v>4200</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
@@ -5518,16 +5560,16 @@
         </is>
       </c>
       <c r="C163">
-        <v>46.8</v>
+        <v>49.3</v>
       </c>
       <c r="D163">
-        <v>15.4</v>
+        <v>15.7</v>
       </c>
       <c r="E163">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="F163">
-        <v>5150</v>
+        <v>5850</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
@@ -5550,16 +5592,16 @@
         </is>
       </c>
       <c r="C164">
-        <v>40.9</v>
+        <v>42</v>
       </c>
       <c r="D164">
-        <v>13.7</v>
+        <v>13.5</v>
       </c>
       <c r="E164">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="F164">
-        <v>4650</v>
+        <v>4150</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
@@ -5582,16 +5624,16 @@
         </is>
       </c>
       <c r="C165">
-        <v>49</v>
+        <v>49.2</v>
       </c>
       <c r="D165">
-        <v>16.1</v>
+        <v>15.2</v>
       </c>
       <c r="E165">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="F165">
-        <v>5550</v>
+        <v>6300</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
@@ -5614,16 +5656,16 @@
         </is>
       </c>
       <c r="C166">
-        <v>45.5</v>
+        <v>46.2</v>
       </c>
       <c r="D166">
-        <v>13.7</v>
+        <v>14.5</v>
       </c>
       <c r="E166">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="F166">
-        <v>4650</v>
+        <v>4800</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
@@ -5646,16 +5688,16 @@
         </is>
       </c>
       <c r="C167">
-        <v>48.4</v>
+        <v>48.7</v>
       </c>
       <c r="D167">
-        <v>14.6</v>
+        <v>15.1</v>
       </c>
       <c r="E167">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="F167">
-        <v>5850</v>
+        <v>5350</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
@@ -5678,20 +5720,20 @@
         </is>
       </c>
       <c r="C168">
-        <v>45.8</v>
+        <v>50.2</v>
       </c>
       <c r="D168">
-        <v>14.6</v>
+        <v>14.3</v>
       </c>
       <c r="E168">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="F168">
-        <v>4200</v>
+        <v>5700</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H168">
@@ -5710,20 +5752,20 @@
         </is>
       </c>
       <c r="C169">
-        <v>49.3</v>
+        <v>45.1</v>
       </c>
       <c r="D169">
-        <v>15.7</v>
+        <v>14.5</v>
       </c>
       <c r="E169">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F169">
-        <v>5850</v>
+        <v>5000</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H169">
@@ -5742,16 +5784,16 @@
         </is>
       </c>
       <c r="C170">
-        <v>42</v>
+        <v>46.5</v>
       </c>
       <c r="D170">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="E170">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="F170">
-        <v>4150</v>
+        <v>4400</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
@@ -5774,16 +5816,16 @@
         </is>
       </c>
       <c r="C171">
-        <v>49.2</v>
+        <v>46.3</v>
       </c>
       <c r="D171">
-        <v>15.2</v>
+        <v>15.8</v>
       </c>
       <c r="E171">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="F171">
-        <v>6300</v>
+        <v>5050</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
@@ -5806,16 +5848,16 @@
         </is>
       </c>
       <c r="C172">
-        <v>46.2</v>
+        <v>42.9</v>
       </c>
       <c r="D172">
-        <v>14.5</v>
+        <v>13.1</v>
       </c>
       <c r="E172">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="F172">
-        <v>4800</v>
+        <v>5000</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
@@ -5838,16 +5880,16 @@
         </is>
       </c>
       <c r="C173">
-        <v>48.7</v>
+        <v>46.1</v>
       </c>
       <c r="D173">
         <v>15.1</v>
       </c>
       <c r="E173">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="F173">
-        <v>5350</v>
+        <v>5100</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
@@ -5870,16 +5912,16 @@
         </is>
       </c>
       <c r="C174">
-        <v>50.2</v>
+        <v>47.8</v>
       </c>
       <c r="D174">
-        <v>14.3</v>
+        <v>15</v>
       </c>
       <c r="E174">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F174">
-        <v>5700</v>
+        <v>5650</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
@@ -5902,16 +5944,16 @@
         </is>
       </c>
       <c r="C175">
-        <v>45.1</v>
+        <v>48.2</v>
       </c>
       <c r="D175">
-        <v>14.5</v>
+        <v>14.3</v>
       </c>
       <c r="E175">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="F175">
-        <v>5000</v>
+        <v>4600</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
@@ -5934,20 +5976,20 @@
         </is>
       </c>
       <c r="C176">
-        <v>46.5</v>
+        <v>50</v>
       </c>
       <c r="D176">
-        <v>14.5</v>
+        <v>15.3</v>
       </c>
       <c r="E176">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="F176">
-        <v>4400</v>
+        <v>5550</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H176">
@@ -5966,16 +6008,16 @@
         </is>
       </c>
       <c r="C177">
-        <v>46.3</v>
+        <v>47.3</v>
       </c>
       <c r="D177">
-        <v>15.8</v>
+        <v>15.3</v>
       </c>
       <c r="E177">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="F177">
-        <v>5050</v>
+        <v>5250</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
@@ -5998,16 +6040,16 @@
         </is>
       </c>
       <c r="C178">
-        <v>42.9</v>
+        <v>42.8</v>
       </c>
       <c r="D178">
-        <v>13.1</v>
+        <v>14.2</v>
       </c>
       <c r="E178">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="F178">
-        <v>5000</v>
+        <v>4700</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
@@ -6030,20 +6072,20 @@
         </is>
       </c>
       <c r="C179">
-        <v>46.1</v>
+        <v>45.1</v>
       </c>
       <c r="D179">
-        <v>15.1</v>
+        <v>14.5</v>
       </c>
       <c r="E179">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="F179">
-        <v>5100</v>
+        <v>5050</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H179">
@@ -6062,16 +6104,21 @@
         </is>
       </c>
       <c r="C180">
-        <v>44.5</v>
+        <v>59.6</v>
       </c>
       <c r="D180">
-        <v>14.3</v>
+        <v>17</v>
       </c>
       <c r="E180">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="F180">
-        <v>4100</v>
+        <v>6050</v>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
       </c>
       <c r="H180">
         <v>2007</v>
@@ -6089,24 +6136,24 @@
         </is>
       </c>
       <c r="C181">
-        <v>47.8</v>
+        <v>49.1</v>
       </c>
       <c r="D181">
-        <v>15</v>
+        <v>14.8</v>
       </c>
       <c r="E181">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="F181">
-        <v>5650</v>
+        <v>5150</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H181">
-        <v>2007</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="182">
@@ -6121,24 +6168,24 @@
         </is>
       </c>
       <c r="C182">
-        <v>48.2</v>
+        <v>48.4</v>
       </c>
       <c r="D182">
-        <v>14.3</v>
+        <v>16.3</v>
       </c>
       <c r="E182">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="F182">
-        <v>4600</v>
+        <v>5400</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H182">
-        <v>2007</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="183">
@@ -6153,24 +6200,24 @@
         </is>
       </c>
       <c r="C183">
-        <v>50</v>
+        <v>42.6</v>
       </c>
       <c r="D183">
-        <v>15.3</v>
+        <v>13.7</v>
       </c>
       <c r="E183">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="F183">
-        <v>5550</v>
+        <v>4950</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H183">
-        <v>2007</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="184">
@@ -6185,13 +6232,13 @@
         </is>
       </c>
       <c r="C184">
-        <v>47.3</v>
+        <v>44.4</v>
       </c>
       <c r="D184">
-        <v>15.3</v>
+        <v>17.3</v>
       </c>
       <c r="E184">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F184">
         <v>5250</v>
@@ -6202,7 +6249,7 @@
         </is>
       </c>
       <c r="H184">
-        <v>2007</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="185">
@@ -6217,16 +6264,16 @@
         </is>
       </c>
       <c r="C185">
-        <v>42.8</v>
+        <v>44</v>
       </c>
       <c r="D185">
-        <v>14.2</v>
+        <v>13.6</v>
       </c>
       <c r="E185">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="F185">
-        <v>4700</v>
+        <v>4350</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
@@ -6234,7 +6281,7 @@
         </is>
       </c>
       <c r="H185">
-        <v>2007</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="186">
@@ -6249,24 +6296,24 @@
         </is>
       </c>
       <c r="C186">
-        <v>45.1</v>
+        <v>48.7</v>
       </c>
       <c r="D186">
-        <v>14.5</v>
+        <v>15.7</v>
       </c>
       <c r="E186">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F186">
-        <v>5050</v>
+        <v>5350</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H186">
-        <v>2007</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="187">
@@ -6281,24 +6328,24 @@
         </is>
       </c>
       <c r="C187">
-        <v>59.6</v>
+        <v>42.7</v>
       </c>
       <c r="D187">
-        <v>17</v>
+        <v>13.7</v>
       </c>
       <c r="E187">
-        <v>230</v>
+        <v>208</v>
       </c>
       <c r="F187">
-        <v>6050</v>
+        <v>3950</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H187">
-        <v>2007</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="188">
@@ -6313,20 +6360,20 @@
         </is>
       </c>
       <c r="C188">
-        <v>49.1</v>
+        <v>49.6</v>
       </c>
       <c r="D188">
-        <v>14.8</v>
+        <v>16</v>
       </c>
       <c r="E188">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="F188">
-        <v>5150</v>
+        <v>5700</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H188">
@@ -6345,20 +6392,20 @@
         </is>
       </c>
       <c r="C189">
-        <v>48.4</v>
+        <v>45.3</v>
       </c>
       <c r="D189">
-        <v>16.3</v>
+        <v>13.7</v>
       </c>
       <c r="E189">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="F189">
-        <v>5400</v>
+        <v>4300</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H189">
@@ -6377,20 +6424,20 @@
         </is>
       </c>
       <c r="C190">
-        <v>42.6</v>
+        <v>49.6</v>
       </c>
       <c r="D190">
-        <v>13.7</v>
+        <v>15</v>
       </c>
       <c r="E190">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="F190">
-        <v>4950</v>
+        <v>4750</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H190">
@@ -6409,16 +6456,16 @@
         </is>
       </c>
       <c r="C191">
-        <v>44.4</v>
+        <v>50.5</v>
       </c>
       <c r="D191">
-        <v>17.3</v>
+        <v>15.9</v>
       </c>
       <c r="E191">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="F191">
-        <v>5250</v>
+        <v>5550</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
@@ -6441,16 +6488,16 @@
         </is>
       </c>
       <c r="C192">
-        <v>44</v>
+        <v>43.6</v>
       </c>
       <c r="D192">
-        <v>13.6</v>
+        <v>13.9</v>
       </c>
       <c r="E192">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="F192">
-        <v>4350</v>
+        <v>4900</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
@@ -6473,20 +6520,20 @@
         </is>
       </c>
       <c r="C193">
-        <v>48.7</v>
+        <v>45.5</v>
       </c>
       <c r="D193">
-        <v>15.7</v>
+        <v>13.9</v>
       </c>
       <c r="E193">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="F193">
-        <v>5350</v>
+        <v>4200</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H193">
@@ -6505,20 +6552,20 @@
         </is>
       </c>
       <c r="C194">
-        <v>42.7</v>
+        <v>50.5</v>
       </c>
       <c r="D194">
-        <v>13.7</v>
+        <v>15.9</v>
       </c>
       <c r="E194">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="F194">
-        <v>3950</v>
+        <v>5400</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H194">
@@ -6537,20 +6584,20 @@
         </is>
       </c>
       <c r="C195">
-        <v>49.6</v>
+        <v>44.9</v>
       </c>
       <c r="D195">
-        <v>16</v>
+        <v>13.3</v>
       </c>
       <c r="E195">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="F195">
-        <v>5700</v>
+        <v>5100</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H195">
@@ -6569,20 +6616,20 @@
         </is>
       </c>
       <c r="C196">
-        <v>45.3</v>
+        <v>45.2</v>
       </c>
       <c r="D196">
-        <v>13.7</v>
+        <v>15.8</v>
       </c>
       <c r="E196">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="F196">
-        <v>4300</v>
+        <v>5300</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H196">
@@ -6601,20 +6648,20 @@
         </is>
       </c>
       <c r="C197">
-        <v>49.6</v>
+        <v>46.6</v>
       </c>
       <c r="D197">
-        <v>15</v>
+        <v>14.2</v>
       </c>
       <c r="E197">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="F197">
-        <v>4750</v>
+        <v>4850</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H197">
@@ -6633,16 +6680,16 @@
         </is>
       </c>
       <c r="C198">
-        <v>50.5</v>
+        <v>48.5</v>
       </c>
       <c r="D198">
-        <v>15.9</v>
+        <v>14.1</v>
       </c>
       <c r="E198">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F198">
-        <v>5550</v>
+        <v>5300</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
@@ -6665,16 +6712,16 @@
         </is>
       </c>
       <c r="C199">
-        <v>43.6</v>
+        <v>45.1</v>
       </c>
       <c r="D199">
-        <v>13.9</v>
+        <v>14.4</v>
       </c>
       <c r="E199">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="F199">
-        <v>4900</v>
+        <v>4400</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
@@ -6697,20 +6744,20 @@
         </is>
       </c>
       <c r="C200">
-        <v>45.5</v>
+        <v>50.1</v>
       </c>
       <c r="D200">
-        <v>13.9</v>
+        <v>15</v>
       </c>
       <c r="E200">
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="F200">
-        <v>4200</v>
+        <v>5000</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H200">
@@ -6729,20 +6776,20 @@
         </is>
       </c>
       <c r="C201">
-        <v>50.5</v>
+        <v>46.5</v>
       </c>
       <c r="D201">
-        <v>15.9</v>
+        <v>14.4</v>
       </c>
       <c r="E201">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="F201">
-        <v>5400</v>
+        <v>4900</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H201">
@@ -6761,20 +6808,20 @@
         </is>
       </c>
       <c r="C202">
-        <v>44.9</v>
+        <v>45</v>
       </c>
       <c r="D202">
-        <v>13.3</v>
+        <v>15.4</v>
       </c>
       <c r="E202">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="F202">
-        <v>5100</v>
+        <v>5050</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H202">
@@ -6793,20 +6840,20 @@
         </is>
       </c>
       <c r="C203">
-        <v>45.2</v>
+        <v>43.8</v>
       </c>
       <c r="D203">
-        <v>15.8</v>
+        <v>13.9</v>
       </c>
       <c r="E203">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="F203">
-        <v>5300</v>
+        <v>4300</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H203">
@@ -6825,20 +6872,20 @@
         </is>
       </c>
       <c r="C204">
-        <v>46.6</v>
+        <v>45.5</v>
       </c>
       <c r="D204">
-        <v>14.2</v>
+        <v>15</v>
       </c>
       <c r="E204">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="F204">
-        <v>4850</v>
+        <v>5000</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H204">
@@ -6857,20 +6904,20 @@
         </is>
       </c>
       <c r="C205">
-        <v>48.5</v>
+        <v>43.2</v>
       </c>
       <c r="D205">
-        <v>14.1</v>
+        <v>14.5</v>
       </c>
       <c r="E205">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="F205">
-        <v>5300</v>
+        <v>4450</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H205">
@@ -6889,20 +6936,20 @@
         </is>
       </c>
       <c r="C206">
-        <v>45.1</v>
+        <v>50.4</v>
       </c>
       <c r="D206">
-        <v>14.4</v>
+        <v>15.3</v>
       </c>
       <c r="E206">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="F206">
-        <v>4400</v>
+        <v>5550</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H206">
@@ -6921,20 +6968,20 @@
         </is>
       </c>
       <c r="C207">
-        <v>50.1</v>
+        <v>45.3</v>
       </c>
       <c r="D207">
-        <v>15</v>
+        <v>13.8</v>
       </c>
       <c r="E207">
-        <v>225</v>
+        <v>208</v>
       </c>
       <c r="F207">
-        <v>5000</v>
+        <v>4200</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H207">
@@ -6953,20 +7000,20 @@
         </is>
       </c>
       <c r="C208">
-        <v>46.5</v>
+        <v>46.2</v>
       </c>
       <c r="D208">
-        <v>14.4</v>
+        <v>14.9</v>
       </c>
       <c r="E208">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="F208">
-        <v>4900</v>
+        <v>5300</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H208">
@@ -6985,20 +7032,20 @@
         </is>
       </c>
       <c r="C209">
-        <v>45</v>
+        <v>45.7</v>
       </c>
       <c r="D209">
-        <v>15.4</v>
+        <v>13.9</v>
       </c>
       <c r="E209">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="F209">
-        <v>5050</v>
+        <v>4400</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H209">
@@ -7017,20 +7064,20 @@
         </is>
       </c>
       <c r="C210">
-        <v>43.8</v>
+        <v>54.3</v>
       </c>
       <c r="D210">
-        <v>13.9</v>
+        <v>15.7</v>
       </c>
       <c r="E210">
-        <v>208</v>
+        <v>231</v>
       </c>
       <c r="F210">
-        <v>4300</v>
+        <v>5650</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H210">
@@ -7049,20 +7096,20 @@
         </is>
       </c>
       <c r="C211">
-        <v>45.5</v>
+        <v>45.8</v>
       </c>
       <c r="D211">
-        <v>15</v>
+        <v>14.2</v>
       </c>
       <c r="E211">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F211">
-        <v>5000</v>
+        <v>4700</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H211">
@@ -7081,20 +7128,20 @@
         </is>
       </c>
       <c r="C212">
-        <v>43.2</v>
+        <v>49.8</v>
       </c>
       <c r="D212">
-        <v>14.5</v>
+        <v>16.8</v>
       </c>
       <c r="E212">
-        <v>208</v>
+        <v>230</v>
       </c>
       <c r="F212">
-        <v>4450</v>
+        <v>5700</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H212">
@@ -7113,16 +7160,16 @@
         </is>
       </c>
       <c r="C213">
-        <v>50.4</v>
+        <v>49.5</v>
       </c>
       <c r="D213">
-        <v>15.3</v>
+        <v>16.2</v>
       </c>
       <c r="E213">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="F213">
-        <v>5550</v>
+        <v>5800</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
@@ -7145,16 +7192,16 @@
         </is>
       </c>
       <c r="C214">
-        <v>45.3</v>
+        <v>43.5</v>
       </c>
       <c r="D214">
-        <v>13.8</v>
+        <v>14.2</v>
       </c>
       <c r="E214">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="F214">
-        <v>4200</v>
+        <v>4700</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
@@ -7177,16 +7224,16 @@
         </is>
       </c>
       <c r="C215">
-        <v>46.2</v>
+        <v>50.7</v>
       </c>
       <c r="D215">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="E215">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F215">
-        <v>5300</v>
+        <v>5550</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
@@ -7209,16 +7256,16 @@
         </is>
       </c>
       <c r="C216">
-        <v>45.7</v>
+        <v>47.7</v>
       </c>
       <c r="D216">
-        <v>13.9</v>
+        <v>15</v>
       </c>
       <c r="E216">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F216">
-        <v>4400</v>
+        <v>4750</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
@@ -7241,16 +7288,16 @@
         </is>
       </c>
       <c r="C217">
-        <v>54.3</v>
+        <v>46.4</v>
       </c>
       <c r="D217">
-        <v>15.7</v>
+        <v>15.6</v>
       </c>
       <c r="E217">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="F217">
-        <v>5650</v>
+        <v>5000</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
@@ -7273,20 +7320,20 @@
         </is>
       </c>
       <c r="C218">
-        <v>45.8</v>
+        <v>48.2</v>
       </c>
       <c r="D218">
-        <v>14.2</v>
+        <v>15.6</v>
       </c>
       <c r="E218">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F218">
-        <v>4700</v>
+        <v>5100</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H218">
@@ -7305,20 +7352,20 @@
         </is>
       </c>
       <c r="C219">
-        <v>49.8</v>
+        <v>46.5</v>
       </c>
       <c r="D219">
-        <v>16.8</v>
+        <v>14.8</v>
       </c>
       <c r="E219">
-        <v>230</v>
+        <v>217</v>
       </c>
       <c r="F219">
-        <v>5700</v>
+        <v>5200</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H219">
@@ -7337,16 +7384,21 @@
         </is>
       </c>
       <c r="C220">
-        <v>46.2</v>
+        <v>46.4</v>
       </c>
       <c r="D220">
-        <v>14.4</v>
+        <v>15</v>
       </c>
       <c r="E220">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F220">
-        <v>4650</v>
+        <v>4700</v>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
       </c>
       <c r="H220">
         <v>2008</v>
@@ -7364,13 +7416,13 @@
         </is>
       </c>
       <c r="C221">
-        <v>49.5</v>
+        <v>48.6</v>
       </c>
       <c r="D221">
-        <v>16.2</v>
+        <v>16</v>
       </c>
       <c r="E221">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F221">
         <v>5800</v>
@@ -7396,16 +7448,16 @@
         </is>
       </c>
       <c r="C222">
-        <v>43.5</v>
+        <v>47.5</v>
       </c>
       <c r="D222">
         <v>14.2</v>
       </c>
       <c r="E222">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="F222">
-        <v>4700</v>
+        <v>4600</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
@@ -7428,16 +7480,16 @@
         </is>
       </c>
       <c r="C223">
-        <v>50.7</v>
+        <v>51.1</v>
       </c>
       <c r="D223">
-        <v>15</v>
+        <v>16.3</v>
       </c>
       <c r="E223">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F223">
-        <v>5550</v>
+        <v>6000</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
@@ -7460,13 +7512,13 @@
         </is>
       </c>
       <c r="C224">
-        <v>47.7</v>
+        <v>45.2</v>
       </c>
       <c r="D224">
-        <v>15</v>
+        <v>13.8</v>
       </c>
       <c r="E224">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F224">
         <v>4750</v>
@@ -7492,16 +7544,16 @@
         </is>
       </c>
       <c r="C225">
-        <v>46.4</v>
+        <v>45.2</v>
       </c>
       <c r="D225">
-        <v>15.6</v>
+        <v>16.4</v>
       </c>
       <c r="E225">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F225">
-        <v>5000</v>
+        <v>5950</v>
       </c>
       <c r="G225" t="inlineStr">
         <is>
@@ -7524,24 +7576,24 @@
         </is>
       </c>
       <c r="C226">
-        <v>48.2</v>
+        <v>49.1</v>
       </c>
       <c r="D226">
-        <v>15.6</v>
+        <v>14.5</v>
       </c>
       <c r="E226">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="F226">
-        <v>5100</v>
+        <v>4625</v>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H226">
-        <v>2008</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="227">
@@ -7556,24 +7608,24 @@
         </is>
       </c>
       <c r="C227">
-        <v>46.5</v>
+        <v>52.5</v>
       </c>
       <c r="D227">
-        <v>14.8</v>
+        <v>15.6</v>
       </c>
       <c r="E227">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="F227">
-        <v>5200</v>
+        <v>5450</v>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H227">
-        <v>2008</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="228">
@@ -7588,16 +7640,16 @@
         </is>
       </c>
       <c r="C228">
-        <v>46.4</v>
+        <v>47.4</v>
       </c>
       <c r="D228">
-        <v>15</v>
+        <v>14.6</v>
       </c>
       <c r="E228">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="F228">
-        <v>4700</v>
+        <v>4725</v>
       </c>
       <c r="G228" t="inlineStr">
         <is>
@@ -7605,7 +7657,7 @@
         </is>
       </c>
       <c r="H228">
-        <v>2008</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="229">
@@ -7620,16 +7672,16 @@
         </is>
       </c>
       <c r="C229">
-        <v>48.6</v>
+        <v>50</v>
       </c>
       <c r="D229">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="E229">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="F229">
-        <v>5800</v>
+        <v>5350</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
@@ -7637,7 +7689,7 @@
         </is>
       </c>
       <c r="H229">
-        <v>2008</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="230">
@@ -7652,16 +7704,16 @@
         </is>
       </c>
       <c r="C230">
-        <v>47.5</v>
+        <v>44.9</v>
       </c>
       <c r="D230">
-        <v>14.2</v>
+        <v>13.8</v>
       </c>
       <c r="E230">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F230">
-        <v>4600</v>
+        <v>4750</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
@@ -7669,7 +7721,7 @@
         </is>
       </c>
       <c r="H230">
-        <v>2008</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="231">
@@ -7684,16 +7736,16 @@
         </is>
       </c>
       <c r="C231">
-        <v>51.1</v>
+        <v>50.8</v>
       </c>
       <c r="D231">
-        <v>16.3</v>
+        <v>17.3</v>
       </c>
       <c r="E231">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="F231">
-        <v>6000</v>
+        <v>5600</v>
       </c>
       <c r="G231" t="inlineStr">
         <is>
@@ -7701,7 +7753,7 @@
         </is>
       </c>
       <c r="H231">
-        <v>2008</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="232">
@@ -7716,16 +7768,16 @@
         </is>
       </c>
       <c r="C232">
-        <v>45.2</v>
+        <v>43.4</v>
       </c>
       <c r="D232">
-        <v>13.8</v>
+        <v>14.4</v>
       </c>
       <c r="E232">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="F232">
-        <v>4750</v>
+        <v>4600</v>
       </c>
       <c r="G232" t="inlineStr">
         <is>
@@ -7733,7 +7785,7 @@
         </is>
       </c>
       <c r="H232">
-        <v>2008</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="233">
@@ -7748,16 +7800,16 @@
         </is>
       </c>
       <c r="C233">
-        <v>45.2</v>
+        <v>51.3</v>
       </c>
       <c r="D233">
-        <v>16.4</v>
+        <v>14.2</v>
       </c>
       <c r="E233">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="F233">
-        <v>5950</v>
+        <v>5300</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
@@ -7765,7 +7817,7 @@
         </is>
       </c>
       <c r="H233">
-        <v>2008</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="234">
@@ -7780,16 +7832,16 @@
         </is>
       </c>
       <c r="C234">
-        <v>49.1</v>
+        <v>47.5</v>
       </c>
       <c r="D234">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="E234">
         <v>212</v>
       </c>
       <c r="F234">
-        <v>4625</v>
+        <v>4875</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
@@ -7812,16 +7864,16 @@
         </is>
       </c>
       <c r="C235">
-        <v>52.5</v>
+        <v>52.1</v>
       </c>
       <c r="D235">
-        <v>15.6</v>
+        <v>17</v>
       </c>
       <c r="E235">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="F235">
-        <v>5450</v>
+        <v>5550</v>
       </c>
       <c r="G235" t="inlineStr">
         <is>
@@ -7844,16 +7896,16 @@
         </is>
       </c>
       <c r="C236">
-        <v>47.4</v>
+        <v>47.5</v>
       </c>
       <c r="D236">
-        <v>14.6</v>
+        <v>15</v>
       </c>
       <c r="E236">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F236">
-        <v>4725</v>
+        <v>4950</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
@@ -7876,16 +7928,16 @@
         </is>
       </c>
       <c r="C237">
-        <v>50</v>
+        <v>52.2</v>
       </c>
       <c r="D237">
-        <v>15.9</v>
+        <v>17.1</v>
       </c>
       <c r="E237">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="F237">
-        <v>5350</v>
+        <v>5400</v>
       </c>
       <c r="G237" t="inlineStr">
         <is>
@@ -7908,10 +7960,10 @@
         </is>
       </c>
       <c r="C238">
-        <v>44.9</v>
+        <v>45.5</v>
       </c>
       <c r="D238">
-        <v>13.8</v>
+        <v>14.5</v>
       </c>
       <c r="E238">
         <v>212</v>
@@ -7940,16 +7992,16 @@
         </is>
       </c>
       <c r="C239">
-        <v>50.8</v>
+        <v>49.5</v>
       </c>
       <c r="D239">
-        <v>17.3</v>
+        <v>16.1</v>
       </c>
       <c r="E239">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="F239">
-        <v>5600</v>
+        <v>5650</v>
       </c>
       <c r="G239" t="inlineStr">
         <is>
@@ -7972,16 +8024,16 @@
         </is>
       </c>
       <c r="C240">
-        <v>43.4</v>
+        <v>44.5</v>
       </c>
       <c r="D240">
-        <v>14.4</v>
+        <v>14.7</v>
       </c>
       <c r="E240">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="F240">
-        <v>4600</v>
+        <v>4850</v>
       </c>
       <c r="G240" t="inlineStr">
         <is>
@@ -8004,16 +8056,16 @@
         </is>
       </c>
       <c r="C241">
-        <v>51.3</v>
+        <v>50.8</v>
       </c>
       <c r="D241">
-        <v>14.2</v>
+        <v>15.7</v>
       </c>
       <c r="E241">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="F241">
-        <v>5300</v>
+        <v>5200</v>
       </c>
       <c r="G241" t="inlineStr">
         <is>
@@ -8036,20 +8088,20 @@
         </is>
       </c>
       <c r="C242">
-        <v>47.5</v>
+        <v>49.4</v>
       </c>
       <c r="D242">
-        <v>14</v>
+        <v>15.8</v>
       </c>
       <c r="E242">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F242">
-        <v>4875</v>
+        <v>4925</v>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H242">
@@ -8068,20 +8120,20 @@
         </is>
       </c>
       <c r="C243">
-        <v>52.1</v>
+        <v>46.9</v>
       </c>
       <c r="D243">
-        <v>17</v>
+        <v>14.6</v>
       </c>
       <c r="E243">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="F243">
-        <v>5550</v>
+        <v>4875</v>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H243">
@@ -8100,16 +8152,16 @@
         </is>
       </c>
       <c r="C244">
-        <v>47.5</v>
+        <v>48.4</v>
       </c>
       <c r="D244">
-        <v>15</v>
+        <v>14.4</v>
       </c>
       <c r="E244">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="F244">
-        <v>4950</v>
+        <v>4625</v>
       </c>
       <c r="G244" t="inlineStr">
         <is>
@@ -8132,16 +8184,16 @@
         </is>
       </c>
       <c r="C245">
-        <v>52.2</v>
+        <v>51.1</v>
       </c>
       <c r="D245">
-        <v>17.1</v>
+        <v>16.5</v>
       </c>
       <c r="E245">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F245">
-        <v>5400</v>
+        <v>5250</v>
       </c>
       <c r="G245" t="inlineStr">
         <is>
@@ -8164,16 +8216,16 @@
         </is>
       </c>
       <c r="C246">
-        <v>45.5</v>
+        <v>48.5</v>
       </c>
       <c r="D246">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="E246">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="F246">
-        <v>4750</v>
+        <v>4850</v>
       </c>
       <c r="G246" t="inlineStr">
         <is>
@@ -8196,16 +8248,16 @@
         </is>
       </c>
       <c r="C247">
-        <v>49.5</v>
+        <v>55.9</v>
       </c>
       <c r="D247">
-        <v>16.1</v>
+        <v>17</v>
       </c>
       <c r="E247">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="F247">
-        <v>5650</v>
+        <v>5600</v>
       </c>
       <c r="G247" t="inlineStr">
         <is>
@@ -8228,16 +8280,16 @@
         </is>
       </c>
       <c r="C248">
-        <v>44.5</v>
+        <v>47.2</v>
       </c>
       <c r="D248">
-        <v>14.7</v>
+        <v>15.5</v>
       </c>
       <c r="E248">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F248">
-        <v>4850</v>
+        <v>4975</v>
       </c>
       <c r="G248" t="inlineStr">
         <is>
@@ -8260,16 +8312,16 @@
         </is>
       </c>
       <c r="C249">
-        <v>50.8</v>
+        <v>49.1</v>
       </c>
       <c r="D249">
-        <v>15.7</v>
+        <v>15</v>
       </c>
       <c r="E249">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F249">
-        <v>5200</v>
+        <v>5500</v>
       </c>
       <c r="G249" t="inlineStr">
         <is>
@@ -8292,16 +8344,16 @@
         </is>
       </c>
       <c r="C250">
-        <v>49.4</v>
+        <v>46.8</v>
       </c>
       <c r="D250">
-        <v>15.8</v>
+        <v>16.1</v>
       </c>
       <c r="E250">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="F250">
-        <v>4925</v>
+        <v>5500</v>
       </c>
       <c r="G250" t="inlineStr">
         <is>
@@ -8324,16 +8376,16 @@
         </is>
       </c>
       <c r="C251">
-        <v>46.9</v>
+        <v>41.7</v>
       </c>
       <c r="D251">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="E251">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="F251">
-        <v>4875</v>
+        <v>4700</v>
       </c>
       <c r="G251" t="inlineStr">
         <is>
@@ -8356,20 +8408,20 @@
         </is>
       </c>
       <c r="C252">
-        <v>48.4</v>
+        <v>53.4</v>
       </c>
       <c r="D252">
-        <v>14.4</v>
+        <v>15.8</v>
       </c>
       <c r="E252">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="F252">
-        <v>4625</v>
+        <v>5500</v>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H252">
@@ -8388,20 +8440,20 @@
         </is>
       </c>
       <c r="C253">
-        <v>51.1</v>
+        <v>43.3</v>
       </c>
       <c r="D253">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="E253">
-        <v>225</v>
+        <v>208</v>
       </c>
       <c r="F253">
-        <v>5250</v>
+        <v>4575</v>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H253">
@@ -8420,20 +8472,20 @@
         </is>
       </c>
       <c r="C254">
-        <v>48.5</v>
+        <v>48.1</v>
       </c>
       <c r="D254">
-        <v>15</v>
+        <v>15.1</v>
       </c>
       <c r="E254">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="F254">
-        <v>4850</v>
+        <v>5500</v>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H254">
@@ -8452,20 +8504,20 @@
         </is>
       </c>
       <c r="C255">
-        <v>55.9</v>
+        <v>50.5</v>
       </c>
       <c r="D255">
-        <v>17</v>
+        <v>15.2</v>
       </c>
       <c r="E255">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="F255">
-        <v>5600</v>
+        <v>5000</v>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H255">
@@ -8484,20 +8536,20 @@
         </is>
       </c>
       <c r="C256">
-        <v>47.2</v>
+        <v>49.8</v>
       </c>
       <c r="D256">
-        <v>15.5</v>
+        <v>15.9</v>
       </c>
       <c r="E256">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="F256">
-        <v>4975</v>
+        <v>5950</v>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H256">
@@ -8516,20 +8568,20 @@
         </is>
       </c>
       <c r="C257">
-        <v>49.1</v>
+        <v>43.5</v>
       </c>
       <c r="D257">
-        <v>15</v>
+        <v>15.2</v>
       </c>
       <c r="E257">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="F257">
-        <v>5500</v>
+        <v>4650</v>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H257">
@@ -8548,16 +8600,21 @@
         </is>
       </c>
       <c r="C258">
-        <v>47.3</v>
+        <v>51.5</v>
       </c>
       <c r="D258">
-        <v>13.8</v>
+        <v>16.3</v>
       </c>
       <c r="E258">
-        <v>216</v>
+        <v>230</v>
       </c>
       <c r="F258">
-        <v>4725</v>
+        <v>5500</v>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
       </c>
       <c r="H258">
         <v>2009</v>
@@ -8575,20 +8632,20 @@
         </is>
       </c>
       <c r="C259">
-        <v>46.8</v>
+        <v>46.2</v>
       </c>
       <c r="D259">
-        <v>16.1</v>
+        <v>14.1</v>
       </c>
       <c r="E259">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="F259">
-        <v>5500</v>
+        <v>4375</v>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H259">
@@ -8607,20 +8664,20 @@
         </is>
       </c>
       <c r="C260">
-        <v>41.7</v>
+        <v>55.1</v>
       </c>
       <c r="D260">
-        <v>14.7</v>
+        <v>16</v>
       </c>
       <c r="E260">
-        <v>210</v>
+        <v>230</v>
       </c>
       <c r="F260">
-        <v>4700</v>
+        <v>5850</v>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H260">
@@ -8639,16 +8696,16 @@
         </is>
       </c>
       <c r="C261">
-        <v>53.4</v>
+        <v>48.8</v>
       </c>
       <c r="D261">
-        <v>15.8</v>
+        <v>16.2</v>
       </c>
       <c r="E261">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="F261">
-        <v>5500</v>
+        <v>6000</v>
       </c>
       <c r="G261" t="inlineStr">
         <is>
@@ -8671,16 +8728,16 @@
         </is>
       </c>
       <c r="C262">
-        <v>43.3</v>
+        <v>47.2</v>
       </c>
       <c r="D262">
-        <v>14</v>
+        <v>13.7</v>
       </c>
       <c r="E262">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="F262">
-        <v>4575</v>
+        <v>4925</v>
       </c>
       <c r="G262" t="inlineStr">
         <is>
@@ -8703,20 +8760,20 @@
         </is>
       </c>
       <c r="C263">
-        <v>48.1</v>
+        <v>46.8</v>
       </c>
       <c r="D263">
-        <v>15.1</v>
+        <v>14.3</v>
       </c>
       <c r="E263">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="F263">
-        <v>5500</v>
+        <v>4850</v>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H263">
@@ -8735,20 +8792,20 @@
         </is>
       </c>
       <c r="C264">
-        <v>50.5</v>
+        <v>50.4</v>
       </c>
       <c r="D264">
-        <v>15.2</v>
+        <v>15.7</v>
       </c>
       <c r="E264">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="F264">
-        <v>5000</v>
+        <v>5750</v>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H264">
@@ -8767,20 +8824,20 @@
         </is>
       </c>
       <c r="C265">
-        <v>49.8</v>
+        <v>45.2</v>
       </c>
       <c r="D265">
-        <v>15.9</v>
+        <v>14.8</v>
       </c>
       <c r="E265">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="F265">
-        <v>5950</v>
+        <v>5200</v>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H265">
@@ -8799,20 +8856,20 @@
         </is>
       </c>
       <c r="C266">
-        <v>43.5</v>
+        <v>49.9</v>
       </c>
       <c r="D266">
-        <v>15.2</v>
+        <v>16.1</v>
       </c>
       <c r="E266">
         <v>213</v>
       </c>
       <c r="F266">
-        <v>4650</v>
+        <v>5400</v>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H266">
@@ -8822,89 +8879,89 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Gentoo</t>
+          <t>Chinstrap</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Biscoe</t>
+          <t>Dream</t>
         </is>
       </c>
       <c r="C267">
-        <v>51.5</v>
+        <v>46.5</v>
       </c>
       <c r="D267">
-        <v>16.3</v>
+        <v>17.9</v>
       </c>
       <c r="E267">
-        <v>230</v>
+        <v>192</v>
       </c>
       <c r="F267">
-        <v>5500</v>
+        <v>3500</v>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H267">
-        <v>2009</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Gentoo</t>
+          <t>Chinstrap</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Biscoe</t>
+          <t>Dream</t>
         </is>
       </c>
       <c r="C268">
-        <v>46.2</v>
+        <v>50</v>
       </c>
       <c r="D268">
-        <v>14.1</v>
+        <v>19.5</v>
       </c>
       <c r="E268">
-        <v>217</v>
+        <v>196</v>
       </c>
       <c r="F268">
-        <v>4375</v>
+        <v>3900</v>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H268">
-        <v>2009</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Gentoo</t>
+          <t>Chinstrap</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Biscoe</t>
+          <t>Dream</t>
         </is>
       </c>
       <c r="C269">
-        <v>55.1</v>
+        <v>51.3</v>
       </c>
       <c r="D269">
-        <v>16</v>
+        <v>19.2</v>
       </c>
       <c r="E269">
-        <v>230</v>
+        <v>193</v>
       </c>
       <c r="F269">
-        <v>5850</v>
+        <v>3650</v>
       </c>
       <c r="G269" t="inlineStr">
         <is>
@@ -8912,58 +8969,63 @@
         </is>
       </c>
       <c r="H269">
-        <v>2009</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Gentoo</t>
+          <t>Chinstrap</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Biscoe</t>
+          <t>Dream</t>
         </is>
       </c>
       <c r="C270">
-        <v>44.5</v>
+        <v>45.4</v>
       </c>
       <c r="D270">
-        <v>15.7</v>
+        <v>18.7</v>
       </c>
       <c r="E270">
-        <v>217</v>
+        <v>188</v>
       </c>
       <c r="F270">
-        <v>4875</v>
+        <v>3525</v>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
       </c>
       <c r="H270">
-        <v>2009</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Gentoo</t>
+          <t>Chinstrap</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Biscoe</t>
+          <t>Dream</t>
         </is>
       </c>
       <c r="C271">
-        <v>48.8</v>
+        <v>52.7</v>
       </c>
       <c r="D271">
-        <v>16.2</v>
+        <v>19.8</v>
       </c>
       <c r="E271">
-        <v>222</v>
+        <v>197</v>
       </c>
       <c r="F271">
-        <v>6000</v>
+        <v>3725</v>
       </c>
       <c r="G271" t="inlineStr">
         <is>
@@ -8971,31 +9033,31 @@
         </is>
       </c>
       <c r="H271">
-        <v>2009</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Gentoo</t>
+          <t>Chinstrap</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Biscoe</t>
+          <t>Dream</t>
         </is>
       </c>
       <c r="C272">
-        <v>47.2</v>
+        <v>45.2</v>
       </c>
       <c r="D272">
-        <v>13.7</v>
+        <v>17.8</v>
       </c>
       <c r="E272">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="F272">
-        <v>4925</v>
+        <v>3950</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -9003,150 +9065,167 @@
         </is>
       </c>
       <c r="H272">
-        <v>2009</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Gentoo</t>
+          <t>Chinstrap</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Biscoe</t>
+          <t>Dream</t>
+        </is>
+      </c>
+      <c r="C273">
+        <v>46.1</v>
+      </c>
+      <c r="D273">
+        <v>18.2</v>
+      </c>
+      <c r="E273">
+        <v>178</v>
+      </c>
+      <c r="F273">
+        <v>3250</v>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>female</t>
         </is>
       </c>
       <c r="H273">
-        <v>2009</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Gentoo</t>
+          <t>Chinstrap</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Biscoe</t>
+          <t>Dream</t>
         </is>
       </c>
       <c r="C274">
-        <v>46.8</v>
+        <v>51.3</v>
       </c>
       <c r="D274">
-        <v>14.3</v>
+        <v>18.2</v>
       </c>
       <c r="E274">
-        <v>215</v>
+        <v>197</v>
       </c>
       <c r="F274">
-        <v>4850</v>
+        <v>3750</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H274">
-        <v>2009</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Gentoo</t>
+          <t>Chinstrap</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Biscoe</t>
+          <t>Dream</t>
         </is>
       </c>
       <c r="C275">
-        <v>50.4</v>
+        <v>46</v>
       </c>
       <c r="D275">
-        <v>15.7</v>
+        <v>18.9</v>
       </c>
       <c r="E275">
-        <v>222</v>
+        <v>195</v>
       </c>
       <c r="F275">
-        <v>5750</v>
+        <v>4150</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H275">
-        <v>2009</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Gentoo</t>
+          <t>Chinstrap</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Biscoe</t>
+          <t>Dream</t>
         </is>
       </c>
       <c r="C276">
-        <v>45.2</v>
+        <v>51.3</v>
       </c>
       <c r="D276">
-        <v>14.8</v>
+        <v>19.9</v>
       </c>
       <c r="E276">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="F276">
-        <v>5200</v>
+        <v>3700</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H276">
-        <v>2009</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Gentoo</t>
+          <t>Chinstrap</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Biscoe</t>
+          <t>Dream</t>
         </is>
       </c>
       <c r="C277">
-        <v>49.9</v>
+        <v>46.6</v>
       </c>
       <c r="D277">
-        <v>16.1</v>
+        <v>17.8</v>
       </c>
       <c r="E277">
-        <v>213</v>
+        <v>193</v>
       </c>
       <c r="F277">
-        <v>5400</v>
+        <v>3800</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H277">
-        <v>2009</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="278">
@@ -9161,20 +9240,20 @@
         </is>
       </c>
       <c r="C278">
-        <v>46.5</v>
+        <v>51.7</v>
       </c>
       <c r="D278">
-        <v>17.9</v>
+        <v>20.3</v>
       </c>
       <c r="E278">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F278">
-        <v>3500</v>
+        <v>3775</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H278">
@@ -9193,20 +9272,20 @@
         </is>
       </c>
       <c r="C279">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D279">
-        <v>19.5</v>
+        <v>17.3</v>
       </c>
       <c r="E279">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="F279">
-        <v>3900</v>
+        <v>3700</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H279">
@@ -9225,16 +9304,16 @@
         </is>
       </c>
       <c r="C280">
-        <v>51.3</v>
+        <v>52</v>
       </c>
       <c r="D280">
-        <v>19.2</v>
+        <v>18.1</v>
       </c>
       <c r="E280">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="F280">
-        <v>3650</v>
+        <v>4050</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -9257,16 +9336,16 @@
         </is>
       </c>
       <c r="C281">
-        <v>45.4</v>
+        <v>45.9</v>
       </c>
       <c r="D281">
-        <v>18.7</v>
+        <v>17.1</v>
       </c>
       <c r="E281">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F281">
-        <v>3525</v>
+        <v>3575</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -9289,16 +9368,16 @@
         </is>
       </c>
       <c r="C282">
-        <v>52.7</v>
+        <v>50.5</v>
       </c>
       <c r="D282">
-        <v>19.8</v>
+        <v>19.6</v>
       </c>
       <c r="E282">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="F282">
-        <v>3725</v>
+        <v>4050</v>
       </c>
       <c r="G282" t="inlineStr">
         <is>
@@ -9321,20 +9400,20 @@
         </is>
       </c>
       <c r="C283">
-        <v>45.2</v>
+        <v>50.3</v>
       </c>
       <c r="D283">
-        <v>17.8</v>
+        <v>20</v>
       </c>
       <c r="E283">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F283">
-        <v>3950</v>
+        <v>3300</v>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H283">
@@ -9353,16 +9432,16 @@
         </is>
       </c>
       <c r="C284">
-        <v>46.1</v>
+        <v>58</v>
       </c>
       <c r="D284">
-        <v>18.2</v>
+        <v>17.8</v>
       </c>
       <c r="E284">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="F284">
-        <v>3250</v>
+        <v>3700</v>
       </c>
       <c r="G284" t="inlineStr">
         <is>
@@ -9385,20 +9464,20 @@
         </is>
       </c>
       <c r="C285">
-        <v>51.3</v>
+        <v>46.4</v>
       </c>
       <c r="D285">
-        <v>18.2</v>
+        <v>18.6</v>
       </c>
       <c r="E285">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="F285">
-        <v>3750</v>
+        <v>3450</v>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H285">
@@ -9417,20 +9496,20 @@
         </is>
       </c>
       <c r="C286">
-        <v>46</v>
+        <v>49.2</v>
       </c>
       <c r="D286">
-        <v>18.9</v>
+        <v>18.2</v>
       </c>
       <c r="E286">
         <v>195</v>
       </c>
       <c r="F286">
-        <v>4150</v>
+        <v>4400</v>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H286">
@@ -9449,20 +9528,20 @@
         </is>
       </c>
       <c r="C287">
-        <v>51.3</v>
+        <v>42.4</v>
       </c>
       <c r="D287">
-        <v>19.9</v>
+        <v>17.3</v>
       </c>
       <c r="E287">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="F287">
-        <v>3700</v>
+        <v>3600</v>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H287">
@@ -9481,20 +9560,20 @@
         </is>
       </c>
       <c r="C288">
-        <v>46.6</v>
+        <v>48.5</v>
       </c>
       <c r="D288">
-        <v>17.8</v>
+        <v>17.5</v>
       </c>
       <c r="E288">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F288">
-        <v>3800</v>
+        <v>3400</v>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H288">
@@ -9513,20 +9592,20 @@
         </is>
       </c>
       <c r="C289">
-        <v>51.7</v>
+        <v>43.2</v>
       </c>
       <c r="D289">
-        <v>20.3</v>
+        <v>16.6</v>
       </c>
       <c r="E289">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="F289">
-        <v>3775</v>
+        <v>2900</v>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H289">
@@ -9545,20 +9624,20 @@
         </is>
       </c>
       <c r="C290">
-        <v>47</v>
+        <v>50.6</v>
       </c>
       <c r="D290">
-        <v>17.3</v>
+        <v>19.4</v>
       </c>
       <c r="E290">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="F290">
-        <v>3700</v>
+        <v>3800</v>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H290">
@@ -9577,20 +9656,20 @@
         </is>
       </c>
       <c r="C291">
-        <v>52</v>
+        <v>46.7</v>
       </c>
       <c r="D291">
-        <v>18.1</v>
+        <v>17.9</v>
       </c>
       <c r="E291">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F291">
-        <v>4050</v>
+        <v>3300</v>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H291">
@@ -9609,20 +9688,20 @@
         </is>
       </c>
       <c r="C292">
-        <v>45.9</v>
+        <v>52</v>
       </c>
       <c r="D292">
-        <v>17.1</v>
+        <v>19</v>
       </c>
       <c r="E292">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="F292">
-        <v>3575</v>
+        <v>4150</v>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H292">
@@ -9644,21 +9723,21 @@
         <v>50.5</v>
       </c>
       <c r="D293">
-        <v>19.6</v>
+        <v>18.4</v>
       </c>
       <c r="E293">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F293">
-        <v>4050</v>
+        <v>3400</v>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H293">
-        <v>2007</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="294">
@@ -9673,16 +9752,16 @@
         </is>
       </c>
       <c r="C294">
-        <v>50.3</v>
+        <v>49.5</v>
       </c>
       <c r="D294">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E294">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="F294">
-        <v>3300</v>
+        <v>3800</v>
       </c>
       <c r="G294" t="inlineStr">
         <is>
@@ -9690,7 +9769,7 @@
         </is>
       </c>
       <c r="H294">
-        <v>2007</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="295">
@@ -9705,13 +9784,13 @@
         </is>
       </c>
       <c r="C295">
-        <v>58</v>
+        <v>46.4</v>
       </c>
       <c r="D295">
         <v>17.8</v>
       </c>
       <c r="E295">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c r="F295">
         <v>3700</v>
@@ -9722,7 +9801,7 @@
         </is>
       </c>
       <c r="H295">
-        <v>2007</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="296">
@@ -9737,24 +9816,24 @@
         </is>
       </c>
       <c r="C296">
-        <v>46.4</v>
+        <v>52.8</v>
       </c>
       <c r="D296">
-        <v>18.6</v>
+        <v>20</v>
       </c>
       <c r="E296">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="F296">
-        <v>3450</v>
+        <v>4550</v>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H296">
-        <v>2007</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="297">
@@ -9769,24 +9848,24 @@
         </is>
       </c>
       <c r="C297">
-        <v>49.2</v>
+        <v>40.9</v>
       </c>
       <c r="D297">
-        <v>18.2</v>
+        <v>16.6</v>
       </c>
       <c r="E297">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="F297">
-        <v>4400</v>
+        <v>3200</v>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H297">
-        <v>2007</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="298">
@@ -9801,24 +9880,24 @@
         </is>
       </c>
       <c r="C298">
-        <v>42.4</v>
+        <v>54.2</v>
       </c>
       <c r="D298">
-        <v>17.3</v>
+        <v>20.8</v>
       </c>
       <c r="E298">
-        <v>181</v>
+        <v>201</v>
       </c>
       <c r="F298">
-        <v>3600</v>
+        <v>4300</v>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H298">
-        <v>2007</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="299">
@@ -9833,24 +9912,24 @@
         </is>
       </c>
       <c r="C299">
-        <v>48.5</v>
+        <v>42.5</v>
       </c>
       <c r="D299">
-        <v>17.5</v>
+        <v>16.7</v>
       </c>
       <c r="E299">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="F299">
-        <v>3400</v>
+        <v>3350</v>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H299">
-        <v>2007</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="300">
@@ -9865,24 +9944,24 @@
         </is>
       </c>
       <c r="C300">
-        <v>43.2</v>
+        <v>51</v>
       </c>
       <c r="D300">
-        <v>16.6</v>
+        <v>18.8</v>
       </c>
       <c r="E300">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="F300">
-        <v>2900</v>
+        <v>4100</v>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H300">
-        <v>2007</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="301">
@@ -9897,16 +9976,16 @@
         </is>
       </c>
       <c r="C301">
-        <v>50.6</v>
+        <v>49.7</v>
       </c>
       <c r="D301">
-        <v>19.4</v>
+        <v>18.6</v>
       </c>
       <c r="E301">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F301">
-        <v>3800</v>
+        <v>3600</v>
       </c>
       <c r="G301" t="inlineStr">
         <is>
@@ -9914,7 +9993,7 @@
         </is>
       </c>
       <c r="H301">
-        <v>2007</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="302">
@@ -9929,16 +10008,16 @@
         </is>
       </c>
       <c r="C302">
-        <v>46.7</v>
+        <v>47.5</v>
       </c>
       <c r="D302">
-        <v>17.9</v>
+        <v>16.8</v>
       </c>
       <c r="E302">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="F302">
-        <v>3300</v>
+        <v>3900</v>
       </c>
       <c r="G302" t="inlineStr">
         <is>
@@ -9946,7 +10025,7 @@
         </is>
       </c>
       <c r="H302">
-        <v>2007</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="303">
@@ -9961,24 +10040,24 @@
         </is>
       </c>
       <c r="C303">
-        <v>52</v>
+        <v>47.6</v>
       </c>
       <c r="D303">
-        <v>19</v>
+        <v>18.3</v>
       </c>
       <c r="E303">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="F303">
-        <v>4150</v>
+        <v>3850</v>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H303">
-        <v>2007</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="304">
@@ -9993,20 +10072,20 @@
         </is>
       </c>
       <c r="C304">
-        <v>50.5</v>
+        <v>52</v>
       </c>
       <c r="D304">
-        <v>18.4</v>
+        <v>20.7</v>
       </c>
       <c r="E304">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="F304">
-        <v>3400</v>
+        <v>4800</v>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H304">
@@ -10025,20 +10104,20 @@
         </is>
       </c>
       <c r="C305">
-        <v>49.5</v>
+        <v>46.9</v>
       </c>
       <c r="D305">
-        <v>19</v>
+        <v>16.6</v>
       </c>
       <c r="E305">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="F305">
-        <v>3800</v>
+        <v>2700</v>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H305">
@@ -10057,20 +10136,20 @@
         </is>
       </c>
       <c r="C306">
-        <v>46.4</v>
+        <v>53.5</v>
       </c>
       <c r="D306">
-        <v>17.8</v>
+        <v>19.9</v>
       </c>
       <c r="E306">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="F306">
-        <v>3700</v>
+        <v>4500</v>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H306">
@@ -10089,16 +10168,16 @@
         </is>
       </c>
       <c r="C307">
-        <v>52.8</v>
+        <v>49</v>
       </c>
       <c r="D307">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="E307">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="F307">
-        <v>4550</v>
+        <v>3950</v>
       </c>
       <c r="G307" t="inlineStr">
         <is>
@@ -10121,16 +10200,16 @@
         </is>
       </c>
       <c r="C308">
-        <v>40.9</v>
+        <v>46.2</v>
       </c>
       <c r="D308">
-        <v>16.6</v>
+        <v>17.5</v>
       </c>
       <c r="E308">
         <v>187</v>
       </c>
       <c r="F308">
-        <v>3200</v>
+        <v>3650</v>
       </c>
       <c r="G308" t="inlineStr">
         <is>
@@ -10153,16 +10232,16 @@
         </is>
       </c>
       <c r="C309">
-        <v>54.2</v>
+        <v>50.9</v>
       </c>
       <c r="D309">
-        <v>20.8</v>
+        <v>19.1</v>
       </c>
       <c r="E309">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="F309">
-        <v>4300</v>
+        <v>3550</v>
       </c>
       <c r="G309" t="inlineStr">
         <is>
@@ -10185,16 +10264,16 @@
         </is>
       </c>
       <c r="C310">
-        <v>42.5</v>
+        <v>45.5</v>
       </c>
       <c r="D310">
-        <v>16.7</v>
+        <v>17</v>
       </c>
       <c r="E310">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="F310">
-        <v>3350</v>
+        <v>3500</v>
       </c>
       <c r="G310" t="inlineStr">
         <is>
@@ -10217,24 +10296,24 @@
         </is>
       </c>
       <c r="C311">
-        <v>51</v>
+        <v>50.9</v>
       </c>
       <c r="D311">
-        <v>18.8</v>
+        <v>17.9</v>
       </c>
       <c r="E311">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="F311">
-        <v>4100</v>
+        <v>3675</v>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H311">
-        <v>2008</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="312">
@@ -10249,16 +10328,16 @@
         </is>
       </c>
       <c r="C312">
-        <v>49.7</v>
+        <v>50.8</v>
       </c>
       <c r="D312">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="E312">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="F312">
-        <v>3600</v>
+        <v>4450</v>
       </c>
       <c r="G312" t="inlineStr">
         <is>
@@ -10266,7 +10345,7 @@
         </is>
       </c>
       <c r="H312">
-        <v>2008</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="313">
@@ -10281,16 +10360,16 @@
         </is>
       </c>
       <c r="C313">
-        <v>47.5</v>
+        <v>50.1</v>
       </c>
       <c r="D313">
-        <v>16.8</v>
+        <v>17.9</v>
       </c>
       <c r="E313">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="F313">
-        <v>3900</v>
+        <v>3400</v>
       </c>
       <c r="G313" t="inlineStr">
         <is>
@@ -10298,7 +10377,7 @@
         </is>
       </c>
       <c r="H313">
-        <v>2008</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="314">
@@ -10313,24 +10392,24 @@
         </is>
       </c>
       <c r="C314">
-        <v>47.6</v>
+        <v>49</v>
       </c>
       <c r="D314">
-        <v>18.3</v>
+        <v>19.6</v>
       </c>
       <c r="E314">
-        <v>195</v>
+        <v>212</v>
       </c>
       <c r="F314">
-        <v>3850</v>
+        <v>4300</v>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H314">
-        <v>2008</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="315">
@@ -10345,16 +10424,16 @@
         </is>
       </c>
       <c r="C315">
-        <v>52</v>
+        <v>51.5</v>
       </c>
       <c r="D315">
-        <v>20.7</v>
+        <v>18.7</v>
       </c>
       <c r="E315">
-        <v>210</v>
+        <v>187</v>
       </c>
       <c r="F315">
-        <v>4800</v>
+        <v>3250</v>
       </c>
       <c r="G315" t="inlineStr">
         <is>
@@ -10362,7 +10441,7 @@
         </is>
       </c>
       <c r="H315">
-        <v>2008</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="316">
@@ -10377,16 +10456,16 @@
         </is>
       </c>
       <c r="C316">
-        <v>46.9</v>
+        <v>49.8</v>
       </c>
       <c r="D316">
-        <v>16.6</v>
+        <v>17.3</v>
       </c>
       <c r="E316">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="F316">
-        <v>2700</v>
+        <v>3675</v>
       </c>
       <c r="G316" t="inlineStr">
         <is>
@@ -10394,7 +10473,7 @@
         </is>
       </c>
       <c r="H316">
-        <v>2008</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="317">
@@ -10409,24 +10488,24 @@
         </is>
       </c>
       <c r="C317">
-        <v>53.5</v>
+        <v>48.1</v>
       </c>
       <c r="D317">
-        <v>19.9</v>
+        <v>16.4</v>
       </c>
       <c r="E317">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="F317">
-        <v>4500</v>
+        <v>3325</v>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H317">
-        <v>2008</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="318">
@@ -10441,13 +10520,13 @@
         </is>
       </c>
       <c r="C318">
-        <v>49</v>
+        <v>51.4</v>
       </c>
       <c r="D318">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="E318">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="F318">
         <v>3950</v>
@@ -10458,7 +10537,7 @@
         </is>
       </c>
       <c r="H318">
-        <v>2008</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="319">
@@ -10473,16 +10552,16 @@
         </is>
       </c>
       <c r="C319">
-        <v>46.2</v>
+        <v>45.7</v>
       </c>
       <c r="D319">
-        <v>17.5</v>
+        <v>17.3</v>
       </c>
       <c r="E319">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="F319">
-        <v>3650</v>
+        <v>3600</v>
       </c>
       <c r="G319" t="inlineStr">
         <is>
@@ -10490,7 +10569,7 @@
         </is>
       </c>
       <c r="H319">
-        <v>2008</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="320">
@@ -10505,16 +10584,16 @@
         </is>
       </c>
       <c r="C320">
-        <v>50.9</v>
+        <v>50.7</v>
       </c>
       <c r="D320">
-        <v>19.1</v>
+        <v>19.7</v>
       </c>
       <c r="E320">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="F320">
-        <v>3550</v>
+        <v>4050</v>
       </c>
       <c r="G320" t="inlineStr">
         <is>
@@ -10522,7 +10601,7 @@
         </is>
       </c>
       <c r="H320">
-        <v>2008</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="321">
@@ -10537,16 +10616,16 @@
         </is>
       </c>
       <c r="C321">
-        <v>45.5</v>
+        <v>42.5</v>
       </c>
       <c r="D321">
-        <v>17</v>
+        <v>17.3</v>
       </c>
       <c r="E321">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="F321">
-        <v>3500</v>
+        <v>3350</v>
       </c>
       <c r="G321" t="inlineStr">
         <is>
@@ -10554,7 +10633,7 @@
         </is>
       </c>
       <c r="H321">
-        <v>2008</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="322">
@@ -10569,20 +10648,20 @@
         </is>
       </c>
       <c r="C322">
-        <v>50.9</v>
+        <v>52.2</v>
       </c>
       <c r="D322">
-        <v>17.9</v>
+        <v>18.8</v>
       </c>
       <c r="E322">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F322">
-        <v>3675</v>
+        <v>3450</v>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H322">
@@ -10601,20 +10680,20 @@
         </is>
       </c>
       <c r="C323">
-        <v>50.8</v>
+        <v>45.2</v>
       </c>
       <c r="D323">
-        <v>18.5</v>
+        <v>16.6</v>
       </c>
       <c r="E323">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="F323">
-        <v>4450</v>
+        <v>3250</v>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H323">
@@ -10633,20 +10712,20 @@
         </is>
       </c>
       <c r="C324">
-        <v>50.1</v>
+        <v>49.3</v>
       </c>
       <c r="D324">
-        <v>17.9</v>
+        <v>19.9</v>
       </c>
       <c r="E324">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="F324">
-        <v>3400</v>
+        <v>4050</v>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H324">
@@ -10665,16 +10744,16 @@
         </is>
       </c>
       <c r="C325">
-        <v>49</v>
+        <v>50.2</v>
       </c>
       <c r="D325">
-        <v>19.6</v>
+        <v>18.8</v>
       </c>
       <c r="E325">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="F325">
-        <v>4300</v>
+        <v>3800</v>
       </c>
       <c r="G325" t="inlineStr">
         <is>
@@ -10697,20 +10776,20 @@
         </is>
       </c>
       <c r="C326">
-        <v>51.5</v>
+        <v>45.6</v>
       </c>
       <c r="D326">
-        <v>18.7</v>
+        <v>19.4</v>
       </c>
       <c r="E326">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="F326">
-        <v>3250</v>
+        <v>3525</v>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H326">
@@ -10729,20 +10808,20 @@
         </is>
       </c>
       <c r="C327">
-        <v>49.8</v>
+        <v>51.9</v>
       </c>
       <c r="D327">
-        <v>17.3</v>
+        <v>19.5</v>
       </c>
       <c r="E327">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="F327">
-        <v>3675</v>
+        <v>3950</v>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H327">
@@ -10761,16 +10840,16 @@
         </is>
       </c>
       <c r="C328">
-        <v>48.1</v>
+        <v>46.8</v>
       </c>
       <c r="D328">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="E328">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="F328">
-        <v>3325</v>
+        <v>3650</v>
       </c>
       <c r="G328" t="inlineStr">
         <is>
@@ -10793,20 +10872,20 @@
         </is>
       </c>
       <c r="C329">
-        <v>51.4</v>
+        <v>45.7</v>
       </c>
       <c r="D329">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E329">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F329">
-        <v>3950</v>
+        <v>3650</v>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H329">
@@ -10825,20 +10904,20 @@
         </is>
       </c>
       <c r="C330">
-        <v>45.7</v>
+        <v>55.8</v>
       </c>
       <c r="D330">
-        <v>17.3</v>
+        <v>19.8</v>
       </c>
       <c r="E330">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F330">
-        <v>3600</v>
+        <v>4000</v>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H330">
@@ -10857,20 +10936,20 @@
         </is>
       </c>
       <c r="C331">
-        <v>50.7</v>
+        <v>43.5</v>
       </c>
       <c r="D331">
-        <v>19.7</v>
+        <v>18.1</v>
       </c>
       <c r="E331">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F331">
-        <v>4050</v>
+        <v>3400</v>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H331">
@@ -10889,20 +10968,20 @@
         </is>
       </c>
       <c r="C332">
-        <v>42.5</v>
+        <v>49.6</v>
       </c>
       <c r="D332">
-        <v>17.3</v>
+        <v>18.2</v>
       </c>
       <c r="E332">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="F332">
-        <v>3350</v>
+        <v>3775</v>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H332">
@@ -10921,16 +11000,16 @@
         </is>
       </c>
       <c r="C333">
-        <v>52.2</v>
+        <v>50.8</v>
       </c>
       <c r="D333">
-        <v>18.8</v>
+        <v>19</v>
       </c>
       <c r="E333">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="F333">
-        <v>3450</v>
+        <v>4100</v>
       </c>
       <c r="G333" t="inlineStr">
         <is>
@@ -10953,16 +11032,16 @@
         </is>
       </c>
       <c r="C334">
-        <v>45.2</v>
+        <v>50.2</v>
       </c>
       <c r="D334">
-        <v>16.6</v>
+        <v>18.7</v>
       </c>
       <c r="E334">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="F334">
-        <v>3250</v>
+        <v>3775</v>
       </c>
       <c r="G334" t="inlineStr">
         <is>
@@ -10970,358 +11049,6 @@
         </is>
       </c>
       <c r="H334">
-        <v>2009</v>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" t="inlineStr">
-        <is>
-          <t>Chinstrap</t>
-        </is>
-      </c>
-      <c r="B335" t="inlineStr">
-        <is>
-          <t>Dream</t>
-        </is>
-      </c>
-      <c r="C335">
-        <v>49.3</v>
-      </c>
-      <c r="D335">
-        <v>19.9</v>
-      </c>
-      <c r="E335">
-        <v>203</v>
-      </c>
-      <c r="F335">
-        <v>4050</v>
-      </c>
-      <c r="G335" t="inlineStr">
-        <is>
-          <t>male</t>
-        </is>
-      </c>
-      <c r="H335">
-        <v>2009</v>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" t="inlineStr">
-        <is>
-          <t>Chinstrap</t>
-        </is>
-      </c>
-      <c r="B336" t="inlineStr">
-        <is>
-          <t>Dream</t>
-        </is>
-      </c>
-      <c r="C336">
-        <v>50.2</v>
-      </c>
-      <c r="D336">
-        <v>18.8</v>
-      </c>
-      <c r="E336">
-        <v>202</v>
-      </c>
-      <c r="F336">
-        <v>3800</v>
-      </c>
-      <c r="G336" t="inlineStr">
-        <is>
-          <t>male</t>
-        </is>
-      </c>
-      <c r="H336">
-        <v>2009</v>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" t="inlineStr">
-        <is>
-          <t>Chinstrap</t>
-        </is>
-      </c>
-      <c r="B337" t="inlineStr">
-        <is>
-          <t>Dream</t>
-        </is>
-      </c>
-      <c r="C337">
-        <v>45.6</v>
-      </c>
-      <c r="D337">
-        <v>19.4</v>
-      </c>
-      <c r="E337">
-        <v>194</v>
-      </c>
-      <c r="F337">
-        <v>3525</v>
-      </c>
-      <c r="G337" t="inlineStr">
-        <is>
-          <t>female</t>
-        </is>
-      </c>
-      <c r="H337">
-        <v>2009</v>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" t="inlineStr">
-        <is>
-          <t>Chinstrap</t>
-        </is>
-      </c>
-      <c r="B338" t="inlineStr">
-        <is>
-          <t>Dream</t>
-        </is>
-      </c>
-      <c r="C338">
-        <v>51.9</v>
-      </c>
-      <c r="D338">
-        <v>19.5</v>
-      </c>
-      <c r="E338">
-        <v>206</v>
-      </c>
-      <c r="F338">
-        <v>3950</v>
-      </c>
-      <c r="G338" t="inlineStr">
-        <is>
-          <t>male</t>
-        </is>
-      </c>
-      <c r="H338">
-        <v>2009</v>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" t="inlineStr">
-        <is>
-          <t>Chinstrap</t>
-        </is>
-      </c>
-      <c r="B339" t="inlineStr">
-        <is>
-          <t>Dream</t>
-        </is>
-      </c>
-      <c r="C339">
-        <v>46.8</v>
-      </c>
-      <c r="D339">
-        <v>16.5</v>
-      </c>
-      <c r="E339">
-        <v>189</v>
-      </c>
-      <c r="F339">
-        <v>3650</v>
-      </c>
-      <c r="G339" t="inlineStr">
-        <is>
-          <t>female</t>
-        </is>
-      </c>
-      <c r="H339">
-        <v>2009</v>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" t="inlineStr">
-        <is>
-          <t>Chinstrap</t>
-        </is>
-      </c>
-      <c r="B340" t="inlineStr">
-        <is>
-          <t>Dream</t>
-        </is>
-      </c>
-      <c r="C340">
-        <v>45.7</v>
-      </c>
-      <c r="D340">
-        <v>17</v>
-      </c>
-      <c r="E340">
-        <v>195</v>
-      </c>
-      <c r="F340">
-        <v>3650</v>
-      </c>
-      <c r="G340" t="inlineStr">
-        <is>
-          <t>female</t>
-        </is>
-      </c>
-      <c r="H340">
-        <v>2009</v>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341" t="inlineStr">
-        <is>
-          <t>Chinstrap</t>
-        </is>
-      </c>
-      <c r="B341" t="inlineStr">
-        <is>
-          <t>Dream</t>
-        </is>
-      </c>
-      <c r="C341">
-        <v>55.8</v>
-      </c>
-      <c r="D341">
-        <v>19.8</v>
-      </c>
-      <c r="E341">
-        <v>207</v>
-      </c>
-      <c r="F341">
-        <v>4000</v>
-      </c>
-      <c r="G341" t="inlineStr">
-        <is>
-          <t>male</t>
-        </is>
-      </c>
-      <c r="H341">
-        <v>2009</v>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" t="inlineStr">
-        <is>
-          <t>Chinstrap</t>
-        </is>
-      </c>
-      <c r="B342" t="inlineStr">
-        <is>
-          <t>Dream</t>
-        </is>
-      </c>
-      <c r="C342">
-        <v>43.5</v>
-      </c>
-      <c r="D342">
-        <v>18.1</v>
-      </c>
-      <c r="E342">
-        <v>202</v>
-      </c>
-      <c r="F342">
-        <v>3400</v>
-      </c>
-      <c r="G342" t="inlineStr">
-        <is>
-          <t>female</t>
-        </is>
-      </c>
-      <c r="H342">
-        <v>2009</v>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" t="inlineStr">
-        <is>
-          <t>Chinstrap</t>
-        </is>
-      </c>
-      <c r="B343" t="inlineStr">
-        <is>
-          <t>Dream</t>
-        </is>
-      </c>
-      <c r="C343">
-        <v>49.6</v>
-      </c>
-      <c r="D343">
-        <v>18.2</v>
-      </c>
-      <c r="E343">
-        <v>193</v>
-      </c>
-      <c r="F343">
-        <v>3775</v>
-      </c>
-      <c r="G343" t="inlineStr">
-        <is>
-          <t>male</t>
-        </is>
-      </c>
-      <c r="H343">
-        <v>2009</v>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" t="inlineStr">
-        <is>
-          <t>Chinstrap</t>
-        </is>
-      </c>
-      <c r="B344" t="inlineStr">
-        <is>
-          <t>Dream</t>
-        </is>
-      </c>
-      <c r="C344">
-        <v>50.8</v>
-      </c>
-      <c r="D344">
-        <v>19</v>
-      </c>
-      <c r="E344">
-        <v>210</v>
-      </c>
-      <c r="F344">
-        <v>4100</v>
-      </c>
-      <c r="G344" t="inlineStr">
-        <is>
-          <t>male</t>
-        </is>
-      </c>
-      <c r="H344">
-        <v>2009</v>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" t="inlineStr">
-        <is>
-          <t>Chinstrap</t>
-        </is>
-      </c>
-      <c r="B345" t="inlineStr">
-        <is>
-          <t>Dream</t>
-        </is>
-      </c>
-      <c r="C345">
-        <v>50.2</v>
-      </c>
-      <c r="D345">
-        <v>18.7</v>
-      </c>
-      <c r="E345">
-        <v>198</v>
-      </c>
-      <c r="F345">
-        <v>3775</v>
-      </c>
-      <c r="G345" t="inlineStr">
-        <is>
-          <t>female</t>
-        </is>
-      </c>
-      <c r="H345">
         <v>2009</v>
       </c>
     </row>

--- a/DTS_204_Dataset.xlsx
+++ b/DTS_204_Dataset.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H334"/>
+  <dimension ref="A1:H345"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -503,23 +503,6 @@
           <t>Torgersen</t>
         </is>
       </c>
-      <c r="C5">
-        <v>36.7</v>
-      </c>
-      <c r="D5">
-        <v>19.3</v>
-      </c>
-      <c r="E5">
-        <v>193</v>
-      </c>
-      <c r="F5">
-        <v>3450</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>female</t>
-        </is>
-      </c>
       <c r="H5">
         <v>2007</v>
       </c>
@@ -536,20 +519,20 @@
         </is>
       </c>
       <c r="C6">
-        <v>39.3</v>
+        <v>36.7</v>
       </c>
       <c r="D6">
-        <v>20.6</v>
+        <v>19.3</v>
       </c>
       <c r="E6">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="F6">
-        <v>3650</v>
+        <v>3450</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H6">
@@ -568,20 +551,20 @@
         </is>
       </c>
       <c r="C7">
-        <v>38.9</v>
+        <v>39.3</v>
       </c>
       <c r="D7">
-        <v>17.8</v>
+        <v>20.6</v>
       </c>
       <c r="E7">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="F7">
-        <v>3625</v>
+        <v>3650</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H7">
@@ -600,20 +583,20 @@
         </is>
       </c>
       <c r="C8">
-        <v>39.2</v>
+        <v>38.9</v>
       </c>
       <c r="D8">
-        <v>19.6</v>
+        <v>17.8</v>
       </c>
       <c r="E8">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="F8">
-        <v>4675</v>
+        <v>3625</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H8">
@@ -632,20 +615,20 @@
         </is>
       </c>
       <c r="C9">
-        <v>41.1</v>
+        <v>39.2</v>
       </c>
       <c r="D9">
-        <v>17.6</v>
+        <v>19.6</v>
       </c>
       <c r="E9">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="F9">
-        <v>3200</v>
+        <v>4675</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H9">
@@ -664,21 +647,16 @@
         </is>
       </c>
       <c r="C10">
-        <v>38.6</v>
+        <v>34.1</v>
       </c>
       <c r="D10">
-        <v>21.2</v>
+        <v>18.1</v>
       </c>
       <c r="E10">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F10">
-        <v>3800</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>male</t>
-        </is>
+        <v>3475</v>
       </c>
       <c r="H10">
         <v>2007</v>
@@ -696,21 +674,16 @@
         </is>
       </c>
       <c r="C11">
-        <v>34.6</v>
+        <v>42</v>
       </c>
       <c r="D11">
-        <v>21.1</v>
+        <v>20.2</v>
       </c>
       <c r="E11">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="F11">
-        <v>4400</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>male</t>
-        </is>
+        <v>4250</v>
       </c>
       <c r="H11">
         <v>2007</v>
@@ -728,21 +701,16 @@
         </is>
       </c>
       <c r="C12">
-        <v>36.6</v>
+        <v>37.8</v>
       </c>
       <c r="D12">
-        <v>17.8</v>
+        <v>17.1</v>
       </c>
       <c r="E12">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F12">
-        <v>3700</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>female</t>
-        </is>
+        <v>3300</v>
       </c>
       <c r="H12">
         <v>2007</v>
@@ -760,21 +728,16 @@
         </is>
       </c>
       <c r="C13">
-        <v>38.7</v>
+        <v>37.8</v>
       </c>
       <c r="D13">
-        <v>19</v>
+        <v>17.3</v>
       </c>
       <c r="E13">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="F13">
-        <v>3450</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>female</t>
-        </is>
+        <v>3700</v>
       </c>
       <c r="H13">
         <v>2007</v>
@@ -792,20 +755,20 @@
         </is>
       </c>
       <c r="C14">
-        <v>42.5</v>
+        <v>41.1</v>
       </c>
       <c r="D14">
-        <v>20.7</v>
+        <v>17.6</v>
       </c>
       <c r="E14">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="F14">
-        <v>4500</v>
+        <v>3200</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H14">
@@ -824,20 +787,20 @@
         </is>
       </c>
       <c r="C15">
-        <v>34.4</v>
+        <v>38.6</v>
       </c>
       <c r="D15">
-        <v>18.4</v>
+        <v>21.2</v>
       </c>
       <c r="E15">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="F15">
-        <v>3325</v>
+        <v>3800</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H15">
@@ -856,16 +819,16 @@
         </is>
       </c>
       <c r="C16">
-        <v>46</v>
+        <v>34.6</v>
       </c>
       <c r="D16">
-        <v>21.5</v>
+        <v>21.1</v>
       </c>
       <c r="E16">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="F16">
-        <v>4200</v>
+        <v>4400</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -884,20 +847,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Biscoe</t>
+          <t>Torgersen</t>
         </is>
       </c>
       <c r="C17">
-        <v>37.8</v>
+        <v>36.6</v>
       </c>
       <c r="D17">
-        <v>18.3</v>
+        <v>17.8</v>
       </c>
       <c r="E17">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="F17">
-        <v>3400</v>
+        <v>3700</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -916,24 +879,24 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Biscoe</t>
+          <t>Torgersen</t>
         </is>
       </c>
       <c r="C18">
-        <v>37.7</v>
+        <v>38.7</v>
       </c>
       <c r="D18">
-        <v>18.7</v>
+        <v>19</v>
       </c>
       <c r="E18">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="F18">
-        <v>3600</v>
+        <v>3450</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H18">
@@ -948,24 +911,24 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Biscoe</t>
+          <t>Torgersen</t>
         </is>
       </c>
       <c r="C19">
-        <v>35.9</v>
+        <v>42.5</v>
       </c>
       <c r="D19">
-        <v>19.2</v>
+        <v>20.7</v>
       </c>
       <c r="E19">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="F19">
-        <v>3800</v>
+        <v>4500</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H19">
@@ -980,24 +943,24 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Biscoe</t>
+          <t>Torgersen</t>
         </is>
       </c>
       <c r="C20">
-        <v>38.2</v>
+        <v>34.4</v>
       </c>
       <c r="D20">
-        <v>18.1</v>
+        <v>18.4</v>
       </c>
       <c r="E20">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F20">
-        <v>3950</v>
+        <v>3325</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H20">
@@ -1012,20 +975,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Biscoe</t>
+          <t>Torgersen</t>
         </is>
       </c>
       <c r="C21">
-        <v>38.8</v>
+        <v>46</v>
       </c>
       <c r="D21">
-        <v>17.2</v>
+        <v>21.5</v>
       </c>
       <c r="E21">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="F21">
-        <v>3800</v>
+        <v>4200</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1048,16 +1011,16 @@
         </is>
       </c>
       <c r="C22">
-        <v>35.3</v>
+        <v>37.8</v>
       </c>
       <c r="D22">
-        <v>18.9</v>
+        <v>18.3</v>
       </c>
       <c r="E22">
-        <v>187</v>
+        <v>174</v>
       </c>
       <c r="F22">
-        <v>3800</v>
+        <v>3400</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1080,16 +1043,16 @@
         </is>
       </c>
       <c r="C23">
-        <v>40.6</v>
+        <v>37.7</v>
       </c>
       <c r="D23">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="E23">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F23">
-        <v>3550</v>
+        <v>3600</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1112,16 +1075,16 @@
         </is>
       </c>
       <c r="C24">
-        <v>40.5</v>
+        <v>35.9</v>
       </c>
       <c r="D24">
-        <v>17.9</v>
+        <v>19.2</v>
       </c>
       <c r="E24">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F24">
-        <v>3200</v>
+        <v>3800</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1144,20 +1107,20 @@
         </is>
       </c>
       <c r="C25">
-        <v>37.9</v>
+        <v>38.2</v>
       </c>
       <c r="D25">
-        <v>18.6</v>
+        <v>18.1</v>
       </c>
       <c r="E25">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="F25">
-        <v>3150</v>
+        <v>3950</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H25">
@@ -1176,16 +1139,16 @@
         </is>
       </c>
       <c r="C26">
-        <v>40.5</v>
+        <v>38.8</v>
       </c>
       <c r="D26">
-        <v>18.9</v>
+        <v>17.2</v>
       </c>
       <c r="E26">
         <v>180</v>
       </c>
       <c r="F26">
-        <v>3950</v>
+        <v>3800</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1204,20 +1167,20 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Dream</t>
+          <t>Biscoe</t>
         </is>
       </c>
       <c r="C27">
-        <v>39.5</v>
+        <v>35.3</v>
       </c>
       <c r="D27">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
       <c r="E27">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="F27">
-        <v>3250</v>
+        <v>3800</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1236,20 +1199,20 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Dream</t>
+          <t>Biscoe</t>
         </is>
       </c>
       <c r="C28">
-        <v>37.2</v>
+        <v>40.6</v>
       </c>
       <c r="D28">
-        <v>18.1</v>
+        <v>18.6</v>
       </c>
       <c r="E28">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="F28">
-        <v>3900</v>
+        <v>3550</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1268,20 +1231,20 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Dream</t>
+          <t>Biscoe</t>
         </is>
       </c>
       <c r="C29">
-        <v>39.5</v>
+        <v>40.5</v>
       </c>
       <c r="D29">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="E29">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F29">
-        <v>3300</v>
+        <v>3200</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1300,24 +1263,24 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Dream</t>
+          <t>Biscoe</t>
         </is>
       </c>
       <c r="C30">
-        <v>40.9</v>
+        <v>37.9</v>
       </c>
       <c r="D30">
-        <v>18.9</v>
+        <v>18.6</v>
       </c>
       <c r="E30">
-        <v>184</v>
+        <v>172</v>
       </c>
       <c r="F30">
-        <v>3900</v>
+        <v>3150</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H30">
@@ -1332,24 +1295,24 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Dream</t>
+          <t>Biscoe</t>
         </is>
       </c>
       <c r="C31">
-        <v>36.4</v>
+        <v>40.5</v>
       </c>
       <c r="D31">
-        <v>17</v>
+        <v>18.9</v>
       </c>
       <c r="E31">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="F31">
-        <v>3325</v>
+        <v>3950</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H31">
@@ -1368,20 +1331,20 @@
         </is>
       </c>
       <c r="C32">
-        <v>39.2</v>
+        <v>39.5</v>
       </c>
       <c r="D32">
-        <v>21.1</v>
+        <v>16.7</v>
       </c>
       <c r="E32">
-        <v>196</v>
+        <v>178</v>
       </c>
       <c r="F32">
-        <v>4150</v>
+        <v>3250</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H32">
@@ -1400,16 +1363,16 @@
         </is>
       </c>
       <c r="C33">
-        <v>38.8</v>
+        <v>37.2</v>
       </c>
       <c r="D33">
-        <v>20</v>
+        <v>18.1</v>
       </c>
       <c r="E33">
-        <v>190</v>
+        <v>178</v>
       </c>
       <c r="F33">
-        <v>3950</v>
+        <v>3900</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1432,16 +1395,16 @@
         </is>
       </c>
       <c r="C34">
-        <v>42.2</v>
+        <v>39.5</v>
       </c>
       <c r="D34">
-        <v>18.5</v>
+        <v>17.8</v>
       </c>
       <c r="E34">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="F34">
-        <v>3550</v>
+        <v>3300</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1464,20 +1427,20 @@
         </is>
       </c>
       <c r="C35">
-        <v>37.6</v>
+        <v>40.9</v>
       </c>
       <c r="D35">
-        <v>19.3</v>
+        <v>18.9</v>
       </c>
       <c r="E35">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F35">
-        <v>3300</v>
+        <v>3900</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H35">
@@ -1496,20 +1459,20 @@
         </is>
       </c>
       <c r="C36">
-        <v>39.8</v>
+        <v>36.4</v>
       </c>
       <c r="D36">
-        <v>19.1</v>
+        <v>17</v>
       </c>
       <c r="E36">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="F36">
-        <v>4650</v>
+        <v>3325</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H36">
@@ -1528,20 +1491,20 @@
         </is>
       </c>
       <c r="C37">
-        <v>36.5</v>
+        <v>39.2</v>
       </c>
       <c r="D37">
-        <v>18</v>
+        <v>21.1</v>
       </c>
       <c r="E37">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="F37">
-        <v>3150</v>
+        <v>4150</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H37">
@@ -1560,16 +1523,16 @@
         </is>
       </c>
       <c r="C38">
-        <v>40.8</v>
+        <v>38.8</v>
       </c>
       <c r="D38">
-        <v>18.4</v>
+        <v>20</v>
       </c>
       <c r="E38">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="F38">
-        <v>3900</v>
+        <v>3950</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1592,16 +1555,16 @@
         </is>
       </c>
       <c r="C39">
-        <v>36</v>
+        <v>42.2</v>
       </c>
       <c r="D39">
         <v>18.5</v>
       </c>
       <c r="E39">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="F39">
-        <v>3100</v>
+        <v>3550</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1624,20 +1587,20 @@
         </is>
       </c>
       <c r="C40">
-        <v>44.1</v>
+        <v>37.6</v>
       </c>
       <c r="D40">
-        <v>19.7</v>
+        <v>19.3</v>
       </c>
       <c r="E40">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="F40">
-        <v>4400</v>
+        <v>3300</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H40">
@@ -1656,20 +1619,20 @@
         </is>
       </c>
       <c r="C41">
-        <v>37</v>
+        <v>39.8</v>
       </c>
       <c r="D41">
-        <v>16.9</v>
+        <v>19.1</v>
       </c>
       <c r="E41">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F41">
-        <v>3000</v>
+        <v>4650</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H41">
@@ -1688,20 +1651,20 @@
         </is>
       </c>
       <c r="C42">
-        <v>39.6</v>
+        <v>36.5</v>
       </c>
       <c r="D42">
-        <v>18.8</v>
+        <v>18</v>
       </c>
       <c r="E42">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="F42">
-        <v>4600</v>
+        <v>3150</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H42">
@@ -1720,16 +1683,16 @@
         </is>
       </c>
       <c r="C43">
-        <v>41.1</v>
+        <v>40.8</v>
       </c>
       <c r="D43">
-        <v>19</v>
+        <v>18.4</v>
       </c>
       <c r="E43">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="F43">
-        <v>3425</v>
+        <v>3900</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1755,13 +1718,13 @@
         <v>36</v>
       </c>
       <c r="D44">
-        <v>17.9</v>
+        <v>18.5</v>
       </c>
       <c r="E44">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F44">
-        <v>3450</v>
+        <v>3100</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1784,16 +1747,16 @@
         </is>
       </c>
       <c r="C45">
-        <v>42.3</v>
+        <v>44.1</v>
       </c>
       <c r="D45">
-        <v>21.2</v>
+        <v>19.7</v>
       </c>
       <c r="E45">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="F45">
-        <v>4150</v>
+        <v>4400</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1812,20 +1775,20 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Biscoe</t>
+          <t>Dream</t>
         </is>
       </c>
       <c r="C46">
-        <v>39.6</v>
+        <v>37</v>
       </c>
       <c r="D46">
-        <v>17.7</v>
+        <v>16.9</v>
       </c>
       <c r="E46">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F46">
-        <v>3500</v>
+        <v>3000</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -1833,7 +1796,7 @@
         </is>
       </c>
       <c r="H46">
-        <v>2008</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="47">
@@ -1844,20 +1807,20 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Biscoe</t>
+          <t>Dream</t>
         </is>
       </c>
       <c r="C47">
-        <v>40.1</v>
+        <v>39.6</v>
       </c>
       <c r="D47">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="E47">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F47">
-        <v>4300</v>
+        <v>4600</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -1865,7 +1828,7 @@
         </is>
       </c>
       <c r="H47">
-        <v>2008</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="48">
@@ -1876,28 +1839,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Biscoe</t>
+          <t>Dream</t>
         </is>
       </c>
       <c r="C48">
-        <v>35</v>
+        <v>41.1</v>
       </c>
       <c r="D48">
-        <v>17.9</v>
+        <v>19</v>
       </c>
       <c r="E48">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="F48">
-        <v>3450</v>
+        <v>3425</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H48">
-        <v>2008</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="49">
@@ -1908,28 +1871,23 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Biscoe</t>
+          <t>Dream</t>
         </is>
       </c>
       <c r="C49">
-        <v>42</v>
+        <v>37.5</v>
       </c>
       <c r="D49">
-        <v>19.5</v>
+        <v>18.9</v>
       </c>
       <c r="E49">
-        <v>200</v>
+        <v>179</v>
       </c>
       <c r="F49">
-        <v>4050</v>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>male</t>
-        </is>
+        <v>2975</v>
       </c>
       <c r="H49">
-        <v>2008</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="50">
@@ -1940,20 +1898,20 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Biscoe</t>
+          <t>Dream</t>
         </is>
       </c>
       <c r="C50">
-        <v>34.5</v>
+        <v>36</v>
       </c>
       <c r="D50">
-        <v>18.1</v>
+        <v>17.9</v>
       </c>
       <c r="E50">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F50">
-        <v>2900</v>
+        <v>3450</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -1961,7 +1919,7 @@
         </is>
       </c>
       <c r="H50">
-        <v>2008</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="51">
@@ -1972,20 +1930,20 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Biscoe</t>
+          <t>Dream</t>
         </is>
       </c>
       <c r="C51">
-        <v>41.4</v>
+        <v>42.3</v>
       </c>
       <c r="D51">
-        <v>18.6</v>
+        <v>21.2</v>
       </c>
       <c r="E51">
         <v>191</v>
       </c>
       <c r="F51">
-        <v>3700</v>
+        <v>4150</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -1993,7 +1951,7 @@
         </is>
       </c>
       <c r="H51">
-        <v>2008</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="52">
@@ -2008,16 +1966,16 @@
         </is>
       </c>
       <c r="C52">
-        <v>39</v>
+        <v>39.6</v>
       </c>
       <c r="D52">
-        <v>17.5</v>
+        <v>17.7</v>
       </c>
       <c r="E52">
         <v>186</v>
       </c>
       <c r="F52">
-        <v>3550</v>
+        <v>3500</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2040,16 +1998,16 @@
         </is>
       </c>
       <c r="C53">
-        <v>40.6</v>
+        <v>40.1</v>
       </c>
       <c r="D53">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="E53">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="F53">
-        <v>3800</v>
+        <v>4300</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2072,16 +2030,16 @@
         </is>
       </c>
       <c r="C54">
-        <v>36.5</v>
+        <v>35</v>
       </c>
       <c r="D54">
-        <v>16.6</v>
+        <v>17.9</v>
       </c>
       <c r="E54">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="F54">
-        <v>2850</v>
+        <v>3450</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2104,16 +2062,16 @@
         </is>
       </c>
       <c r="C55">
-        <v>37.6</v>
+        <v>42</v>
       </c>
       <c r="D55">
-        <v>19.1</v>
+        <v>19.5</v>
       </c>
       <c r="E55">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="F55">
-        <v>3750</v>
+        <v>4050</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2136,16 +2094,16 @@
         </is>
       </c>
       <c r="C56">
-        <v>35.7</v>
+        <v>34.5</v>
       </c>
       <c r="D56">
-        <v>16.9</v>
+        <v>18.1</v>
       </c>
       <c r="E56">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F56">
-        <v>3150</v>
+        <v>2900</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2168,16 +2126,16 @@
         </is>
       </c>
       <c r="C57">
-        <v>41.3</v>
+        <v>41.4</v>
       </c>
       <c r="D57">
-        <v>21.1</v>
+        <v>18.6</v>
       </c>
       <c r="E57">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="F57">
-        <v>4400</v>
+        <v>3700</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2200,16 +2158,16 @@
         </is>
       </c>
       <c r="C58">
-        <v>37.6</v>
+        <v>39</v>
       </c>
       <c r="D58">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="E58">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F58">
-        <v>3600</v>
+        <v>3550</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2232,16 +2190,16 @@
         </is>
       </c>
       <c r="C59">
-        <v>41.1</v>
+        <v>40.6</v>
       </c>
       <c r="D59">
-        <v>18.2</v>
+        <v>18.8</v>
       </c>
       <c r="E59">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="F59">
-        <v>4050</v>
+        <v>3800</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2264,13 +2222,13 @@
         </is>
       </c>
       <c r="C60">
-        <v>36.4</v>
+        <v>36.5</v>
       </c>
       <c r="D60">
-        <v>17.1</v>
+        <v>16.6</v>
       </c>
       <c r="E60">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="F60">
         <v>2850</v>
@@ -2296,16 +2254,16 @@
         </is>
       </c>
       <c r="C61">
-        <v>41.6</v>
+        <v>37.6</v>
       </c>
       <c r="D61">
-        <v>18</v>
+        <v>19.1</v>
       </c>
       <c r="E61">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F61">
-        <v>3950</v>
+        <v>3750</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2328,16 +2286,16 @@
         </is>
       </c>
       <c r="C62">
-        <v>35.5</v>
+        <v>35.7</v>
       </c>
       <c r="D62">
-        <v>16.2</v>
+        <v>16.9</v>
       </c>
       <c r="E62">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="F62">
-        <v>3350</v>
+        <v>3150</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -2360,16 +2318,16 @@
         </is>
       </c>
       <c r="C63">
-        <v>41.1</v>
+        <v>41.3</v>
       </c>
       <c r="D63">
-        <v>19.1</v>
+        <v>21.1</v>
       </c>
       <c r="E63">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="F63">
-        <v>4100</v>
+        <v>4400</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2388,20 +2346,20 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Torgersen</t>
+          <t>Biscoe</t>
         </is>
       </c>
       <c r="C64">
-        <v>35.9</v>
+        <v>37.6</v>
       </c>
       <c r="D64">
-        <v>16.6</v>
+        <v>17</v>
       </c>
       <c r="E64">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="F64">
-        <v>3050</v>
+        <v>3600</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -2420,20 +2378,20 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Torgersen</t>
+          <t>Biscoe</t>
         </is>
       </c>
       <c r="C65">
-        <v>41.8</v>
+        <v>41.1</v>
       </c>
       <c r="D65">
-        <v>19.4</v>
+        <v>18.2</v>
       </c>
       <c r="E65">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="F65">
-        <v>4450</v>
+        <v>4050</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -2452,20 +2410,20 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Torgersen</t>
+          <t>Biscoe</t>
         </is>
       </c>
       <c r="C66">
-        <v>33.5</v>
+        <v>36.4</v>
       </c>
       <c r="D66">
-        <v>19</v>
+        <v>17.1</v>
       </c>
       <c r="E66">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="F66">
-        <v>3600</v>
+        <v>2850</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -2484,20 +2442,20 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Torgersen</t>
+          <t>Biscoe</t>
         </is>
       </c>
       <c r="C67">
-        <v>39.7</v>
+        <v>41.6</v>
       </c>
       <c r="D67">
-        <v>18.4</v>
+        <v>18</v>
       </c>
       <c r="E67">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F67">
-        <v>3900</v>
+        <v>3950</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -2516,20 +2474,20 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Torgersen</t>
+          <t>Biscoe</t>
         </is>
       </c>
       <c r="C68">
-        <v>39.6</v>
+        <v>35.5</v>
       </c>
       <c r="D68">
-        <v>17.2</v>
+        <v>16.2</v>
       </c>
       <c r="E68">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F68">
-        <v>3550</v>
+        <v>3350</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -2548,20 +2506,20 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Torgersen</t>
+          <t>Biscoe</t>
         </is>
       </c>
       <c r="C69">
-        <v>45.8</v>
+        <v>41.1</v>
       </c>
       <c r="D69">
-        <v>18.9</v>
+        <v>19.1</v>
       </c>
       <c r="E69">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="F69">
-        <v>4150</v>
+        <v>4100</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -2584,16 +2542,16 @@
         </is>
       </c>
       <c r="C70">
-        <v>35.5</v>
+        <v>35.9</v>
       </c>
       <c r="D70">
-        <v>17.5</v>
+        <v>16.6</v>
       </c>
       <c r="E70">
         <v>190</v>
       </c>
       <c r="F70">
-        <v>3700</v>
+        <v>3050</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -2616,16 +2574,16 @@
         </is>
       </c>
       <c r="C71">
-        <v>42.8</v>
+        <v>41.8</v>
       </c>
       <c r="D71">
-        <v>18.5</v>
+        <v>19.4</v>
       </c>
       <c r="E71">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F71">
-        <v>4250</v>
+        <v>4450</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -2648,16 +2606,16 @@
         </is>
       </c>
       <c r="C72">
-        <v>40.9</v>
+        <v>33.5</v>
       </c>
       <c r="D72">
-        <v>16.8</v>
+        <v>19</v>
       </c>
       <c r="E72">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F72">
-        <v>3700</v>
+        <v>3600</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -2680,13 +2638,13 @@
         </is>
       </c>
       <c r="C73">
-        <v>37.2</v>
+        <v>39.7</v>
       </c>
       <c r="D73">
-        <v>19.4</v>
+        <v>18.4</v>
       </c>
       <c r="E73">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="F73">
         <v>3900</v>
@@ -2712,13 +2670,13 @@
         </is>
       </c>
       <c r="C74">
-        <v>36.2</v>
+        <v>39.6</v>
       </c>
       <c r="D74">
-        <v>16.1</v>
+        <v>17.2</v>
       </c>
       <c r="E74">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="F74">
         <v>3550</v>
@@ -2744,16 +2702,16 @@
         </is>
       </c>
       <c r="C75">
-        <v>42.1</v>
+        <v>45.8</v>
       </c>
       <c r="D75">
-        <v>19.1</v>
+        <v>18.9</v>
       </c>
       <c r="E75">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F75">
-        <v>4000</v>
+        <v>4150</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -2776,16 +2734,16 @@
         </is>
       </c>
       <c r="C76">
-        <v>34.6</v>
+        <v>35.5</v>
       </c>
       <c r="D76">
-        <v>17.2</v>
+        <v>17.5</v>
       </c>
       <c r="E76">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F76">
-        <v>3200</v>
+        <v>3700</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -2808,16 +2766,16 @@
         </is>
       </c>
       <c r="C77">
-        <v>42.9</v>
+        <v>42.8</v>
       </c>
       <c r="D77">
-        <v>17.6</v>
+        <v>18.5</v>
       </c>
       <c r="E77">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F77">
-        <v>4700</v>
+        <v>4250</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -2840,16 +2798,16 @@
         </is>
       </c>
       <c r="C78">
-        <v>36.7</v>
+        <v>40.9</v>
       </c>
       <c r="D78">
-        <v>18.8</v>
+        <v>16.8</v>
       </c>
       <c r="E78">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="F78">
-        <v>3800</v>
+        <v>3700</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -2872,16 +2830,16 @@
         </is>
       </c>
       <c r="C79">
-        <v>35.1</v>
+        <v>37.2</v>
       </c>
       <c r="D79">
         <v>19.4</v>
       </c>
       <c r="E79">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="F79">
-        <v>4200</v>
+        <v>3900</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -2900,20 +2858,20 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Dream</t>
+          <t>Torgersen</t>
         </is>
       </c>
       <c r="C80">
-        <v>37.3</v>
+        <v>36.2</v>
       </c>
       <c r="D80">
-        <v>17.8</v>
+        <v>16.1</v>
       </c>
       <c r="E80">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="F80">
-        <v>3350</v>
+        <v>3550</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -2932,20 +2890,20 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Dream</t>
+          <t>Torgersen</t>
         </is>
       </c>
       <c r="C81">
-        <v>41.3</v>
+        <v>42.1</v>
       </c>
       <c r="D81">
-        <v>20.3</v>
+        <v>19.1</v>
       </c>
       <c r="E81">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F81">
-        <v>3550</v>
+        <v>4000</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -2964,24 +2922,24 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Dream</t>
+          <t>Torgersen</t>
         </is>
       </c>
       <c r="C82">
-        <v>36.3</v>
+        <v>34.6</v>
       </c>
       <c r="D82">
-        <v>19.5</v>
+        <v>17.2</v>
       </c>
       <c r="E82">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F82">
-        <v>3800</v>
+        <v>3200</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H82">
@@ -2996,24 +2954,24 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Dream</t>
+          <t>Torgersen</t>
         </is>
       </c>
       <c r="C83">
-        <v>36.9</v>
+        <v>42.9</v>
       </c>
       <c r="D83">
-        <v>18.6</v>
+        <v>17.6</v>
       </c>
       <c r="E83">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="F83">
-        <v>3500</v>
+        <v>4700</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H83">
@@ -3028,24 +2986,24 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Dream</t>
+          <t>Torgersen</t>
         </is>
       </c>
       <c r="C84">
-        <v>38.3</v>
+        <v>36.7</v>
       </c>
       <c r="D84">
-        <v>19.2</v>
+        <v>18.8</v>
       </c>
       <c r="E84">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F84">
-        <v>3950</v>
+        <v>3800</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H84">
@@ -3060,24 +3018,24 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Dream</t>
+          <t>Torgersen</t>
         </is>
       </c>
       <c r="C85">
-        <v>38.9</v>
+        <v>35.1</v>
       </c>
       <c r="D85">
-        <v>18.8</v>
+        <v>19.4</v>
       </c>
       <c r="E85">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="F85">
-        <v>3600</v>
+        <v>4200</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H85">
@@ -3096,16 +3054,16 @@
         </is>
       </c>
       <c r="C86">
-        <v>35.7</v>
+        <v>37.3</v>
       </c>
       <c r="D86">
-        <v>18</v>
+        <v>17.8</v>
       </c>
       <c r="E86">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="F86">
-        <v>3550</v>
+        <v>3350</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -3128,16 +3086,16 @@
         </is>
       </c>
       <c r="C87">
-        <v>41.1</v>
+        <v>41.3</v>
       </c>
       <c r="D87">
-        <v>18.1</v>
+        <v>20.3</v>
       </c>
       <c r="E87">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="F87">
-        <v>4300</v>
+        <v>3550</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -3160,20 +3118,20 @@
         </is>
       </c>
       <c r="C88">
-        <v>34</v>
+        <v>36.3</v>
       </c>
       <c r="D88">
-        <v>17.1</v>
+        <v>19.5</v>
       </c>
       <c r="E88">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="F88">
-        <v>3400</v>
+        <v>3800</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H88">
@@ -3192,20 +3150,20 @@
         </is>
       </c>
       <c r="C89">
-        <v>39.6</v>
+        <v>36.9</v>
       </c>
       <c r="D89">
-        <v>18.1</v>
+        <v>18.6</v>
       </c>
       <c r="E89">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="F89">
-        <v>4450</v>
+        <v>3500</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H89">
@@ -3224,20 +3182,20 @@
         </is>
       </c>
       <c r="C90">
-        <v>36.2</v>
+        <v>38.3</v>
       </c>
       <c r="D90">
-        <v>17.3</v>
+        <v>19.2</v>
       </c>
       <c r="E90">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F90">
-        <v>3300</v>
+        <v>3950</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H90">
@@ -3256,20 +3214,20 @@
         </is>
       </c>
       <c r="C91">
-        <v>40.8</v>
+        <v>38.9</v>
       </c>
       <c r="D91">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="E91">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="F91">
-        <v>4300</v>
+        <v>3600</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H91">
@@ -3288,16 +3246,16 @@
         </is>
       </c>
       <c r="C92">
-        <v>38.1</v>
+        <v>35.7</v>
       </c>
       <c r="D92">
-        <v>18.6</v>
+        <v>18</v>
       </c>
       <c r="E92">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="F92">
-        <v>3700</v>
+        <v>3550</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -3320,16 +3278,16 @@
         </is>
       </c>
       <c r="C93">
-        <v>40.3</v>
+        <v>41.1</v>
       </c>
       <c r="D93">
-        <v>18.5</v>
+        <v>18.1</v>
       </c>
       <c r="E93">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="F93">
-        <v>4350</v>
+        <v>4300</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -3352,16 +3310,16 @@
         </is>
       </c>
       <c r="C94">
-        <v>33.1</v>
+        <v>34</v>
       </c>
       <c r="D94">
-        <v>16.1</v>
+        <v>17.1</v>
       </c>
       <c r="E94">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="F94">
-        <v>2900</v>
+        <v>3400</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -3384,16 +3342,16 @@
         </is>
       </c>
       <c r="C95">
-        <v>43.2</v>
+        <v>39.6</v>
       </c>
       <c r="D95">
-        <v>18.5</v>
+        <v>18.1</v>
       </c>
       <c r="E95">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="F95">
-        <v>4100</v>
+        <v>4450</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -3412,20 +3370,20 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Biscoe</t>
+          <t>Dream</t>
         </is>
       </c>
       <c r="C96">
-        <v>35</v>
+        <v>36.2</v>
       </c>
       <c r="D96">
-        <v>17.9</v>
+        <v>17.3</v>
       </c>
       <c r="E96">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="F96">
-        <v>3725</v>
+        <v>3300</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -3433,7 +3391,7 @@
         </is>
       </c>
       <c r="H96">
-        <v>2009</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="97">
@@ -3444,20 +3402,20 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Biscoe</t>
+          <t>Dream</t>
         </is>
       </c>
       <c r="C97">
-        <v>41</v>
+        <v>40.8</v>
       </c>
       <c r="D97">
-        <v>20</v>
+        <v>18.9</v>
       </c>
       <c r="E97">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="F97">
-        <v>4725</v>
+        <v>4300</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -3465,7 +3423,7 @@
         </is>
       </c>
       <c r="H97">
-        <v>2009</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="98">
@@ -3476,20 +3434,20 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Biscoe</t>
+          <t>Dream</t>
         </is>
       </c>
       <c r="C98">
-        <v>37.7</v>
+        <v>38.1</v>
       </c>
       <c r="D98">
-        <v>16</v>
+        <v>18.6</v>
       </c>
       <c r="E98">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="F98">
-        <v>3075</v>
+        <v>3700</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -3497,7 +3455,7 @@
         </is>
       </c>
       <c r="H98">
-        <v>2009</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="99">
@@ -3508,20 +3466,20 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Biscoe</t>
+          <t>Dream</t>
         </is>
       </c>
       <c r="C99">
-        <v>37.8</v>
+        <v>40.3</v>
       </c>
       <c r="D99">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="E99">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="F99">
-        <v>4250</v>
+        <v>4350</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -3529,7 +3487,7 @@
         </is>
       </c>
       <c r="H99">
-        <v>2009</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="100">
@@ -3540,20 +3498,20 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Biscoe</t>
+          <t>Dream</t>
         </is>
       </c>
       <c r="C100">
-        <v>37.9</v>
+        <v>33.1</v>
       </c>
       <c r="D100">
-        <v>18.6</v>
+        <v>16.1</v>
       </c>
       <c r="E100">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="F100">
-        <v>2925</v>
+        <v>2900</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -3561,7 +3519,7 @@
         </is>
       </c>
       <c r="H100">
-        <v>2009</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="101">
@@ -3572,20 +3530,20 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Biscoe</t>
+          <t>Dream</t>
         </is>
       </c>
       <c r="C101">
-        <v>39.7</v>
+        <v>43.2</v>
       </c>
       <c r="D101">
-        <v>18.9</v>
+        <v>18.5</v>
       </c>
       <c r="E101">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="F101">
-        <v>3550</v>
+        <v>4100</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -3593,7 +3551,7 @@
         </is>
       </c>
       <c r="H101">
-        <v>2009</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="102">
@@ -3608,16 +3566,16 @@
         </is>
       </c>
       <c r="C102">
-        <v>38.6</v>
+        <v>35</v>
       </c>
       <c r="D102">
-        <v>17.2</v>
+        <v>17.9</v>
       </c>
       <c r="E102">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="F102">
-        <v>3750</v>
+        <v>3725</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -3640,16 +3598,16 @@
         </is>
       </c>
       <c r="C103">
-        <v>38.2</v>
+        <v>41</v>
       </c>
       <c r="D103">
         <v>20</v>
       </c>
       <c r="E103">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="F103">
-        <v>3900</v>
+        <v>4725</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -3672,16 +3630,16 @@
         </is>
       </c>
       <c r="C104">
-        <v>38.1</v>
+        <v>37.7</v>
       </c>
       <c r="D104">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E104">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F104">
-        <v>3175</v>
+        <v>3075</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -3704,16 +3662,16 @@
         </is>
       </c>
       <c r="C105">
-        <v>43.2</v>
+        <v>37.8</v>
       </c>
       <c r="D105">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E105">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="F105">
-        <v>4775</v>
+        <v>4250</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -3736,16 +3694,16 @@
         </is>
       </c>
       <c r="C106">
-        <v>38.1</v>
+        <v>37.9</v>
       </c>
       <c r="D106">
-        <v>16.5</v>
+        <v>18.6</v>
       </c>
       <c r="E106">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="F106">
-        <v>3825</v>
+        <v>2925</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -3768,16 +3726,16 @@
         </is>
       </c>
       <c r="C107">
-        <v>45.6</v>
+        <v>39.7</v>
       </c>
       <c r="D107">
-        <v>20.3</v>
+        <v>18.9</v>
       </c>
       <c r="E107">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="F107">
-        <v>4600</v>
+        <v>3550</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -3800,16 +3758,16 @@
         </is>
       </c>
       <c r="C108">
-        <v>39.7</v>
+        <v>38.6</v>
       </c>
       <c r="D108">
-        <v>17.7</v>
+        <v>17.2</v>
       </c>
       <c r="E108">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="F108">
-        <v>3200</v>
+        <v>3750</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -3832,16 +3790,16 @@
         </is>
       </c>
       <c r="C109">
-        <v>42.2</v>
+        <v>38.2</v>
       </c>
       <c r="D109">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="E109">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="F109">
-        <v>4275</v>
+        <v>3900</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -3864,16 +3822,16 @@
         </is>
       </c>
       <c r="C110">
-        <v>39.6</v>
+        <v>38.1</v>
       </c>
       <c r="D110">
-        <v>20.7</v>
+        <v>17</v>
       </c>
       <c r="E110">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="F110">
-        <v>3900</v>
+        <v>3175</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -3896,16 +3854,16 @@
         </is>
       </c>
       <c r="C111">
-        <v>42.7</v>
+        <v>43.2</v>
       </c>
       <c r="D111">
-        <v>18.3</v>
+        <v>19</v>
       </c>
       <c r="E111">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F111">
-        <v>4075</v>
+        <v>4775</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -3924,20 +3882,20 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Torgersen</t>
+          <t>Biscoe</t>
         </is>
       </c>
       <c r="C112">
-        <v>38.6</v>
+        <v>38.1</v>
       </c>
       <c r="D112">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="E112">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="F112">
-        <v>2900</v>
+        <v>3825</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -3956,20 +3914,20 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Torgersen</t>
+          <t>Biscoe</t>
         </is>
       </c>
       <c r="C113">
-        <v>37.3</v>
+        <v>45.6</v>
       </c>
       <c r="D113">
-        <v>20.5</v>
+        <v>20.3</v>
       </c>
       <c r="E113">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="F113">
-        <v>3775</v>
+        <v>4600</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -3988,20 +3946,20 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Torgersen</t>
+          <t>Biscoe</t>
         </is>
       </c>
       <c r="C114">
-        <v>35.7</v>
+        <v>39.7</v>
       </c>
       <c r="D114">
-        <v>17</v>
+        <v>17.7</v>
       </c>
       <c r="E114">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="F114">
-        <v>3350</v>
+        <v>3200</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -4020,20 +3978,20 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Torgersen</t>
+          <t>Biscoe</t>
         </is>
       </c>
       <c r="C115">
-        <v>41.1</v>
+        <v>42.2</v>
       </c>
       <c r="D115">
-        <v>18.6</v>
+        <v>19.5</v>
       </c>
       <c r="E115">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="F115">
-        <v>3325</v>
+        <v>4275</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -4052,20 +4010,20 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Torgersen</t>
+          <t>Biscoe</t>
         </is>
       </c>
       <c r="C116">
-        <v>36.2</v>
+        <v>39.6</v>
       </c>
       <c r="D116">
-        <v>17.2</v>
+        <v>20.7</v>
       </c>
       <c r="E116">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="F116">
-        <v>3150</v>
+        <v>3900</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -4084,20 +4042,20 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Torgersen</t>
+          <t>Biscoe</t>
         </is>
       </c>
       <c r="C117">
-        <v>37.7</v>
+        <v>42.7</v>
       </c>
       <c r="D117">
-        <v>19.8</v>
+        <v>18.3</v>
       </c>
       <c r="E117">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F117">
-        <v>3500</v>
+        <v>4075</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -4120,16 +4078,16 @@
         </is>
       </c>
       <c r="C118">
-        <v>40.2</v>
+        <v>38.6</v>
       </c>
       <c r="D118">
         <v>17</v>
       </c>
       <c r="E118">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="F118">
-        <v>3450</v>
+        <v>2900</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -4152,16 +4110,16 @@
         </is>
       </c>
       <c r="C119">
-        <v>41.4</v>
+        <v>37.3</v>
       </c>
       <c r="D119">
-        <v>18.5</v>
+        <v>20.5</v>
       </c>
       <c r="E119">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="F119">
-        <v>3875</v>
+        <v>3775</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -4184,16 +4142,16 @@
         </is>
       </c>
       <c r="C120">
-        <v>35.2</v>
+        <v>35.7</v>
       </c>
       <c r="D120">
-        <v>15.9</v>
+        <v>17</v>
       </c>
       <c r="E120">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="F120">
-        <v>3050</v>
+        <v>3350</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -4216,16 +4174,16 @@
         </is>
       </c>
       <c r="C121">
-        <v>40.6</v>
+        <v>41.1</v>
       </c>
       <c r="D121">
-        <v>19</v>
+        <v>18.6</v>
       </c>
       <c r="E121">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="F121">
-        <v>4000</v>
+        <v>3325</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -4248,16 +4206,16 @@
         </is>
       </c>
       <c r="C122">
-        <v>38.8</v>
+        <v>36.2</v>
       </c>
       <c r="D122">
-        <v>17.6</v>
+        <v>17.2</v>
       </c>
       <c r="E122">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="F122">
-        <v>3275</v>
+        <v>3150</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -4280,16 +4238,16 @@
         </is>
       </c>
       <c r="C123">
-        <v>41.5</v>
+        <v>37.7</v>
       </c>
       <c r="D123">
-        <v>18.3</v>
+        <v>19.8</v>
       </c>
       <c r="E123">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F123">
-        <v>4300</v>
+        <v>3500</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -4312,16 +4270,16 @@
         </is>
       </c>
       <c r="C124">
-        <v>39</v>
+        <v>40.2</v>
       </c>
       <c r="D124">
-        <v>17.1</v>
+        <v>17</v>
       </c>
       <c r="E124">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="F124">
-        <v>3050</v>
+        <v>3450</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -4344,16 +4302,16 @@
         </is>
       </c>
       <c r="C125">
-        <v>44.1</v>
+        <v>41.4</v>
       </c>
       <c r="D125">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="E125">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="F125">
-        <v>4000</v>
+        <v>3875</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
@@ -4376,16 +4334,16 @@
         </is>
       </c>
       <c r="C126">
-        <v>38.5</v>
+        <v>35.2</v>
       </c>
       <c r="D126">
-        <v>17.9</v>
+        <v>15.9</v>
       </c>
       <c r="E126">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="F126">
-        <v>3325</v>
+        <v>3050</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
@@ -4408,16 +4366,16 @@
         </is>
       </c>
       <c r="C127">
-        <v>43.1</v>
+        <v>40.6</v>
       </c>
       <c r="D127">
-        <v>19.2</v>
+        <v>19</v>
       </c>
       <c r="E127">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F127">
-        <v>3500</v>
+        <v>4000</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
@@ -4436,20 +4394,20 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Dream</t>
+          <t>Torgersen</t>
         </is>
       </c>
       <c r="C128">
-        <v>36.8</v>
+        <v>38.8</v>
       </c>
       <c r="D128">
-        <v>18.5</v>
+        <v>17.6</v>
       </c>
       <c r="E128">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="F128">
-        <v>3500</v>
+        <v>3275</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
@@ -4468,20 +4426,20 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Dream</t>
+          <t>Torgersen</t>
         </is>
       </c>
       <c r="C129">
-        <v>37.5</v>
+        <v>41.5</v>
       </c>
       <c r="D129">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="E129">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F129">
-        <v>4475</v>
+        <v>4300</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
@@ -4500,20 +4458,20 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Dream</t>
+          <t>Torgersen</t>
         </is>
       </c>
       <c r="C130">
-        <v>38.1</v>
+        <v>39</v>
       </c>
       <c r="D130">
-        <v>17.6</v>
+        <v>17.1</v>
       </c>
       <c r="E130">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="F130">
-        <v>3425</v>
+        <v>3050</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
@@ -4532,20 +4490,20 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Dream</t>
+          <t>Torgersen</t>
         </is>
       </c>
       <c r="C131">
-        <v>41.1</v>
+        <v>44.1</v>
       </c>
       <c r="D131">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="E131">
-        <v>190</v>
+        <v>210</v>
       </c>
       <c r="F131">
-        <v>3900</v>
+        <v>4000</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
@@ -4564,20 +4522,20 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Dream</t>
+          <t>Torgersen</t>
         </is>
       </c>
       <c r="C132">
-        <v>35.6</v>
+        <v>38.5</v>
       </c>
       <c r="D132">
-        <v>17.5</v>
+        <v>17.9</v>
       </c>
       <c r="E132">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F132">
-        <v>3175</v>
+        <v>3325</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
@@ -4596,20 +4554,20 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Dream</t>
+          <t>Torgersen</t>
         </is>
       </c>
       <c r="C133">
-        <v>40.2</v>
+        <v>43.1</v>
       </c>
       <c r="D133">
-        <v>20.1</v>
+        <v>19.2</v>
       </c>
       <c r="E133">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F133">
-        <v>3975</v>
+        <v>3500</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
@@ -4632,16 +4590,16 @@
         </is>
       </c>
       <c r="C134">
-        <v>37</v>
+        <v>36.8</v>
       </c>
       <c r="D134">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="E134">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="F134">
-        <v>3400</v>
+        <v>3500</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -4664,16 +4622,16 @@
         </is>
       </c>
       <c r="C135">
-        <v>39.7</v>
+        <v>37.5</v>
       </c>
       <c r="D135">
-        <v>17.9</v>
+        <v>18.5</v>
       </c>
       <c r="E135">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="F135">
-        <v>4250</v>
+        <v>4475</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -4696,16 +4654,16 @@
         </is>
       </c>
       <c r="C136">
-        <v>40.2</v>
+        <v>38.1</v>
       </c>
       <c r="D136">
-        <v>17.1</v>
+        <v>17.6</v>
       </c>
       <c r="E136">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="F136">
-        <v>3400</v>
+        <v>3425</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
@@ -4728,16 +4686,16 @@
         </is>
       </c>
       <c r="C137">
-        <v>40.6</v>
+        <v>41.1</v>
       </c>
       <c r="D137">
-        <v>17.2</v>
+        <v>17.5</v>
       </c>
       <c r="E137">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F137">
-        <v>3475</v>
+        <v>3900</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
@@ -4760,16 +4718,16 @@
         </is>
       </c>
       <c r="C138">
-        <v>32.1</v>
+        <v>35.6</v>
       </c>
       <c r="D138">
-        <v>15.5</v>
+        <v>17.5</v>
       </c>
       <c r="E138">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F138">
-        <v>3050</v>
+        <v>3175</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
@@ -4792,16 +4750,16 @@
         </is>
       </c>
       <c r="C139">
-        <v>40.7</v>
+        <v>40.2</v>
       </c>
       <c r="D139">
-        <v>17</v>
+        <v>20.1</v>
       </c>
       <c r="E139">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="F139">
-        <v>3725</v>
+        <v>3975</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
@@ -4824,16 +4782,16 @@
         </is>
       </c>
       <c r="C140">
-        <v>37.3</v>
+        <v>37</v>
       </c>
       <c r="D140">
-        <v>16.8</v>
+        <v>16.5</v>
       </c>
       <c r="E140">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="F140">
-        <v>3000</v>
+        <v>3400</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -4856,16 +4814,16 @@
         </is>
       </c>
       <c r="C141">
-        <v>39</v>
+        <v>39.7</v>
       </c>
       <c r="D141">
-        <v>18.7</v>
+        <v>17.9</v>
       </c>
       <c r="E141">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="F141">
-        <v>3650</v>
+        <v>4250</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
@@ -4888,20 +4846,20 @@
         </is>
       </c>
       <c r="C142">
-        <v>39.2</v>
+        <v>40.2</v>
       </c>
       <c r="D142">
-        <v>18.6</v>
+        <v>17.1</v>
       </c>
       <c r="E142">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="F142">
-        <v>4250</v>
+        <v>3400</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H142">
@@ -4920,20 +4878,20 @@
         </is>
       </c>
       <c r="C143">
-        <v>36.6</v>
+        <v>40.6</v>
       </c>
       <c r="D143">
-        <v>18.4</v>
+        <v>17.2</v>
       </c>
       <c r="E143">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="F143">
         <v>3475</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H143">
@@ -4952,16 +4910,16 @@
         </is>
       </c>
       <c r="C144">
-        <v>36</v>
+        <v>32.1</v>
       </c>
       <c r="D144">
-        <v>17.8</v>
+        <v>15.5</v>
       </c>
       <c r="E144">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="F144">
-        <v>3450</v>
+        <v>3050</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -4984,16 +4942,16 @@
         </is>
       </c>
       <c r="C145">
-        <v>37.8</v>
+        <v>40.7</v>
       </c>
       <c r="D145">
-        <v>18.1</v>
+        <v>17</v>
       </c>
       <c r="E145">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="F145">
-        <v>3750</v>
+        <v>3725</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
@@ -5016,16 +4974,16 @@
         </is>
       </c>
       <c r="C146">
-        <v>36</v>
+        <v>37.3</v>
       </c>
       <c r="D146">
-        <v>17.1</v>
+        <v>16.8</v>
       </c>
       <c r="E146">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="F146">
-        <v>3700</v>
+        <v>3000</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
@@ -5048,16 +5006,16 @@
         </is>
       </c>
       <c r="C147">
-        <v>41.5</v>
+        <v>39</v>
       </c>
       <c r="D147">
-        <v>18.5</v>
+        <v>18.7</v>
       </c>
       <c r="E147">
-        <v>201</v>
+        <v>185</v>
       </c>
       <c r="F147">
-        <v>4000</v>
+        <v>3650</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -5071,89 +5029,89 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Gentoo</t>
+          <t>Adelie</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Biscoe</t>
+          <t>Dream</t>
         </is>
       </c>
       <c r="C148">
-        <v>46.1</v>
+        <v>39.2</v>
       </c>
       <c r="D148">
-        <v>13.2</v>
+        <v>18.6</v>
       </c>
       <c r="E148">
-        <v>211</v>
+        <v>190</v>
       </c>
       <c r="F148">
-        <v>4500</v>
+        <v>4250</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H148">
-        <v>2007</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Gentoo</t>
+          <t>Adelie</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Biscoe</t>
+          <t>Dream</t>
         </is>
       </c>
       <c r="C149">
-        <v>50</v>
+        <v>36.6</v>
       </c>
       <c r="D149">
-        <v>16.3</v>
+        <v>18.4</v>
       </c>
       <c r="E149">
-        <v>230</v>
+        <v>184</v>
       </c>
       <c r="F149">
-        <v>5700</v>
+        <v>3475</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H149">
-        <v>2007</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Gentoo</t>
+          <t>Adelie</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Biscoe</t>
+          <t>Dream</t>
         </is>
       </c>
       <c r="C150">
-        <v>48.7</v>
+        <v>36</v>
       </c>
       <c r="D150">
-        <v>14.1</v>
+        <v>17.8</v>
       </c>
       <c r="E150">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="F150">
-        <v>4450</v>
+        <v>3450</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
@@ -5161,31 +5119,31 @@
         </is>
       </c>
       <c r="H150">
-        <v>2007</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Gentoo</t>
+          <t>Adelie</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Biscoe</t>
+          <t>Dream</t>
         </is>
       </c>
       <c r="C151">
-        <v>50</v>
+        <v>37.8</v>
       </c>
       <c r="D151">
-        <v>15.2</v>
+        <v>18.1</v>
       </c>
       <c r="E151">
-        <v>218</v>
+        <v>193</v>
       </c>
       <c r="F151">
-        <v>5700</v>
+        <v>3750</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
@@ -5193,71 +5151,71 @@
         </is>
       </c>
       <c r="H151">
-        <v>2007</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Gentoo</t>
+          <t>Adelie</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Biscoe</t>
+          <t>Dream</t>
         </is>
       </c>
       <c r="C152">
-        <v>47.6</v>
+        <v>36</v>
       </c>
       <c r="D152">
-        <v>14.5</v>
+        <v>17.1</v>
       </c>
       <c r="E152">
-        <v>215</v>
+        <v>187</v>
       </c>
       <c r="F152">
-        <v>5400</v>
+        <v>3700</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H152">
-        <v>2007</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Gentoo</t>
+          <t>Adelie</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Biscoe</t>
+          <t>Dream</t>
         </is>
       </c>
       <c r="C153">
-        <v>46.5</v>
+        <v>41.5</v>
       </c>
       <c r="D153">
-        <v>13.5</v>
+        <v>18.5</v>
       </c>
       <c r="E153">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="F153">
-        <v>4550</v>
+        <v>4000</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H153">
-        <v>2007</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="154">
@@ -5272,16 +5230,16 @@
         </is>
       </c>
       <c r="C154">
-        <v>45.4</v>
+        <v>46.1</v>
       </c>
       <c r="D154">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E154">
         <v>211</v>
       </c>
       <c r="F154">
-        <v>4800</v>
+        <v>4500</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
@@ -5304,16 +5262,16 @@
         </is>
       </c>
       <c r="C155">
-        <v>46.7</v>
+        <v>50</v>
       </c>
       <c r="D155">
-        <v>15.3</v>
+        <v>16.3</v>
       </c>
       <c r="E155">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="F155">
-        <v>5200</v>
+        <v>5700</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
@@ -5336,16 +5294,16 @@
         </is>
       </c>
       <c r="C156">
-        <v>43.3</v>
+        <v>48.7</v>
       </c>
       <c r="D156">
-        <v>13.4</v>
+        <v>14.1</v>
       </c>
       <c r="E156">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F156">
-        <v>4400</v>
+        <v>4450</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
@@ -5368,16 +5326,16 @@
         </is>
       </c>
       <c r="C157">
-        <v>46.8</v>
+        <v>50</v>
       </c>
       <c r="D157">
-        <v>15.4</v>
+        <v>15.2</v>
       </c>
       <c r="E157">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="F157">
-        <v>5150</v>
+        <v>5700</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
@@ -5400,20 +5358,20 @@
         </is>
       </c>
       <c r="C158">
-        <v>40.9</v>
+        <v>47.6</v>
       </c>
       <c r="D158">
-        <v>13.7</v>
+        <v>14.5</v>
       </c>
       <c r="E158">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F158">
-        <v>4650</v>
+        <v>5400</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H158">
@@ -5432,20 +5390,20 @@
         </is>
       </c>
       <c r="C159">
-        <v>49</v>
+        <v>46.5</v>
       </c>
       <c r="D159">
-        <v>16.1</v>
+        <v>13.5</v>
       </c>
       <c r="E159">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="F159">
-        <v>5550</v>
+        <v>4550</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H159">
@@ -5464,16 +5422,16 @@
         </is>
       </c>
       <c r="C160">
-        <v>45.5</v>
+        <v>45.4</v>
       </c>
       <c r="D160">
-        <v>13.7</v>
+        <v>14.6</v>
       </c>
       <c r="E160">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F160">
-        <v>4650</v>
+        <v>4800</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
@@ -5496,16 +5454,16 @@
         </is>
       </c>
       <c r="C161">
-        <v>48.4</v>
+        <v>46.7</v>
       </c>
       <c r="D161">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E161">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="F161">
-        <v>5850</v>
+        <v>5200</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
@@ -5528,16 +5486,16 @@
         </is>
       </c>
       <c r="C162">
-        <v>45.8</v>
+        <v>43.3</v>
       </c>
       <c r="D162">
-        <v>14.6</v>
+        <v>13.4</v>
       </c>
       <c r="E162">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F162">
-        <v>4200</v>
+        <v>4400</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
@@ -5560,16 +5518,16 @@
         </is>
       </c>
       <c r="C163">
-        <v>49.3</v>
+        <v>46.8</v>
       </c>
       <c r="D163">
-        <v>15.7</v>
+        <v>15.4</v>
       </c>
       <c r="E163">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F163">
-        <v>5850</v>
+        <v>5150</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
@@ -5592,16 +5550,16 @@
         </is>
       </c>
       <c r="C164">
-        <v>42</v>
+        <v>40.9</v>
       </c>
       <c r="D164">
-        <v>13.5</v>
+        <v>13.7</v>
       </c>
       <c r="E164">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="F164">
-        <v>4150</v>
+        <v>4650</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
@@ -5624,16 +5582,16 @@
         </is>
       </c>
       <c r="C165">
-        <v>49.2</v>
+        <v>49</v>
       </c>
       <c r="D165">
-        <v>15.2</v>
+        <v>16.1</v>
       </c>
       <c r="E165">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="F165">
-        <v>6300</v>
+        <v>5550</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
@@ -5656,16 +5614,16 @@
         </is>
       </c>
       <c r="C166">
-        <v>46.2</v>
+        <v>45.5</v>
       </c>
       <c r="D166">
-        <v>14.5</v>
+        <v>13.7</v>
       </c>
       <c r="E166">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="F166">
-        <v>4800</v>
+        <v>4650</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
@@ -5688,16 +5646,16 @@
         </is>
       </c>
       <c r="C167">
-        <v>48.7</v>
+        <v>48.4</v>
       </c>
       <c r="D167">
-        <v>15.1</v>
+        <v>14.6</v>
       </c>
       <c r="E167">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="F167">
-        <v>5350</v>
+        <v>5850</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
@@ -5720,20 +5678,20 @@
         </is>
       </c>
       <c r="C168">
-        <v>50.2</v>
+        <v>45.8</v>
       </c>
       <c r="D168">
-        <v>14.3</v>
+        <v>14.6</v>
       </c>
       <c r="E168">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="F168">
-        <v>5700</v>
+        <v>4200</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H168">
@@ -5752,20 +5710,20 @@
         </is>
       </c>
       <c r="C169">
-        <v>45.1</v>
+        <v>49.3</v>
       </c>
       <c r="D169">
-        <v>14.5</v>
+        <v>15.7</v>
       </c>
       <c r="E169">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="F169">
-        <v>5000</v>
+        <v>5850</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H169">
@@ -5784,16 +5742,16 @@
         </is>
       </c>
       <c r="C170">
-        <v>46.5</v>
+        <v>42</v>
       </c>
       <c r="D170">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="E170">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F170">
-        <v>4400</v>
+        <v>4150</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
@@ -5816,16 +5774,16 @@
         </is>
       </c>
       <c r="C171">
-        <v>46.3</v>
+        <v>49.2</v>
       </c>
       <c r="D171">
-        <v>15.8</v>
+        <v>15.2</v>
       </c>
       <c r="E171">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="F171">
-        <v>5050</v>
+        <v>6300</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
@@ -5848,16 +5806,16 @@
         </is>
       </c>
       <c r="C172">
-        <v>42.9</v>
+        <v>46.2</v>
       </c>
       <c r="D172">
-        <v>13.1</v>
+        <v>14.5</v>
       </c>
       <c r="E172">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="F172">
-        <v>5000</v>
+        <v>4800</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
@@ -5880,16 +5838,16 @@
         </is>
       </c>
       <c r="C173">
-        <v>46.1</v>
+        <v>48.7</v>
       </c>
       <c r="D173">
         <v>15.1</v>
       </c>
       <c r="E173">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="F173">
-        <v>5100</v>
+        <v>5350</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
@@ -5912,16 +5870,16 @@
         </is>
       </c>
       <c r="C174">
-        <v>47.8</v>
+        <v>50.2</v>
       </c>
       <c r="D174">
-        <v>15</v>
+        <v>14.3</v>
       </c>
       <c r="E174">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="F174">
-        <v>5650</v>
+        <v>5700</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
@@ -5944,16 +5902,16 @@
         </is>
       </c>
       <c r="C175">
-        <v>48.2</v>
+        <v>45.1</v>
       </c>
       <c r="D175">
-        <v>14.3</v>
+        <v>14.5</v>
       </c>
       <c r="E175">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="F175">
-        <v>4600</v>
+        <v>5000</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
@@ -5976,20 +5934,20 @@
         </is>
       </c>
       <c r="C176">
-        <v>50</v>
+        <v>46.5</v>
       </c>
       <c r="D176">
-        <v>15.3</v>
+        <v>14.5</v>
       </c>
       <c r="E176">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="F176">
-        <v>5550</v>
+        <v>4400</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H176">
@@ -6008,16 +5966,16 @@
         </is>
       </c>
       <c r="C177">
-        <v>47.3</v>
+        <v>46.3</v>
       </c>
       <c r="D177">
-        <v>15.3</v>
+        <v>15.8</v>
       </c>
       <c r="E177">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="F177">
-        <v>5250</v>
+        <v>5050</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
@@ -6040,16 +5998,16 @@
         </is>
       </c>
       <c r="C178">
-        <v>42.8</v>
+        <v>42.9</v>
       </c>
       <c r="D178">
-        <v>14.2</v>
+        <v>13.1</v>
       </c>
       <c r="E178">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="F178">
-        <v>4700</v>
+        <v>5000</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
@@ -6072,20 +6030,20 @@
         </is>
       </c>
       <c r="C179">
-        <v>45.1</v>
+        <v>46.1</v>
       </c>
       <c r="D179">
-        <v>14.5</v>
+        <v>15.1</v>
       </c>
       <c r="E179">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="F179">
-        <v>5050</v>
+        <v>5100</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H179">
@@ -6104,21 +6062,16 @@
         </is>
       </c>
       <c r="C180">
-        <v>59.6</v>
+        <v>44.5</v>
       </c>
       <c r="D180">
-        <v>17</v>
+        <v>14.3</v>
       </c>
       <c r="E180">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="F180">
-        <v>6050</v>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>male</t>
-        </is>
+        <v>4100</v>
       </c>
       <c r="H180">
         <v>2007</v>
@@ -6136,24 +6089,24 @@
         </is>
       </c>
       <c r="C181">
-        <v>49.1</v>
+        <v>47.8</v>
       </c>
       <c r="D181">
-        <v>14.8</v>
+        <v>15</v>
       </c>
       <c r="E181">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="F181">
-        <v>5150</v>
+        <v>5650</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H181">
-        <v>2008</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="182">
@@ -6168,24 +6121,24 @@
         </is>
       </c>
       <c r="C182">
-        <v>48.4</v>
+        <v>48.2</v>
       </c>
       <c r="D182">
-        <v>16.3</v>
+        <v>14.3</v>
       </c>
       <c r="E182">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="F182">
-        <v>5400</v>
+        <v>4600</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H182">
-        <v>2008</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="183">
@@ -6200,24 +6153,24 @@
         </is>
       </c>
       <c r="C183">
-        <v>42.6</v>
+        <v>50</v>
       </c>
       <c r="D183">
-        <v>13.7</v>
+        <v>15.3</v>
       </c>
       <c r="E183">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="F183">
-        <v>4950</v>
+        <v>5550</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H183">
-        <v>2008</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="184">
@@ -6232,13 +6185,13 @@
         </is>
       </c>
       <c r="C184">
-        <v>44.4</v>
+        <v>47.3</v>
       </c>
       <c r="D184">
-        <v>17.3</v>
+        <v>15.3</v>
       </c>
       <c r="E184">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="F184">
         <v>5250</v>
@@ -6249,7 +6202,7 @@
         </is>
       </c>
       <c r="H184">
-        <v>2008</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="185">
@@ -6264,16 +6217,16 @@
         </is>
       </c>
       <c r="C185">
-        <v>44</v>
+        <v>42.8</v>
       </c>
       <c r="D185">
-        <v>13.6</v>
+        <v>14.2</v>
       </c>
       <c r="E185">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F185">
-        <v>4350</v>
+        <v>4700</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
@@ -6281,7 +6234,7 @@
         </is>
       </c>
       <c r="H185">
-        <v>2008</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="186">
@@ -6296,24 +6249,24 @@
         </is>
       </c>
       <c r="C186">
-        <v>48.7</v>
+        <v>45.1</v>
       </c>
       <c r="D186">
-        <v>15.7</v>
+        <v>14.5</v>
       </c>
       <c r="E186">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F186">
-        <v>5350</v>
+        <v>5050</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H186">
-        <v>2008</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="187">
@@ -6328,24 +6281,24 @@
         </is>
       </c>
       <c r="C187">
-        <v>42.7</v>
+        <v>59.6</v>
       </c>
       <c r="D187">
-        <v>13.7</v>
+        <v>17</v>
       </c>
       <c r="E187">
-        <v>208</v>
+        <v>230</v>
       </c>
       <c r="F187">
-        <v>3950</v>
+        <v>6050</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H187">
-        <v>2008</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="188">
@@ -6360,20 +6313,20 @@
         </is>
       </c>
       <c r="C188">
-        <v>49.6</v>
+        <v>49.1</v>
       </c>
       <c r="D188">
-        <v>16</v>
+        <v>14.8</v>
       </c>
       <c r="E188">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="F188">
-        <v>5700</v>
+        <v>5150</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H188">
@@ -6392,20 +6345,20 @@
         </is>
       </c>
       <c r="C189">
-        <v>45.3</v>
+        <v>48.4</v>
       </c>
       <c r="D189">
-        <v>13.7</v>
+        <v>16.3</v>
       </c>
       <c r="E189">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="F189">
-        <v>4300</v>
+        <v>5400</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H189">
@@ -6424,20 +6377,20 @@
         </is>
       </c>
       <c r="C190">
-        <v>49.6</v>
+        <v>42.6</v>
       </c>
       <c r="D190">
-        <v>15</v>
+        <v>13.7</v>
       </c>
       <c r="E190">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F190">
-        <v>4750</v>
+        <v>4950</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H190">
@@ -6456,16 +6409,16 @@
         </is>
       </c>
       <c r="C191">
-        <v>50.5</v>
+        <v>44.4</v>
       </c>
       <c r="D191">
-        <v>15.9</v>
+        <v>17.3</v>
       </c>
       <c r="E191">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F191">
-        <v>5550</v>
+        <v>5250</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
@@ -6488,16 +6441,16 @@
         </is>
       </c>
       <c r="C192">
-        <v>43.6</v>
+        <v>44</v>
       </c>
       <c r="D192">
-        <v>13.9</v>
+        <v>13.6</v>
       </c>
       <c r="E192">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="F192">
-        <v>4900</v>
+        <v>4350</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
@@ -6520,20 +6473,20 @@
         </is>
       </c>
       <c r="C193">
-        <v>45.5</v>
+        <v>48.7</v>
       </c>
       <c r="D193">
-        <v>13.9</v>
+        <v>15.7</v>
       </c>
       <c r="E193">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="F193">
-        <v>4200</v>
+        <v>5350</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H193">
@@ -6552,20 +6505,20 @@
         </is>
       </c>
       <c r="C194">
-        <v>50.5</v>
+        <v>42.7</v>
       </c>
       <c r="D194">
-        <v>15.9</v>
+        <v>13.7</v>
       </c>
       <c r="E194">
-        <v>225</v>
+        <v>208</v>
       </c>
       <c r="F194">
-        <v>5400</v>
+        <v>3950</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H194">
@@ -6584,20 +6537,20 @@
         </is>
       </c>
       <c r="C195">
-        <v>44.9</v>
+        <v>49.6</v>
       </c>
       <c r="D195">
-        <v>13.3</v>
+        <v>16</v>
       </c>
       <c r="E195">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="F195">
-        <v>5100</v>
+        <v>5700</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H195">
@@ -6616,20 +6569,20 @@
         </is>
       </c>
       <c r="C196">
-        <v>45.2</v>
+        <v>45.3</v>
       </c>
       <c r="D196">
-        <v>15.8</v>
+        <v>13.7</v>
       </c>
       <c r="E196">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="F196">
-        <v>5300</v>
+        <v>4300</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H196">
@@ -6648,20 +6601,20 @@
         </is>
       </c>
       <c r="C197">
-        <v>46.6</v>
+        <v>49.6</v>
       </c>
       <c r="D197">
-        <v>14.2</v>
+        <v>15</v>
       </c>
       <c r="E197">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="F197">
-        <v>4850</v>
+        <v>4750</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H197">
@@ -6680,16 +6633,16 @@
         </is>
       </c>
       <c r="C198">
-        <v>48.5</v>
+        <v>50.5</v>
       </c>
       <c r="D198">
-        <v>14.1</v>
+        <v>15.9</v>
       </c>
       <c r="E198">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F198">
-        <v>5300</v>
+        <v>5550</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
@@ -6712,16 +6665,16 @@
         </is>
       </c>
       <c r="C199">
-        <v>45.1</v>
+        <v>43.6</v>
       </c>
       <c r="D199">
-        <v>14.4</v>
+        <v>13.9</v>
       </c>
       <c r="E199">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="F199">
-        <v>4400</v>
+        <v>4900</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
@@ -6744,20 +6697,20 @@
         </is>
       </c>
       <c r="C200">
-        <v>50.1</v>
+        <v>45.5</v>
       </c>
       <c r="D200">
-        <v>15</v>
+        <v>13.9</v>
       </c>
       <c r="E200">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="F200">
-        <v>5000</v>
+        <v>4200</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H200">
@@ -6776,20 +6729,20 @@
         </is>
       </c>
       <c r="C201">
-        <v>46.5</v>
+        <v>50.5</v>
       </c>
       <c r="D201">
-        <v>14.4</v>
+        <v>15.9</v>
       </c>
       <c r="E201">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="F201">
-        <v>4900</v>
+        <v>5400</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H201">
@@ -6808,20 +6761,20 @@
         </is>
       </c>
       <c r="C202">
-        <v>45</v>
+        <v>44.9</v>
       </c>
       <c r="D202">
-        <v>15.4</v>
+        <v>13.3</v>
       </c>
       <c r="E202">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="F202">
-        <v>5050</v>
+        <v>5100</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H202">
@@ -6840,20 +6793,20 @@
         </is>
       </c>
       <c r="C203">
-        <v>43.8</v>
+        <v>45.2</v>
       </c>
       <c r="D203">
-        <v>13.9</v>
+        <v>15.8</v>
       </c>
       <c r="E203">
-        <v>208</v>
+        <v>215</v>
       </c>
       <c r="F203">
-        <v>4300</v>
+        <v>5300</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H203">
@@ -6872,20 +6825,20 @@
         </is>
       </c>
       <c r="C204">
-        <v>45.5</v>
+        <v>46.6</v>
       </c>
       <c r="D204">
-        <v>15</v>
+        <v>14.2</v>
       </c>
       <c r="E204">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="F204">
-        <v>5000</v>
+        <v>4850</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H204">
@@ -6904,20 +6857,20 @@
         </is>
       </c>
       <c r="C205">
-        <v>43.2</v>
+        <v>48.5</v>
       </c>
       <c r="D205">
-        <v>14.5</v>
+        <v>14.1</v>
       </c>
       <c r="E205">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="F205">
-        <v>4450</v>
+        <v>5300</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H205">
@@ -6936,20 +6889,20 @@
         </is>
       </c>
       <c r="C206">
-        <v>50.4</v>
+        <v>45.1</v>
       </c>
       <c r="D206">
-        <v>15.3</v>
+        <v>14.4</v>
       </c>
       <c r="E206">
-        <v>224</v>
+        <v>210</v>
       </c>
       <c r="F206">
-        <v>5550</v>
+        <v>4400</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H206">
@@ -6968,20 +6921,20 @@
         </is>
       </c>
       <c r="C207">
-        <v>45.3</v>
+        <v>50.1</v>
       </c>
       <c r="D207">
-        <v>13.8</v>
+        <v>15</v>
       </c>
       <c r="E207">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="F207">
-        <v>4200</v>
+        <v>5000</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H207">
@@ -7000,20 +6953,20 @@
         </is>
       </c>
       <c r="C208">
-        <v>46.2</v>
+        <v>46.5</v>
       </c>
       <c r="D208">
-        <v>14.9</v>
+        <v>14.4</v>
       </c>
       <c r="E208">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="F208">
-        <v>5300</v>
+        <v>4900</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H208">
@@ -7032,20 +6985,20 @@
         </is>
       </c>
       <c r="C209">
-        <v>45.7</v>
+        <v>45</v>
       </c>
       <c r="D209">
-        <v>13.9</v>
+        <v>15.4</v>
       </c>
       <c r="E209">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="F209">
-        <v>4400</v>
+        <v>5050</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H209">
@@ -7064,20 +7017,20 @@
         </is>
       </c>
       <c r="C210">
-        <v>54.3</v>
+        <v>43.8</v>
       </c>
       <c r="D210">
-        <v>15.7</v>
+        <v>13.9</v>
       </c>
       <c r="E210">
-        <v>231</v>
+        <v>208</v>
       </c>
       <c r="F210">
-        <v>5650</v>
+        <v>4300</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H210">
@@ -7096,20 +7049,20 @@
         </is>
       </c>
       <c r="C211">
-        <v>45.8</v>
+        <v>45.5</v>
       </c>
       <c r="D211">
-        <v>14.2</v>
+        <v>15</v>
       </c>
       <c r="E211">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F211">
-        <v>4700</v>
+        <v>5000</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H211">
@@ -7128,20 +7081,20 @@
         </is>
       </c>
       <c r="C212">
-        <v>49.8</v>
+        <v>43.2</v>
       </c>
       <c r="D212">
-        <v>16.8</v>
+        <v>14.5</v>
       </c>
       <c r="E212">
-        <v>230</v>
+        <v>208</v>
       </c>
       <c r="F212">
-        <v>5700</v>
+        <v>4450</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H212">
@@ -7160,16 +7113,16 @@
         </is>
       </c>
       <c r="C213">
-        <v>49.5</v>
+        <v>50.4</v>
       </c>
       <c r="D213">
-        <v>16.2</v>
+        <v>15.3</v>
       </c>
       <c r="E213">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="F213">
-        <v>5800</v>
+        <v>5550</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
@@ -7192,16 +7145,16 @@
         </is>
       </c>
       <c r="C214">
-        <v>43.5</v>
+        <v>45.3</v>
       </c>
       <c r="D214">
-        <v>14.2</v>
+        <v>13.8</v>
       </c>
       <c r="E214">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="F214">
-        <v>4700</v>
+        <v>4200</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
@@ -7224,16 +7177,16 @@
         </is>
       </c>
       <c r="C215">
-        <v>50.7</v>
+        <v>46.2</v>
       </c>
       <c r="D215">
-        <v>15</v>
+        <v>14.9</v>
       </c>
       <c r="E215">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F215">
-        <v>5550</v>
+        <v>5300</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
@@ -7256,16 +7209,16 @@
         </is>
       </c>
       <c r="C216">
-        <v>47.7</v>
+        <v>45.7</v>
       </c>
       <c r="D216">
-        <v>15</v>
+        <v>13.9</v>
       </c>
       <c r="E216">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F216">
-        <v>4750</v>
+        <v>4400</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
@@ -7288,16 +7241,16 @@
         </is>
       </c>
       <c r="C217">
-        <v>46.4</v>
+        <v>54.3</v>
       </c>
       <c r="D217">
-        <v>15.6</v>
+        <v>15.7</v>
       </c>
       <c r="E217">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="F217">
-        <v>5000</v>
+        <v>5650</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
@@ -7320,20 +7273,20 @@
         </is>
       </c>
       <c r="C218">
-        <v>48.2</v>
+        <v>45.8</v>
       </c>
       <c r="D218">
-        <v>15.6</v>
+        <v>14.2</v>
       </c>
       <c r="E218">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F218">
-        <v>5100</v>
+        <v>4700</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H218">
@@ -7352,20 +7305,20 @@
         </is>
       </c>
       <c r="C219">
-        <v>46.5</v>
+        <v>49.8</v>
       </c>
       <c r="D219">
-        <v>14.8</v>
+        <v>16.8</v>
       </c>
       <c r="E219">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="F219">
-        <v>5200</v>
+        <v>5700</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H219">
@@ -7384,21 +7337,16 @@
         </is>
       </c>
       <c r="C220">
-        <v>46.4</v>
+        <v>46.2</v>
       </c>
       <c r="D220">
-        <v>15</v>
+        <v>14.4</v>
       </c>
       <c r="E220">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F220">
-        <v>4700</v>
-      </c>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>female</t>
-        </is>
+        <v>4650</v>
       </c>
       <c r="H220">
         <v>2008</v>
@@ -7416,13 +7364,13 @@
         </is>
       </c>
       <c r="C221">
-        <v>48.6</v>
+        <v>49.5</v>
       </c>
       <c r="D221">
-        <v>16</v>
+        <v>16.2</v>
       </c>
       <c r="E221">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="F221">
         <v>5800</v>
@@ -7448,16 +7396,16 @@
         </is>
       </c>
       <c r="C222">
-        <v>47.5</v>
+        <v>43.5</v>
       </c>
       <c r="D222">
         <v>14.2</v>
       </c>
       <c r="E222">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="F222">
-        <v>4600</v>
+        <v>4700</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
@@ -7480,16 +7428,16 @@
         </is>
       </c>
       <c r="C223">
-        <v>51.1</v>
+        <v>50.7</v>
       </c>
       <c r="D223">
-        <v>16.3</v>
+        <v>15</v>
       </c>
       <c r="E223">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="F223">
-        <v>6000</v>
+        <v>5550</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
@@ -7512,13 +7460,13 @@
         </is>
       </c>
       <c r="C224">
-        <v>45.2</v>
+        <v>47.7</v>
       </c>
       <c r="D224">
-        <v>13.8</v>
+        <v>15</v>
       </c>
       <c r="E224">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F224">
         <v>4750</v>
@@ -7544,16 +7492,16 @@
         </is>
       </c>
       <c r="C225">
-        <v>45.2</v>
+        <v>46.4</v>
       </c>
       <c r="D225">
-        <v>16.4</v>
+        <v>15.6</v>
       </c>
       <c r="E225">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="F225">
-        <v>5950</v>
+        <v>5000</v>
       </c>
       <c r="G225" t="inlineStr">
         <is>
@@ -7576,24 +7524,24 @@
         </is>
       </c>
       <c r="C226">
-        <v>49.1</v>
+        <v>48.2</v>
       </c>
       <c r="D226">
-        <v>14.5</v>
+        <v>15.6</v>
       </c>
       <c r="E226">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="F226">
-        <v>4625</v>
+        <v>5100</v>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H226">
-        <v>2009</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="227">
@@ -7608,24 +7556,24 @@
         </is>
       </c>
       <c r="C227">
-        <v>52.5</v>
+        <v>46.5</v>
       </c>
       <c r="D227">
-        <v>15.6</v>
+        <v>14.8</v>
       </c>
       <c r="E227">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="F227">
-        <v>5450</v>
+        <v>5200</v>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H227">
-        <v>2009</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="228">
@@ -7640,16 +7588,16 @@
         </is>
       </c>
       <c r="C228">
-        <v>47.4</v>
+        <v>46.4</v>
       </c>
       <c r="D228">
-        <v>14.6</v>
+        <v>15</v>
       </c>
       <c r="E228">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="F228">
-        <v>4725</v>
+        <v>4700</v>
       </c>
       <c r="G228" t="inlineStr">
         <is>
@@ -7657,7 +7605,7 @@
         </is>
       </c>
       <c r="H228">
-        <v>2009</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="229">
@@ -7672,16 +7620,16 @@
         </is>
       </c>
       <c r="C229">
-        <v>50</v>
+        <v>48.6</v>
       </c>
       <c r="D229">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="E229">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="F229">
-        <v>5350</v>
+        <v>5800</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
@@ -7689,7 +7637,7 @@
         </is>
       </c>
       <c r="H229">
-        <v>2009</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="230">
@@ -7704,16 +7652,16 @@
         </is>
       </c>
       <c r="C230">
-        <v>44.9</v>
+        <v>47.5</v>
       </c>
       <c r="D230">
-        <v>13.8</v>
+        <v>14.2</v>
       </c>
       <c r="E230">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="F230">
-        <v>4750</v>
+        <v>4600</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
@@ -7721,7 +7669,7 @@
         </is>
       </c>
       <c r="H230">
-        <v>2009</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="231">
@@ -7736,16 +7684,16 @@
         </is>
       </c>
       <c r="C231">
-        <v>50.8</v>
+        <v>51.1</v>
       </c>
       <c r="D231">
-        <v>17.3</v>
+        <v>16.3</v>
       </c>
       <c r="E231">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="F231">
-        <v>5600</v>
+        <v>6000</v>
       </c>
       <c r="G231" t="inlineStr">
         <is>
@@ -7753,7 +7701,7 @@
         </is>
       </c>
       <c r="H231">
-        <v>2009</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="232">
@@ -7768,16 +7716,16 @@
         </is>
       </c>
       <c r="C232">
-        <v>43.4</v>
+        <v>45.2</v>
       </c>
       <c r="D232">
-        <v>14.4</v>
+        <v>13.8</v>
       </c>
       <c r="E232">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F232">
-        <v>4600</v>
+        <v>4750</v>
       </c>
       <c r="G232" t="inlineStr">
         <is>
@@ -7785,7 +7733,7 @@
         </is>
       </c>
       <c r="H232">
-        <v>2009</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="233">
@@ -7800,16 +7748,16 @@
         </is>
       </c>
       <c r="C233">
-        <v>51.3</v>
+        <v>45.2</v>
       </c>
       <c r="D233">
-        <v>14.2</v>
+        <v>16.4</v>
       </c>
       <c r="E233">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="F233">
-        <v>5300</v>
+        <v>5950</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
@@ -7817,7 +7765,7 @@
         </is>
       </c>
       <c r="H233">
-        <v>2009</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="234">
@@ -7832,16 +7780,16 @@
         </is>
       </c>
       <c r="C234">
-        <v>47.5</v>
+        <v>49.1</v>
       </c>
       <c r="D234">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="E234">
         <v>212</v>
       </c>
       <c r="F234">
-        <v>4875</v>
+        <v>4625</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
@@ -7864,16 +7812,16 @@
         </is>
       </c>
       <c r="C235">
-        <v>52.1</v>
+        <v>52.5</v>
       </c>
       <c r="D235">
-        <v>17</v>
+        <v>15.6</v>
       </c>
       <c r="E235">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="F235">
-        <v>5550</v>
+        <v>5450</v>
       </c>
       <c r="G235" t="inlineStr">
         <is>
@@ -7896,16 +7844,16 @@
         </is>
       </c>
       <c r="C236">
-        <v>47.5</v>
+        <v>47.4</v>
       </c>
       <c r="D236">
-        <v>15</v>
+        <v>14.6</v>
       </c>
       <c r="E236">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="F236">
-        <v>4950</v>
+        <v>4725</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
@@ -7928,16 +7876,16 @@
         </is>
       </c>
       <c r="C237">
-        <v>52.2</v>
+        <v>50</v>
       </c>
       <c r="D237">
-        <v>17.1</v>
+        <v>15.9</v>
       </c>
       <c r="E237">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="F237">
-        <v>5400</v>
+        <v>5350</v>
       </c>
       <c r="G237" t="inlineStr">
         <is>
@@ -7960,10 +7908,10 @@
         </is>
       </c>
       <c r="C238">
-        <v>45.5</v>
+        <v>44.9</v>
       </c>
       <c r="D238">
-        <v>14.5</v>
+        <v>13.8</v>
       </c>
       <c r="E238">
         <v>212</v>
@@ -7992,16 +7940,16 @@
         </is>
       </c>
       <c r="C239">
-        <v>49.5</v>
+        <v>50.8</v>
       </c>
       <c r="D239">
-        <v>16.1</v>
+        <v>17.3</v>
       </c>
       <c r="E239">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="F239">
-        <v>5650</v>
+        <v>5600</v>
       </c>
       <c r="G239" t="inlineStr">
         <is>
@@ -8024,16 +7972,16 @@
         </is>
       </c>
       <c r="C240">
-        <v>44.5</v>
+        <v>43.4</v>
       </c>
       <c r="D240">
-        <v>14.7</v>
+        <v>14.4</v>
       </c>
       <c r="E240">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="F240">
-        <v>4850</v>
+        <v>4600</v>
       </c>
       <c r="G240" t="inlineStr">
         <is>
@@ -8056,16 +8004,16 @@
         </is>
       </c>
       <c r="C241">
-        <v>50.8</v>
+        <v>51.3</v>
       </c>
       <c r="D241">
-        <v>15.7</v>
+        <v>14.2</v>
       </c>
       <c r="E241">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="F241">
-        <v>5200</v>
+        <v>5300</v>
       </c>
       <c r="G241" t="inlineStr">
         <is>
@@ -8088,20 +8036,20 @@
         </is>
       </c>
       <c r="C242">
-        <v>49.4</v>
+        <v>47.5</v>
       </c>
       <c r="D242">
-        <v>15.8</v>
+        <v>14</v>
       </c>
       <c r="E242">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="F242">
-        <v>4925</v>
+        <v>4875</v>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H242">
@@ -8120,20 +8068,20 @@
         </is>
       </c>
       <c r="C243">
-        <v>46.9</v>
+        <v>52.1</v>
       </c>
       <c r="D243">
-        <v>14.6</v>
+        <v>17</v>
       </c>
       <c r="E243">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="F243">
-        <v>4875</v>
+        <v>5550</v>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H243">
@@ -8152,16 +8100,16 @@
         </is>
       </c>
       <c r="C244">
-        <v>48.4</v>
+        <v>47.5</v>
       </c>
       <c r="D244">
-        <v>14.4</v>
+        <v>15</v>
       </c>
       <c r="E244">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="F244">
-        <v>4625</v>
+        <v>4950</v>
       </c>
       <c r="G244" t="inlineStr">
         <is>
@@ -8184,16 +8132,16 @@
         </is>
       </c>
       <c r="C245">
-        <v>51.1</v>
+        <v>52.2</v>
       </c>
       <c r="D245">
-        <v>16.5</v>
+        <v>17.1</v>
       </c>
       <c r="E245">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F245">
-        <v>5250</v>
+        <v>5400</v>
       </c>
       <c r="G245" t="inlineStr">
         <is>
@@ -8216,16 +8164,16 @@
         </is>
       </c>
       <c r="C246">
-        <v>48.5</v>
+        <v>45.5</v>
       </c>
       <c r="D246">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="E246">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="F246">
-        <v>4850</v>
+        <v>4750</v>
       </c>
       <c r="G246" t="inlineStr">
         <is>
@@ -8248,16 +8196,16 @@
         </is>
       </c>
       <c r="C247">
-        <v>55.9</v>
+        <v>49.5</v>
       </c>
       <c r="D247">
-        <v>17</v>
+        <v>16.1</v>
       </c>
       <c r="E247">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="F247">
-        <v>5600</v>
+        <v>5650</v>
       </c>
       <c r="G247" t="inlineStr">
         <is>
@@ -8280,16 +8228,16 @@
         </is>
       </c>
       <c r="C248">
-        <v>47.2</v>
+        <v>44.5</v>
       </c>
       <c r="D248">
-        <v>15.5</v>
+        <v>14.7</v>
       </c>
       <c r="E248">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F248">
-        <v>4975</v>
+        <v>4850</v>
       </c>
       <c r="G248" t="inlineStr">
         <is>
@@ -8312,16 +8260,16 @@
         </is>
       </c>
       <c r="C249">
-        <v>49.1</v>
+        <v>50.8</v>
       </c>
       <c r="D249">
-        <v>15</v>
+        <v>15.7</v>
       </c>
       <c r="E249">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="F249">
-        <v>5500</v>
+        <v>5200</v>
       </c>
       <c r="G249" t="inlineStr">
         <is>
@@ -8344,16 +8292,16 @@
         </is>
       </c>
       <c r="C250">
-        <v>46.8</v>
+        <v>49.4</v>
       </c>
       <c r="D250">
-        <v>16.1</v>
+        <v>15.8</v>
       </c>
       <c r="E250">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F250">
-        <v>5500</v>
+        <v>4925</v>
       </c>
       <c r="G250" t="inlineStr">
         <is>
@@ -8376,16 +8324,16 @@
         </is>
       </c>
       <c r="C251">
-        <v>41.7</v>
+        <v>46.9</v>
       </c>
       <c r="D251">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="E251">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="F251">
-        <v>4700</v>
+        <v>4875</v>
       </c>
       <c r="G251" t="inlineStr">
         <is>
@@ -8408,20 +8356,20 @@
         </is>
       </c>
       <c r="C252">
-        <v>53.4</v>
+        <v>48.4</v>
       </c>
       <c r="D252">
-        <v>15.8</v>
+        <v>14.4</v>
       </c>
       <c r="E252">
-        <v>219</v>
+        <v>203</v>
       </c>
       <c r="F252">
-        <v>5500</v>
+        <v>4625</v>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H252">
@@ -8440,20 +8388,20 @@
         </is>
       </c>
       <c r="C253">
-        <v>43.3</v>
+        <v>51.1</v>
       </c>
       <c r="D253">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="E253">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="F253">
-        <v>4575</v>
+        <v>5250</v>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H253">
@@ -8472,20 +8420,20 @@
         </is>
       </c>
       <c r="C254">
-        <v>48.1</v>
+        <v>48.5</v>
       </c>
       <c r="D254">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="E254">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F254">
-        <v>5500</v>
+        <v>4850</v>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H254">
@@ -8504,20 +8452,20 @@
         </is>
       </c>
       <c r="C255">
-        <v>50.5</v>
+        <v>55.9</v>
       </c>
       <c r="D255">
-        <v>15.2</v>
+        <v>17</v>
       </c>
       <c r="E255">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="F255">
-        <v>5000</v>
+        <v>5600</v>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H255">
@@ -8536,20 +8484,20 @@
         </is>
       </c>
       <c r="C256">
-        <v>49.8</v>
+        <v>47.2</v>
       </c>
       <c r="D256">
-        <v>15.9</v>
+        <v>15.5</v>
       </c>
       <c r="E256">
-        <v>229</v>
+        <v>215</v>
       </c>
       <c r="F256">
-        <v>5950</v>
+        <v>4975</v>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H256">
@@ -8568,20 +8516,20 @@
         </is>
       </c>
       <c r="C257">
-        <v>43.5</v>
+        <v>49.1</v>
       </c>
       <c r="D257">
-        <v>15.2</v>
+        <v>15</v>
       </c>
       <c r="E257">
-        <v>213</v>
+        <v>228</v>
       </c>
       <c r="F257">
-        <v>4650</v>
+        <v>5500</v>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H257">
@@ -8600,21 +8548,16 @@
         </is>
       </c>
       <c r="C258">
-        <v>51.5</v>
+        <v>47.3</v>
       </c>
       <c r="D258">
-        <v>16.3</v>
+        <v>13.8</v>
       </c>
       <c r="E258">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="F258">
-        <v>5500</v>
-      </c>
-      <c r="G258" t="inlineStr">
-        <is>
-          <t>male</t>
-        </is>
+        <v>4725</v>
       </c>
       <c r="H258">
         <v>2009</v>
@@ -8632,20 +8575,20 @@
         </is>
       </c>
       <c r="C259">
-        <v>46.2</v>
+        <v>46.8</v>
       </c>
       <c r="D259">
-        <v>14.1</v>
+        <v>16.1</v>
       </c>
       <c r="E259">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F259">
-        <v>4375</v>
+        <v>5500</v>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H259">
@@ -8664,20 +8607,20 @@
         </is>
       </c>
       <c r="C260">
-        <v>55.1</v>
+        <v>41.7</v>
       </c>
       <c r="D260">
-        <v>16</v>
+        <v>14.7</v>
       </c>
       <c r="E260">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="F260">
-        <v>5850</v>
+        <v>4700</v>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H260">
@@ -8696,16 +8639,16 @@
         </is>
       </c>
       <c r="C261">
-        <v>48.8</v>
+        <v>53.4</v>
       </c>
       <c r="D261">
-        <v>16.2</v>
+        <v>15.8</v>
       </c>
       <c r="E261">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F261">
-        <v>6000</v>
+        <v>5500</v>
       </c>
       <c r="G261" t="inlineStr">
         <is>
@@ -8728,16 +8671,16 @@
         </is>
       </c>
       <c r="C262">
-        <v>47.2</v>
+        <v>43.3</v>
       </c>
       <c r="D262">
-        <v>13.7</v>
+        <v>14</v>
       </c>
       <c r="E262">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="F262">
-        <v>4925</v>
+        <v>4575</v>
       </c>
       <c r="G262" t="inlineStr">
         <is>
@@ -8760,20 +8703,20 @@
         </is>
       </c>
       <c r="C263">
-        <v>46.8</v>
+        <v>48.1</v>
       </c>
       <c r="D263">
-        <v>14.3</v>
+        <v>15.1</v>
       </c>
       <c r="E263">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="F263">
-        <v>4850</v>
+        <v>5500</v>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H263">
@@ -8792,20 +8735,20 @@
         </is>
       </c>
       <c r="C264">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
       <c r="D264">
-        <v>15.7</v>
+        <v>15.2</v>
       </c>
       <c r="E264">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="F264">
-        <v>5750</v>
+        <v>5000</v>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H264">
@@ -8824,20 +8767,20 @@
         </is>
       </c>
       <c r="C265">
-        <v>45.2</v>
+        <v>49.8</v>
       </c>
       <c r="D265">
-        <v>14.8</v>
+        <v>15.9</v>
       </c>
       <c r="E265">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="F265">
-        <v>5200</v>
+        <v>5950</v>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H265">
@@ -8856,20 +8799,20 @@
         </is>
       </c>
       <c r="C266">
-        <v>49.9</v>
+        <v>43.5</v>
       </c>
       <c r="D266">
-        <v>16.1</v>
+        <v>15.2</v>
       </c>
       <c r="E266">
         <v>213</v>
       </c>
       <c r="F266">
-        <v>5400</v>
+        <v>4650</v>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H266">
@@ -8879,89 +8822,89 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Chinstrap</t>
+          <t>Gentoo</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Dream</t>
+          <t>Biscoe</t>
         </is>
       </c>
       <c r="C267">
-        <v>46.5</v>
+        <v>51.5</v>
       </c>
       <c r="D267">
-        <v>17.9</v>
+        <v>16.3</v>
       </c>
       <c r="E267">
-        <v>192</v>
+        <v>230</v>
       </c>
       <c r="F267">
-        <v>3500</v>
+        <v>5500</v>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H267">
-        <v>2007</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Chinstrap</t>
+          <t>Gentoo</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Dream</t>
+          <t>Biscoe</t>
         </is>
       </c>
       <c r="C268">
-        <v>50</v>
+        <v>46.2</v>
       </c>
       <c r="D268">
-        <v>19.5</v>
+        <v>14.1</v>
       </c>
       <c r="E268">
-        <v>196</v>
+        <v>217</v>
       </c>
       <c r="F268">
-        <v>3900</v>
+        <v>4375</v>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H268">
-        <v>2007</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Chinstrap</t>
+          <t>Gentoo</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>Dream</t>
+          <t>Biscoe</t>
         </is>
       </c>
       <c r="C269">
-        <v>51.3</v>
+        <v>55.1</v>
       </c>
       <c r="D269">
-        <v>19.2</v>
+        <v>16</v>
       </c>
       <c r="E269">
-        <v>193</v>
+        <v>230</v>
       </c>
       <c r="F269">
-        <v>3650</v>
+        <v>5850</v>
       </c>
       <c r="G269" t="inlineStr">
         <is>
@@ -8969,63 +8912,58 @@
         </is>
       </c>
       <c r="H269">
-        <v>2007</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Chinstrap</t>
+          <t>Gentoo</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>Dream</t>
+          <t>Biscoe</t>
         </is>
       </c>
       <c r="C270">
-        <v>45.4</v>
+        <v>44.5</v>
       </c>
       <c r="D270">
-        <v>18.7</v>
+        <v>15.7</v>
       </c>
       <c r="E270">
-        <v>188</v>
+        <v>217</v>
       </c>
       <c r="F270">
-        <v>3525</v>
-      </c>
-      <c r="G270" t="inlineStr">
-        <is>
-          <t>female</t>
-        </is>
+        <v>4875</v>
       </c>
       <c r="H270">
-        <v>2007</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>Chinstrap</t>
+          <t>Gentoo</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>Dream</t>
+          <t>Biscoe</t>
         </is>
       </c>
       <c r="C271">
-        <v>52.7</v>
+        <v>48.8</v>
       </c>
       <c r="D271">
-        <v>19.8</v>
+        <v>16.2</v>
       </c>
       <c r="E271">
-        <v>197</v>
+        <v>222</v>
       </c>
       <c r="F271">
-        <v>3725</v>
+        <v>6000</v>
       </c>
       <c r="G271" t="inlineStr">
         <is>
@@ -9033,31 +8971,31 @@
         </is>
       </c>
       <c r="H271">
-        <v>2007</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Chinstrap</t>
+          <t>Gentoo</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Dream</t>
+          <t>Biscoe</t>
         </is>
       </c>
       <c r="C272">
-        <v>45.2</v>
+        <v>47.2</v>
       </c>
       <c r="D272">
-        <v>17.8</v>
+        <v>13.7</v>
       </c>
       <c r="E272">
-        <v>198</v>
+        <v>214</v>
       </c>
       <c r="F272">
-        <v>3950</v>
+        <v>4925</v>
       </c>
       <c r="G272" t="inlineStr">
         <is>
@@ -9065,167 +9003,150 @@
         </is>
       </c>
       <c r="H272">
-        <v>2007</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Chinstrap</t>
+          <t>Gentoo</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>Dream</t>
-        </is>
-      </c>
-      <c r="C273">
-        <v>46.1</v>
-      </c>
-      <c r="D273">
-        <v>18.2</v>
-      </c>
-      <c r="E273">
-        <v>178</v>
-      </c>
-      <c r="F273">
-        <v>3250</v>
-      </c>
-      <c r="G273" t="inlineStr">
-        <is>
-          <t>female</t>
+          <t>Biscoe</t>
         </is>
       </c>
       <c r="H273">
-        <v>2007</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Chinstrap</t>
+          <t>Gentoo</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>Dream</t>
+          <t>Biscoe</t>
         </is>
       </c>
       <c r="C274">
-        <v>51.3</v>
+        <v>46.8</v>
       </c>
       <c r="D274">
-        <v>18.2</v>
+        <v>14.3</v>
       </c>
       <c r="E274">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="F274">
-        <v>3750</v>
+        <v>4850</v>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H274">
-        <v>2007</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Chinstrap</t>
+          <t>Gentoo</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>Dream</t>
+          <t>Biscoe</t>
         </is>
       </c>
       <c r="C275">
-        <v>46</v>
+        <v>50.4</v>
       </c>
       <c r="D275">
-        <v>18.9</v>
+        <v>15.7</v>
       </c>
       <c r="E275">
-        <v>195</v>
+        <v>222</v>
       </c>
       <c r="F275">
-        <v>4150</v>
+        <v>5750</v>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H275">
-        <v>2007</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Chinstrap</t>
+          <t>Gentoo</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>Dream</t>
+          <t>Biscoe</t>
         </is>
       </c>
       <c r="C276">
-        <v>51.3</v>
+        <v>45.2</v>
       </c>
       <c r="D276">
-        <v>19.9</v>
+        <v>14.8</v>
       </c>
       <c r="E276">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="F276">
-        <v>3700</v>
+        <v>5200</v>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H276">
-        <v>2007</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Chinstrap</t>
+          <t>Gentoo</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>Dream</t>
+          <t>Biscoe</t>
         </is>
       </c>
       <c r="C277">
-        <v>46.6</v>
+        <v>49.9</v>
       </c>
       <c r="D277">
-        <v>17.8</v>
+        <v>16.1</v>
       </c>
       <c r="E277">
-        <v>193</v>
+        <v>213</v>
       </c>
       <c r="F277">
-        <v>3800</v>
+        <v>5400</v>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H277">
-        <v>2007</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="278">
@@ -9240,20 +9161,20 @@
         </is>
       </c>
       <c r="C278">
-        <v>51.7</v>
+        <v>46.5</v>
       </c>
       <c r="D278">
-        <v>20.3</v>
+        <v>17.9</v>
       </c>
       <c r="E278">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F278">
-        <v>3775</v>
+        <v>3500</v>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H278">
@@ -9272,20 +9193,20 @@
         </is>
       </c>
       <c r="C279">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D279">
-        <v>17.3</v>
+        <v>19.5</v>
       </c>
       <c r="E279">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="F279">
-        <v>3700</v>
+        <v>3900</v>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H279">
@@ -9304,16 +9225,16 @@
         </is>
       </c>
       <c r="C280">
-        <v>52</v>
+        <v>51.3</v>
       </c>
       <c r="D280">
-        <v>18.1</v>
+        <v>19.2</v>
       </c>
       <c r="E280">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="F280">
-        <v>4050</v>
+        <v>3650</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
@@ -9336,16 +9257,16 @@
         </is>
       </c>
       <c r="C281">
-        <v>45.9</v>
+        <v>45.4</v>
       </c>
       <c r="D281">
-        <v>17.1</v>
+        <v>18.7</v>
       </c>
       <c r="E281">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F281">
-        <v>3575</v>
+        <v>3525</v>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -9368,16 +9289,16 @@
         </is>
       </c>
       <c r="C282">
-        <v>50.5</v>
+        <v>52.7</v>
       </c>
       <c r="D282">
-        <v>19.6</v>
+        <v>19.8</v>
       </c>
       <c r="E282">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="F282">
-        <v>4050</v>
+        <v>3725</v>
       </c>
       <c r="G282" t="inlineStr">
         <is>
@@ -9400,20 +9321,20 @@
         </is>
       </c>
       <c r="C283">
-        <v>50.3</v>
+        <v>45.2</v>
       </c>
       <c r="D283">
-        <v>20</v>
+        <v>17.8</v>
       </c>
       <c r="E283">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F283">
-        <v>3300</v>
+        <v>3950</v>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H283">
@@ -9432,16 +9353,16 @@
         </is>
       </c>
       <c r="C284">
-        <v>58</v>
+        <v>46.1</v>
       </c>
       <c r="D284">
-        <v>17.8</v>
+        <v>18.2</v>
       </c>
       <c r="E284">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="F284">
-        <v>3700</v>
+        <v>3250</v>
       </c>
       <c r="G284" t="inlineStr">
         <is>
@@ -9464,20 +9385,20 @@
         </is>
       </c>
       <c r="C285">
-        <v>46.4</v>
+        <v>51.3</v>
       </c>
       <c r="D285">
-        <v>18.6</v>
+        <v>18.2</v>
       </c>
       <c r="E285">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="F285">
-        <v>3450</v>
+        <v>3750</v>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H285">
@@ -9496,20 +9417,20 @@
         </is>
       </c>
       <c r="C286">
-        <v>49.2</v>
+        <v>46</v>
       </c>
       <c r="D286">
-        <v>18.2</v>
+        <v>18.9</v>
       </c>
       <c r="E286">
         <v>195</v>
       </c>
       <c r="F286">
-        <v>4400</v>
+        <v>4150</v>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H286">
@@ -9528,20 +9449,20 @@
         </is>
       </c>
       <c r="C287">
-        <v>42.4</v>
+        <v>51.3</v>
       </c>
       <c r="D287">
-        <v>17.3</v>
+        <v>19.9</v>
       </c>
       <c r="E287">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="F287">
-        <v>3600</v>
+        <v>3700</v>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H287">
@@ -9560,20 +9481,20 @@
         </is>
       </c>
       <c r="C288">
-        <v>48.5</v>
+        <v>46.6</v>
       </c>
       <c r="D288">
-        <v>17.5</v>
+        <v>17.8</v>
       </c>
       <c r="E288">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F288">
-        <v>3400</v>
+        <v>3800</v>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H288">
@@ -9592,20 +9513,20 @@
         </is>
       </c>
       <c r="C289">
-        <v>43.2</v>
+        <v>51.7</v>
       </c>
       <c r="D289">
-        <v>16.6</v>
+        <v>20.3</v>
       </c>
       <c r="E289">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="F289">
-        <v>2900</v>
+        <v>3775</v>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H289">
@@ -9624,20 +9545,20 @@
         </is>
       </c>
       <c r="C290">
-        <v>50.6</v>
+        <v>47</v>
       </c>
       <c r="D290">
-        <v>19.4</v>
+        <v>17.3</v>
       </c>
       <c r="E290">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="F290">
-        <v>3800</v>
+        <v>3700</v>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H290">
@@ -9656,20 +9577,20 @@
         </is>
       </c>
       <c r="C291">
-        <v>46.7</v>
+        <v>52</v>
       </c>
       <c r="D291">
-        <v>17.9</v>
+        <v>18.1</v>
       </c>
       <c r="E291">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="F291">
-        <v>3300</v>
+        <v>4050</v>
       </c>
       <c r="G291" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H291">
@@ -9688,20 +9609,20 @@
         </is>
       </c>
       <c r="C292">
-        <v>52</v>
+        <v>45.9</v>
       </c>
       <c r="D292">
-        <v>19</v>
+        <v>17.1</v>
       </c>
       <c r="E292">
-        <v>197</v>
+        <v>190</v>
       </c>
       <c r="F292">
-        <v>4150</v>
+        <v>3575</v>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H292">
@@ -9723,21 +9644,21 @@
         <v>50.5</v>
       </c>
       <c r="D293">
-        <v>18.4</v>
+        <v>19.6</v>
       </c>
       <c r="E293">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F293">
-        <v>3400</v>
+        <v>4050</v>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H293">
-        <v>2008</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="294">
@@ -9752,16 +9673,16 @@
         </is>
       </c>
       <c r="C294">
-        <v>49.5</v>
+        <v>50.3</v>
       </c>
       <c r="D294">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E294">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F294">
-        <v>3800</v>
+        <v>3300</v>
       </c>
       <c r="G294" t="inlineStr">
         <is>
@@ -9769,7 +9690,7 @@
         </is>
       </c>
       <c r="H294">
-        <v>2008</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="295">
@@ -9784,13 +9705,13 @@
         </is>
       </c>
       <c r="C295">
-        <v>46.4</v>
+        <v>58</v>
       </c>
       <c r="D295">
         <v>17.8</v>
       </c>
       <c r="E295">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="F295">
         <v>3700</v>
@@ -9801,7 +9722,7 @@
         </is>
       </c>
       <c r="H295">
-        <v>2008</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="296">
@@ -9816,24 +9737,24 @@
         </is>
       </c>
       <c r="C296">
-        <v>52.8</v>
+        <v>46.4</v>
       </c>
       <c r="D296">
-        <v>20</v>
+        <v>18.6</v>
       </c>
       <c r="E296">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="F296">
-        <v>4550</v>
+        <v>3450</v>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H296">
-        <v>2008</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="297">
@@ -9848,24 +9769,24 @@
         </is>
       </c>
       <c r="C297">
-        <v>40.9</v>
+        <v>49.2</v>
       </c>
       <c r="D297">
-        <v>16.6</v>
+        <v>18.2</v>
       </c>
       <c r="E297">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="F297">
-        <v>3200</v>
+        <v>4400</v>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H297">
-        <v>2008</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="298">
@@ -9880,24 +9801,24 @@
         </is>
       </c>
       <c r="C298">
-        <v>54.2</v>
+        <v>42.4</v>
       </c>
       <c r="D298">
-        <v>20.8</v>
+        <v>17.3</v>
       </c>
       <c r="E298">
-        <v>201</v>
+        <v>181</v>
       </c>
       <c r="F298">
-        <v>4300</v>
+        <v>3600</v>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H298">
-        <v>2008</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="299">
@@ -9912,24 +9833,24 @@
         </is>
       </c>
       <c r="C299">
-        <v>42.5</v>
+        <v>48.5</v>
       </c>
       <c r="D299">
-        <v>16.7</v>
+        <v>17.5</v>
       </c>
       <c r="E299">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="F299">
-        <v>3350</v>
+        <v>3400</v>
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H299">
-        <v>2008</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="300">
@@ -9944,24 +9865,24 @@
         </is>
       </c>
       <c r="C300">
-        <v>51</v>
+        <v>43.2</v>
       </c>
       <c r="D300">
-        <v>18.8</v>
+        <v>16.6</v>
       </c>
       <c r="E300">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="F300">
-        <v>4100</v>
+        <v>2900</v>
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H300">
-        <v>2008</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="301">
@@ -9976,16 +9897,16 @@
         </is>
       </c>
       <c r="C301">
-        <v>49.7</v>
+        <v>50.6</v>
       </c>
       <c r="D301">
-        <v>18.6</v>
+        <v>19.4</v>
       </c>
       <c r="E301">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="F301">
-        <v>3600</v>
+        <v>3800</v>
       </c>
       <c r="G301" t="inlineStr">
         <is>
@@ -9993,7 +9914,7 @@
         </is>
       </c>
       <c r="H301">
-        <v>2008</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="302">
@@ -10008,16 +9929,16 @@
         </is>
       </c>
       <c r="C302">
-        <v>47.5</v>
+        <v>46.7</v>
       </c>
       <c r="D302">
-        <v>16.8</v>
+        <v>17.9</v>
       </c>
       <c r="E302">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="F302">
-        <v>3900</v>
+        <v>3300</v>
       </c>
       <c r="G302" t="inlineStr">
         <is>
@@ -10025,7 +9946,7 @@
         </is>
       </c>
       <c r="H302">
-        <v>2008</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="303">
@@ -10040,24 +9961,24 @@
         </is>
       </c>
       <c r="C303">
-        <v>47.6</v>
+        <v>52</v>
       </c>
       <c r="D303">
-        <v>18.3</v>
+        <v>19</v>
       </c>
       <c r="E303">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="F303">
-        <v>3850</v>
+        <v>4150</v>
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H303">
-        <v>2008</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="304">
@@ -10072,20 +9993,20 @@
         </is>
       </c>
       <c r="C304">
-        <v>52</v>
+        <v>50.5</v>
       </c>
       <c r="D304">
-        <v>20.7</v>
+        <v>18.4</v>
       </c>
       <c r="E304">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="F304">
-        <v>4800</v>
+        <v>3400</v>
       </c>
       <c r="G304" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H304">
@@ -10104,20 +10025,20 @@
         </is>
       </c>
       <c r="C305">
-        <v>46.9</v>
+        <v>49.5</v>
       </c>
       <c r="D305">
-        <v>16.6</v>
+        <v>19</v>
       </c>
       <c r="E305">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="F305">
-        <v>2700</v>
+        <v>3800</v>
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H305">
@@ -10136,20 +10057,20 @@
         </is>
       </c>
       <c r="C306">
-        <v>53.5</v>
+        <v>46.4</v>
       </c>
       <c r="D306">
-        <v>19.9</v>
+        <v>17.8</v>
       </c>
       <c r="E306">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="F306">
-        <v>4500</v>
+        <v>3700</v>
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H306">
@@ -10168,16 +10089,16 @@
         </is>
       </c>
       <c r="C307">
-        <v>49</v>
+        <v>52.8</v>
       </c>
       <c r="D307">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="E307">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="F307">
-        <v>3950</v>
+        <v>4550</v>
       </c>
       <c r="G307" t="inlineStr">
         <is>
@@ -10200,16 +10121,16 @@
         </is>
       </c>
       <c r="C308">
-        <v>46.2</v>
+        <v>40.9</v>
       </c>
       <c r="D308">
-        <v>17.5</v>
+        <v>16.6</v>
       </c>
       <c r="E308">
         <v>187</v>
       </c>
       <c r="F308">
-        <v>3650</v>
+        <v>3200</v>
       </c>
       <c r="G308" t="inlineStr">
         <is>
@@ -10232,16 +10153,16 @@
         </is>
       </c>
       <c r="C309">
-        <v>50.9</v>
+        <v>54.2</v>
       </c>
       <c r="D309">
-        <v>19.1</v>
+        <v>20.8</v>
       </c>
       <c r="E309">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="F309">
-        <v>3550</v>
+        <v>4300</v>
       </c>
       <c r="G309" t="inlineStr">
         <is>
@@ -10264,16 +10185,16 @@
         </is>
       </c>
       <c r="C310">
-        <v>45.5</v>
+        <v>42.5</v>
       </c>
       <c r="D310">
-        <v>17</v>
+        <v>16.7</v>
       </c>
       <c r="E310">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="F310">
-        <v>3500</v>
+        <v>3350</v>
       </c>
       <c r="G310" t="inlineStr">
         <is>
@@ -10296,24 +10217,24 @@
         </is>
       </c>
       <c r="C311">
-        <v>50.9</v>
+        <v>51</v>
       </c>
       <c r="D311">
-        <v>17.9</v>
+        <v>18.8</v>
       </c>
       <c r="E311">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="F311">
-        <v>3675</v>
+        <v>4100</v>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H311">
-        <v>2009</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="312">
@@ -10328,16 +10249,16 @@
         </is>
       </c>
       <c r="C312">
-        <v>50.8</v>
+        <v>49.7</v>
       </c>
       <c r="D312">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="E312">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="F312">
-        <v>4450</v>
+        <v>3600</v>
       </c>
       <c r="G312" t="inlineStr">
         <is>
@@ -10345,7 +10266,7 @@
         </is>
       </c>
       <c r="H312">
-        <v>2009</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="313">
@@ -10360,16 +10281,16 @@
         </is>
       </c>
       <c r="C313">
-        <v>50.1</v>
+        <v>47.5</v>
       </c>
       <c r="D313">
-        <v>17.9</v>
+        <v>16.8</v>
       </c>
       <c r="E313">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="F313">
-        <v>3400</v>
+        <v>3900</v>
       </c>
       <c r="G313" t="inlineStr">
         <is>
@@ -10377,7 +10298,7 @@
         </is>
       </c>
       <c r="H313">
-        <v>2009</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="314">
@@ -10392,24 +10313,24 @@
         </is>
       </c>
       <c r="C314">
-        <v>49</v>
+        <v>47.6</v>
       </c>
       <c r="D314">
-        <v>19.6</v>
+        <v>18.3</v>
       </c>
       <c r="E314">
-        <v>212</v>
+        <v>195</v>
       </c>
       <c r="F314">
-        <v>4300</v>
+        <v>3850</v>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H314">
-        <v>2009</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="315">
@@ -10424,16 +10345,16 @@
         </is>
       </c>
       <c r="C315">
-        <v>51.5</v>
+        <v>52</v>
       </c>
       <c r="D315">
-        <v>18.7</v>
+        <v>20.7</v>
       </c>
       <c r="E315">
-        <v>187</v>
+        <v>210</v>
       </c>
       <c r="F315">
-        <v>3250</v>
+        <v>4800</v>
       </c>
       <c r="G315" t="inlineStr">
         <is>
@@ -10441,7 +10362,7 @@
         </is>
       </c>
       <c r="H315">
-        <v>2009</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="316">
@@ -10456,16 +10377,16 @@
         </is>
       </c>
       <c r="C316">
-        <v>49.8</v>
+        <v>46.9</v>
       </c>
       <c r="D316">
-        <v>17.3</v>
+        <v>16.6</v>
       </c>
       <c r="E316">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="F316">
-        <v>3675</v>
+        <v>2700</v>
       </c>
       <c r="G316" t="inlineStr">
         <is>
@@ -10473,7 +10394,7 @@
         </is>
       </c>
       <c r="H316">
-        <v>2009</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="317">
@@ -10488,24 +10409,24 @@
         </is>
       </c>
       <c r="C317">
-        <v>48.1</v>
+        <v>53.5</v>
       </c>
       <c r="D317">
-        <v>16.4</v>
+        <v>19.9</v>
       </c>
       <c r="E317">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="F317">
-        <v>3325</v>
+        <v>4500</v>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H317">
-        <v>2009</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="318">
@@ -10520,13 +10441,13 @@
         </is>
       </c>
       <c r="C318">
-        <v>51.4</v>
+        <v>49</v>
       </c>
       <c r="D318">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="E318">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="F318">
         <v>3950</v>
@@ -10537,7 +10458,7 @@
         </is>
       </c>
       <c r="H318">
-        <v>2009</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="319">
@@ -10552,16 +10473,16 @@
         </is>
       </c>
       <c r="C319">
-        <v>45.7</v>
+        <v>46.2</v>
       </c>
       <c r="D319">
-        <v>17.3</v>
+        <v>17.5</v>
       </c>
       <c r="E319">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="F319">
-        <v>3600</v>
+        <v>3650</v>
       </c>
       <c r="G319" t="inlineStr">
         <is>
@@ -10569,7 +10490,7 @@
         </is>
       </c>
       <c r="H319">
-        <v>2009</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="320">
@@ -10584,16 +10505,16 @@
         </is>
       </c>
       <c r="C320">
-        <v>50.7</v>
+        <v>50.9</v>
       </c>
       <c r="D320">
-        <v>19.7</v>
+        <v>19.1</v>
       </c>
       <c r="E320">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="F320">
-        <v>4050</v>
+        <v>3550</v>
       </c>
       <c r="G320" t="inlineStr">
         <is>
@@ -10601,7 +10522,7 @@
         </is>
       </c>
       <c r="H320">
-        <v>2009</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="321">
@@ -10616,16 +10537,16 @@
         </is>
       </c>
       <c r="C321">
-        <v>42.5</v>
+        <v>45.5</v>
       </c>
       <c r="D321">
-        <v>17.3</v>
+        <v>17</v>
       </c>
       <c r="E321">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="F321">
-        <v>3350</v>
+        <v>3500</v>
       </c>
       <c r="G321" t="inlineStr">
         <is>
@@ -10633,7 +10554,7 @@
         </is>
       </c>
       <c r="H321">
-        <v>2009</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="322">
@@ -10648,20 +10569,20 @@
         </is>
       </c>
       <c r="C322">
-        <v>52.2</v>
+        <v>50.9</v>
       </c>
       <c r="D322">
-        <v>18.8</v>
+        <v>17.9</v>
       </c>
       <c r="E322">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F322">
-        <v>3450</v>
+        <v>3675</v>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H322">
@@ -10680,20 +10601,20 @@
         </is>
       </c>
       <c r="C323">
-        <v>45.2</v>
+        <v>50.8</v>
       </c>
       <c r="D323">
-        <v>16.6</v>
+        <v>18.5</v>
       </c>
       <c r="E323">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="F323">
-        <v>3250</v>
+        <v>4450</v>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H323">
@@ -10712,20 +10633,20 @@
         </is>
       </c>
       <c r="C324">
-        <v>49.3</v>
+        <v>50.1</v>
       </c>
       <c r="D324">
-        <v>19.9</v>
+        <v>17.9</v>
       </c>
       <c r="E324">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="F324">
-        <v>4050</v>
+        <v>3400</v>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H324">
@@ -10744,16 +10665,16 @@
         </is>
       </c>
       <c r="C325">
-        <v>50.2</v>
+        <v>49</v>
       </c>
       <c r="D325">
-        <v>18.8</v>
+        <v>19.6</v>
       </c>
       <c r="E325">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="F325">
-        <v>3800</v>
+        <v>4300</v>
       </c>
       <c r="G325" t="inlineStr">
         <is>
@@ -10776,20 +10697,20 @@
         </is>
       </c>
       <c r="C326">
-        <v>45.6</v>
+        <v>51.5</v>
       </c>
       <c r="D326">
-        <v>19.4</v>
+        <v>18.7</v>
       </c>
       <c r="E326">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="F326">
-        <v>3525</v>
+        <v>3250</v>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H326">
@@ -10808,20 +10729,20 @@
         </is>
       </c>
       <c r="C327">
-        <v>51.9</v>
+        <v>49.8</v>
       </c>
       <c r="D327">
-        <v>19.5</v>
+        <v>17.3</v>
       </c>
       <c r="E327">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="F327">
-        <v>3950</v>
+        <v>3675</v>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H327">
@@ -10840,16 +10761,16 @@
         </is>
       </c>
       <c r="C328">
-        <v>46.8</v>
+        <v>48.1</v>
       </c>
       <c r="D328">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="E328">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="F328">
-        <v>3650</v>
+        <v>3325</v>
       </c>
       <c r="G328" t="inlineStr">
         <is>
@@ -10872,20 +10793,20 @@
         </is>
       </c>
       <c r="C329">
-        <v>45.7</v>
+        <v>51.4</v>
       </c>
       <c r="D329">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E329">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="F329">
-        <v>3650</v>
+        <v>3950</v>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H329">
@@ -10904,20 +10825,20 @@
         </is>
       </c>
       <c r="C330">
-        <v>55.8</v>
+        <v>45.7</v>
       </c>
       <c r="D330">
-        <v>19.8</v>
+        <v>17.3</v>
       </c>
       <c r="E330">
-        <v>207</v>
+        <v>193</v>
       </c>
       <c r="F330">
-        <v>4000</v>
+        <v>3600</v>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H330">
@@ -10936,20 +10857,20 @@
         </is>
       </c>
       <c r="C331">
-        <v>43.5</v>
+        <v>50.7</v>
       </c>
       <c r="D331">
-        <v>18.1</v>
+        <v>19.7</v>
       </c>
       <c r="E331">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F331">
-        <v>3400</v>
+        <v>4050</v>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>female</t>
+          <t>male</t>
         </is>
       </c>
       <c r="H331">
@@ -10968,20 +10889,20 @@
         </is>
       </c>
       <c r="C332">
-        <v>49.6</v>
+        <v>42.5</v>
       </c>
       <c r="D332">
-        <v>18.2</v>
+        <v>17.3</v>
       </c>
       <c r="E332">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="F332">
-        <v>3775</v>
+        <v>3350</v>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>male</t>
+          <t>female</t>
         </is>
       </c>
       <c r="H332">
@@ -11000,16 +10921,16 @@
         </is>
       </c>
       <c r="C333">
-        <v>50.8</v>
+        <v>52.2</v>
       </c>
       <c r="D333">
-        <v>19</v>
+        <v>18.8</v>
       </c>
       <c r="E333">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="F333">
-        <v>4100</v>
+        <v>3450</v>
       </c>
       <c r="G333" t="inlineStr">
         <is>
@@ -11032,23 +10953,375 @@
         </is>
       </c>
       <c r="C334">
+        <v>45.2</v>
+      </c>
+      <c r="D334">
+        <v>16.6</v>
+      </c>
+      <c r="E334">
+        <v>191</v>
+      </c>
+      <c r="F334">
+        <v>3250</v>
+      </c>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
+      <c r="H334">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Chinstrap</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Dream</t>
+        </is>
+      </c>
+      <c r="C335">
+        <v>49.3</v>
+      </c>
+      <c r="D335">
+        <v>19.9</v>
+      </c>
+      <c r="E335">
+        <v>203</v>
+      </c>
+      <c r="F335">
+        <v>4050</v>
+      </c>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="H335">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Chinstrap</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>Dream</t>
+        </is>
+      </c>
+      <c r="C336">
         <v>50.2</v>
       </c>
-      <c r="D334">
+      <c r="D336">
+        <v>18.8</v>
+      </c>
+      <c r="E336">
+        <v>202</v>
+      </c>
+      <c r="F336">
+        <v>3800</v>
+      </c>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="H336">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Chinstrap</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Dream</t>
+        </is>
+      </c>
+      <c r="C337">
+        <v>45.6</v>
+      </c>
+      <c r="D337">
+        <v>19.4</v>
+      </c>
+      <c r="E337">
+        <v>194</v>
+      </c>
+      <c r="F337">
+        <v>3525</v>
+      </c>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
+      <c r="H337">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Chinstrap</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Dream</t>
+        </is>
+      </c>
+      <c r="C338">
+        <v>51.9</v>
+      </c>
+      <c r="D338">
+        <v>19.5</v>
+      </c>
+      <c r="E338">
+        <v>206</v>
+      </c>
+      <c r="F338">
+        <v>3950</v>
+      </c>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="H338">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Chinstrap</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Dream</t>
+        </is>
+      </c>
+      <c r="C339">
+        <v>46.8</v>
+      </c>
+      <c r="D339">
+        <v>16.5</v>
+      </c>
+      <c r="E339">
+        <v>189</v>
+      </c>
+      <c r="F339">
+        <v>3650</v>
+      </c>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
+      <c r="H339">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Chinstrap</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Dream</t>
+        </is>
+      </c>
+      <c r="C340">
+        <v>45.7</v>
+      </c>
+      <c r="D340">
+        <v>17</v>
+      </c>
+      <c r="E340">
+        <v>195</v>
+      </c>
+      <c r="F340">
+        <v>3650</v>
+      </c>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
+      <c r="H340">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Chinstrap</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Dream</t>
+        </is>
+      </c>
+      <c r="C341">
+        <v>55.8</v>
+      </c>
+      <c r="D341">
+        <v>19.8</v>
+      </c>
+      <c r="E341">
+        <v>207</v>
+      </c>
+      <c r="F341">
+        <v>4000</v>
+      </c>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="H341">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Chinstrap</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Dream</t>
+        </is>
+      </c>
+      <c r="C342">
+        <v>43.5</v>
+      </c>
+      <c r="D342">
+        <v>18.1</v>
+      </c>
+      <c r="E342">
+        <v>202</v>
+      </c>
+      <c r="F342">
+        <v>3400</v>
+      </c>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
+      <c r="H342">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Chinstrap</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Dream</t>
+        </is>
+      </c>
+      <c r="C343">
+        <v>49.6</v>
+      </c>
+      <c r="D343">
+        <v>18.2</v>
+      </c>
+      <c r="E343">
+        <v>193</v>
+      </c>
+      <c r="F343">
+        <v>3775</v>
+      </c>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="H343">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Chinstrap</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Dream</t>
+        </is>
+      </c>
+      <c r="C344">
+        <v>50.8</v>
+      </c>
+      <c r="D344">
+        <v>19</v>
+      </c>
+      <c r="E344">
+        <v>210</v>
+      </c>
+      <c r="F344">
+        <v>4100</v>
+      </c>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+      <c r="H344">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Chinstrap</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Dream</t>
+        </is>
+      </c>
+      <c r="C345">
+        <v>50.2</v>
+      </c>
+      <c r="D345">
         <v>18.7</v>
       </c>
-      <c r="E334">
+      <c r="E345">
         <v>198</v>
       </c>
-      <c r="F334">
+      <c r="F345">
         <v>3775</v>
       </c>
-      <c r="G334" t="inlineStr">
-        <is>
-          <t>female</t>
-        </is>
-      </c>
-      <c r="H334">
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
+      <c r="H345">
         <v>2009</v>
       </c>
     </row>
